--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -1,16 +1,10 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="11028"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+  <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/environment/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB69C9F5-7824-EF4C-A9A8-68A65BE12C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34980" yWindow="-500" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView windowWidth="19095" windowHeight="7470" activeTab="1"/>
   </bookViews>
   <sheets>
     <sheet name="工程局" sheetId="1" r:id="rId1"/>
@@ -19,12 +13,12 @@
     <sheet name="摆件" sheetId="6" r:id="rId4"/>
     <sheet name="赛车" sheetId="7" r:id="rId5"/>
   </sheets>
-  <calcPr calcId="0"/>
+  <calcPr calcId="144525"/>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="395">
   <si>
     <t>名称</t>
   </si>
@@ -371,9 +365,18 @@
     <t>小型船猪飞</t>
   </si>
   <si>
+    <t>Supply_Damage</t>
+  </si>
+  <si>
+    <t>公正的决斗</t>
+  </si>
+  <si>
     <t>Event_DD_torpedo</t>
   </si>
   <si>
+    <t>鱼雷海</t>
+  </si>
+  <si>
     <t>FirstTorpedoPhase</t>
   </si>
   <si>
@@ -386,6 +389,60 @@
     <t>U国无视战损</t>
   </si>
   <si>
+    <t>Event_SanDiego</t>
+  </si>
+  <si>
+    <t>Cid(157)</t>
+  </si>
+  <si>
+    <t>圣地亚哥专属</t>
+  </si>
+  <si>
+    <t>AllPhase:2.18</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_1</t>
+  </si>
+  <si>
+    <t>暴风1</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_2</t>
+  </si>
+  <si>
+    <t>暴风2</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_3</t>
+  </si>
+  <si>
+    <t>暴风3</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_4</t>
+  </si>
+  <si>
+    <t>暴风4</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_5</t>
+  </si>
+  <si>
+    <t>暴风5</t>
+  </si>
+  <si>
+    <t>Strike_Stormy_6</t>
+  </si>
+  <si>
+    <t>暴风6</t>
+  </si>
+  <si>
+    <t>E1_CVL_Buff</t>
+  </si>
+  <si>
+    <t>中型火命+10</t>
+  </si>
+  <si>
     <t>Dish_I_Fire</t>
   </si>
   <si>
@@ -680,555 +737,843 @@
     <t>威尼斯墨鱼面(I国对空+7)</t>
   </si>
   <si>
+    <t>Collection_E_BB_Evasion</t>
+  </si>
+  <si>
     <t>胡德船模(E国BB回避+3)</t>
   </si>
   <si>
+    <t>Collection_J_DD_Fire</t>
+  </si>
+  <si>
     <t>咸鱼(J国DD火力+3)</t>
   </si>
   <si>
+    <t>Collection_C_Luck</t>
+  </si>
+  <si>
     <t>002(C国幸运+3)</t>
   </si>
   <si>
+    <t>Collection_E_DD_Fire</t>
+  </si>
+  <si>
     <t>坎贝尔敦船模(E国DD火力+3)</t>
   </si>
   <si>
+    <t>Collection_U_DD_Recon</t>
+  </si>
+  <si>
     <t>海军软飞艇(U国DD索敌+3)</t>
   </si>
   <si>
+    <t>Collection_I_DD_Torpedo</t>
+  </si>
+  <si>
     <t>摩托鱼雷(I国DD鱼雷+3)</t>
   </si>
   <si>
+    <t>Collection_U_CL_Recon</t>
+  </si>
+  <si>
     <t>千里眼(U国CL索敌+3)</t>
   </si>
   <si>
+    <t>Collection_S_Fire</t>
+  </si>
+  <si>
     <t>捡到的皮鞋(S国火力+3)</t>
   </si>
   <si>
+    <t>Collection_J_Accuracy</t>
+  </si>
+  <si>
     <t>比叡火控仪(J国命中+2)</t>
   </si>
   <si>
+    <t>Collection_BB_Fire</t>
+  </si>
+  <si>
     <t>莫尼特(BB火力+2)</t>
   </si>
   <si>
+    <t>Collection_U_CA_Antiair</t>
+  </si>
+  <si>
     <t>阿图岛的飞机(U国CA对空+3)</t>
   </si>
   <si>
+    <t>Collection_E_BC_Fire</t>
+  </si>
+  <si>
     <t>大剑（杰克）(E国BC火力+2)</t>
   </si>
   <si>
+    <t>Collection_J_DD_Torpedo</t>
+  </si>
+  <si>
     <t>长矛鱼雷(J国DD鱼雷+2)</t>
   </si>
   <si>
+    <t>Collection_C_Fire</t>
+  </si>
+  <si>
     <t>037战列艇(C国火力+3)</t>
   </si>
   <si>
+    <t>Collection_I_Evasion</t>
+  </si>
+  <si>
     <t>马基.72(I国回避+3)</t>
   </si>
   <si>
+    <t>Collection_Luck</t>
+  </si>
+  <si>
     <t>桌面战记—深海篇(所有船幸运+1)</t>
   </si>
   <si>
+    <t>Collection_G_BC_Fire</t>
+  </si>
+  <si>
     <t>袭击舰炮塔(G国BC火力+2)</t>
   </si>
   <si>
+    <t>Collection_U_CV_Accuracy</t>
+  </si>
+  <si>
     <t>第八鱼雷机中队(U国CV命中+2)</t>
   </si>
   <si>
+    <t>Collection_BB_Antiair</t>
+  </si>
+  <si>
     <t>金笔(BB对空+2)</t>
   </si>
   <si>
+    <t>Collection_E_Antiair</t>
+  </si>
+  <si>
     <t>不列颠战机(E国对空+3)</t>
   </si>
   <si>
+    <t>Collection_BC_Accuracy</t>
+  </si>
+  <si>
     <t>海权(BC命中+2)</t>
   </si>
   <si>
+    <t>Collection_BB_Armor</t>
+  </si>
+  <si>
     <t>瓦伦丁(BB装甲+2)</t>
   </si>
   <si>
+    <t>Collection_U_Torpedo</t>
+  </si>
+  <si>
     <t>PT快艇(U国鱼雷+3)</t>
   </si>
   <si>
+    <t>Collection_J_BB_Fire</t>
+  </si>
+  <si>
     <t>扭曲烟突(J国BB火力+3)</t>
   </si>
   <si>
+    <t>Collection_S_Accuracy</t>
+  </si>
+  <si>
     <t>拖拉机(S国命中+3)</t>
   </si>
   <si>
+    <t>Collection_S_CL_Fire</t>
+  </si>
+  <si>
     <t>模拟磁带(S国CL火力+3)</t>
   </si>
   <si>
+    <t>Collection_G_BB_Evasion</t>
+  </si>
+  <si>
     <t>战列巡洋舰(G国BB回避+2)</t>
   </si>
   <si>
+    <t>Collection_G_BB_Fire</t>
+  </si>
+  <si>
     <t>巨型飞艇(G国BB火力+2)</t>
   </si>
   <si>
+    <t>Collection_U_Accuracy</t>
+  </si>
+  <si>
     <t>八英寸连装炮(U国命中+2)</t>
   </si>
   <si>
+    <t>Collection_SS_Torpedo</t>
+  </si>
+  <si>
     <t>魔鬼鱼雷(SS鱼雷+2)</t>
   </si>
   <si>
+    <t>Collection_F_BB_Fire</t>
+  </si>
+  <si>
     <t>骑兵之剑(F国BB火力+2)</t>
   </si>
   <si>
+    <t>Collection_S_Evasion</t>
+  </si>
+  <si>
     <t>战斗雪橇(S国回避+2)</t>
   </si>
   <si>
+    <t>Collection_C_Accuracy</t>
+  </si>
+  <si>
     <t>无人机(C国命中+3)</t>
   </si>
   <si>
+    <t>Collection_J_DD_Accuracy</t>
+  </si>
+  <si>
     <t>探照灯(J国DD命中+3)</t>
   </si>
   <si>
+    <t>Collection_J_Luck</t>
+  </si>
+  <si>
     <t>神秘炮塔(J国幸运+2)</t>
   </si>
   <si>
+    <t>Collection_U_CL_Evasion</t>
+  </si>
+  <si>
     <t>飞天胡萝卜(U国CL回避+2)</t>
   </si>
   <si>
+    <t>Collection_BB_Fire_1</t>
+  </si>
+  <si>
     <t>神奇的萝卜(BB火力+1)</t>
   </si>
   <si>
+    <t>Collection_U_CVL_Accuracy</t>
+  </si>
+  <si>
     <t>最初的甲板(U国CVL命中+2)</t>
   </si>
   <si>
+    <t>Collection_U_BB_Evasion</t>
+  </si>
+  <si>
     <t>防空机炮(U国BB闪避+2)</t>
   </si>
   <si>
+    <t>Collection_G_CA_Fire</t>
+  </si>
+  <si>
     <t>岸防炮(G国CA火力+2)</t>
   </si>
   <si>
+    <t>Collection_G_Accuracy</t>
+  </si>
+  <si>
     <t>制导武器(G国命中+2)</t>
   </si>
   <si>
+    <t>Collection_BB_Accuracy</t>
+  </si>
+  <si>
     <t>rc虎王(BB命中+2)</t>
   </si>
   <si>
+    <t>Collection_BC_Armor</t>
+  </si>
+  <si>
     <t>战舰“虎”(BC装甲+2)</t>
   </si>
   <si>
+    <t>Collection_G_CV_Fire</t>
+  </si>
+  <si>
     <t>天空惊雷(G国CV火力+5)</t>
   </si>
   <si>
+    <t>Collection_C_Fire_1</t>
+  </si>
+  <si>
     <t>003(C国火力+5)</t>
   </si>
   <si>
+    <t>Collection_I_Fire</t>
+  </si>
+  <si>
     <t>飞行圆桶(I国火力+3)</t>
   </si>
   <si>
+    <t>Collection_Luck_1</t>
+  </si>
+  <si>
     <t>桌面战记—决战无畏之海(所有船幸运+1)</t>
   </si>
   <si>
+    <t>Collection_SS_Torpedo_1</t>
+  </si>
+  <si>
     <t>霍兰潜艇(SS鱼雷+3)</t>
   </si>
   <si>
+    <t>Collection_S_Armor</t>
+  </si>
+  <si>
     <t>炊事拖车(S国装甲+2)</t>
   </si>
   <si>
+    <t>Collection_CV_Evasion</t>
+  </si>
+  <si>
     <t>智能地狱猫(CV回避+3)</t>
   </si>
   <si>
+    <t>Collection_DD_Torpedo</t>
+  </si>
+  <si>
     <t>水中杀手(DD鱼雷+3)</t>
   </si>
   <si>
+    <t>Collection_G_BC_Armor</t>
+  </si>
+  <si>
     <t>陆地巡洋舰(G国BC装甲+5)</t>
   </si>
   <si>
+    <t>Collection_E_Antiair_1</t>
+  </si>
+  <si>
     <t>弹道导弹(E国对空+10)</t>
   </si>
   <si>
+    <t>Collection_S_Antiair</t>
+  </si>
+  <si>
     <t>尼恩发动机(S国对空+10)</t>
   </si>
   <si>
+    <t>Collection_C_Torpedo</t>
+  </si>
+  <si>
     <t>鱼雷快艇(C国鱼雷+5)</t>
   </si>
   <si>
+    <t>Collection_G_Antiair</t>
+  </si>
+  <si>
     <t>新动力(G国对空+10)</t>
   </si>
   <si>
+    <t>Collection_C_Antiair</t>
+  </si>
+  <si>
     <t>长空利剑(C国对空+10)</t>
   </si>
   <si>
+    <t>Collection_C_Torpedo_1</t>
+  </si>
+  <si>
     <t>cbm鱼雷艇(C国鱼雷+3)</t>
   </si>
   <si>
+    <t>Collection_G_CV_Fire_1</t>
+  </si>
+  <si>
     <t>利爪(G国CV火力+5)</t>
   </si>
   <si>
+    <t>Collection_BB_Fire_2</t>
+  </si>
+  <si>
     <t>无畏舰主炮(BB火力+3)</t>
   </si>
   <si>
+    <t>Collection_U_SS_Recon</t>
+  </si>
+  <si>
     <t>北极星(U国SS索敌+2)</t>
   </si>
   <si>
+    <t>Collection_E_Armor</t>
+  </si>
+  <si>
     <t>水柜(E国装甲+5)</t>
   </si>
   <si>
+    <t>Collection_S_DD_Torpedo</t>
+  </si>
+  <si>
     <t>滑行鱼雷艇(S国DD鱼雷+5)</t>
   </si>
   <si>
+    <t>Collection_S_Armor_1</t>
+  </si>
+  <si>
     <t>T-34/85(S国装甲+5)</t>
   </si>
   <si>
+    <t>Collection_C_Luck_1</t>
+  </si>
+  <si>
     <t>胜利仪式(C国幸运+9)</t>
   </si>
   <si>
+    <t>Collection_C_Fire_2</t>
+  </si>
+  <si>
     <t>鹰击(C国火力+5)</t>
   </si>
   <si>
+    <t>Collection_C_Antiair_1</t>
+  </si>
+  <si>
     <t>雄鹰展翅(C国对空+10)</t>
   </si>
   <si>
+    <t>Collection_C_Luck_2</t>
+  </si>
+  <si>
     <t>翱翔天际(C国幸运+6)</t>
   </si>
   <si>
+    <t>Collection_S_Armor_2</t>
+  </si>
+  <si>
     <t>铁甲飞碟(S国装甲+5)</t>
   </si>
   <si>
+    <t>Collection_C_Small_Fire</t>
+  </si>
+  <si>
+    <t>某新型主炮(C国小型船火力+8)</t>
+  </si>
+  <si>
+    <t>Car_SmallShip_Torpedo</t>
+  </si>
+  <si>
     <t>小型船鱼雷+5</t>
   </si>
   <si>
+    <t>Car_Speed</t>
+  </si>
+  <si>
     <t>所有船航速+1</t>
   </si>
   <si>
+    <t>Car_LargeShip_Fire</t>
+  </si>
+  <si>
     <t>大型船火力+5</t>
   </si>
   <si>
+    <t>Car_Luck</t>
+  </si>
+  <si>
     <t>所有船幸运+5</t>
   </si>
   <si>
+    <t>Car_Antiair</t>
+  </si>
+  <si>
     <t>所有船对空+5</t>
   </si>
   <si>
+    <t>Car_LargeShip_Armor</t>
+  </si>
+  <si>
     <t>大型船装甲+7</t>
   </si>
   <si>
+    <t>Car_Evasion</t>
+  </si>
+  <si>
     <t>所有船回避+5</t>
   </si>
   <si>
+    <t>Car_Accuracy</t>
+  </si>
+  <si>
     <t>所有船命中+5</t>
-  </si>
-  <si>
-    <t>Collection_E_BB_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_J_DD_Fire</t>
-  </si>
-  <si>
-    <t>Collection_C_Luck</t>
-  </si>
-  <si>
-    <t>Collection_E_DD_Fire</t>
-  </si>
-  <si>
-    <t>Collection_U_DD_Recon</t>
-  </si>
-  <si>
-    <t>Collection_I_DD_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_U_CL_Recon</t>
-  </si>
-  <si>
-    <t>Collection_S_Fire</t>
-  </si>
-  <si>
-    <t>Collection_J_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_BB_Fire</t>
-  </si>
-  <si>
-    <t>Collection_U_CA_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_E_BC_Fire</t>
-  </si>
-  <si>
-    <t>Collection_J_DD_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_C_Fire</t>
-  </si>
-  <si>
-    <t>Collection_I_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_Luck</t>
-  </si>
-  <si>
-    <t>Collection_G_BC_Fire</t>
-  </si>
-  <si>
-    <t>Collection_U_CV_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_BB_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_E_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_BC_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_BB_Armor</t>
-  </si>
-  <si>
-    <t>Collection_U_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_J_BB_Fire</t>
-  </si>
-  <si>
-    <t>Collection_S_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_S_CL_Fire</t>
-  </si>
-  <si>
-    <t>Collection_G_BB_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_G_BB_Fire</t>
-  </si>
-  <si>
-    <t>Collection_U_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_SS_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_F_BB_Fire</t>
-  </si>
-  <si>
-    <t>Collection_S_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_C_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_J_DD_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_J_Luck</t>
-  </si>
-  <si>
-    <t>Collection_U_CL_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_BB_Fire_1</t>
-  </si>
-  <si>
-    <t>Collection_U_CVL_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_U_BB_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_G_CA_Fire</t>
-  </si>
-  <si>
-    <t>Collection_G_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_BB_Accuracy</t>
-  </si>
-  <si>
-    <t>Collection_BC_Armor</t>
-  </si>
-  <si>
-    <t>Collection_G_CV_Fire</t>
-  </si>
-  <si>
-    <t>Collection_C_Fire_1</t>
-  </si>
-  <si>
-    <t>Collection_I_Fire</t>
-  </si>
-  <si>
-    <t>Collection_Luck_1</t>
-  </si>
-  <si>
-    <t>Collection_SS_Torpedo_1</t>
-  </si>
-  <si>
-    <t>Collection_S_Armor</t>
-  </si>
-  <si>
-    <t>Collection_CV_Evasion</t>
-  </si>
-  <si>
-    <t>Collection_DD_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_G_BC_Armor</t>
-  </si>
-  <si>
-    <t>Collection_E_Antiair_1</t>
-  </si>
-  <si>
-    <t>Collection_S_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_C_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_G_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_C_Antiair</t>
-  </si>
-  <si>
-    <t>Collection_C_Torpedo_1</t>
-  </si>
-  <si>
-    <t>Collection_G_CV_Fire_1</t>
-  </si>
-  <si>
-    <t>Collection_BB_Fire_2</t>
-  </si>
-  <si>
-    <t>Collection_U_SS_Recon</t>
-  </si>
-  <si>
-    <t>Collection_E_Armor</t>
-  </si>
-  <si>
-    <t>Collection_S_DD_Torpedo</t>
-  </si>
-  <si>
-    <t>Collection_S_Armor_1</t>
-  </si>
-  <si>
-    <t>Collection_C_Luck_1</t>
-  </si>
-  <si>
-    <t>Collection_C_Fire_2</t>
-  </si>
-  <si>
-    <t>Collection_C_Antiair_1</t>
-  </si>
-  <si>
-    <t>Collection_C_Luck_2</t>
-  </si>
-  <si>
-    <t>Collection_S_Armor_2</t>
-  </si>
-  <si>
-    <t>Car_SmallShip_Torpedo</t>
-  </si>
-  <si>
-    <t>Car_Speed</t>
-  </si>
-  <si>
-    <t>Car_LargeShip_Fire</t>
-  </si>
-  <si>
-    <t>Car_Luck</t>
-  </si>
-  <si>
-    <t>Car_Antiair</t>
-  </si>
-  <si>
-    <t>Car_LargeShip_Armor</t>
-  </si>
-  <si>
-    <t>Car_Evasion</t>
-  </si>
-  <si>
-    <t>Car_Accuracy</t>
-  </si>
-  <si>
-    <t>鱼雷海</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>圣地亚哥专属</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Cid(157)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Event_SanDiego</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllPhase:2.18</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Supply_Damage</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>公正的决斗</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>AllPhase:0.3</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>Collection_C_Small_Fire</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>C</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>SmallShip</t>
-    <phoneticPr fontId="2" type="noConversion"/>
-  </si>
-  <si>
-    <t>某新型主炮(C国小型船火力+8)</t>
-    <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
+  </numFmts>
+  <fonts count="22">
     <font>
       <sz val="11"/>
       <color theme="1"/>
       <name val="等线"/>
+      <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-    </font>
-    <font>
-      <sz val="9"/>
-      <name val="宋体"/>
-      <family val="3"/>
       <charset val="134"/>
     </font>
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
       <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF0000FF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C0006"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
     </font>
   </fonts>
-  <fills count="2">
+  <fills count="33">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
     </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
   </fills>
-  <borders count="1">
+  <borders count="9">
     <border>
       <left/>
       <right/>
@@ -1236,41 +1581,327 @@
       <bottom/>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="double">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="double">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="double">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="double">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
-  <cellStyleXfs count="1">
+  <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
   </cellStyleXfs>
   <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment horizontal="fill" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
   </cellXfs>
-  <cellStyles count="1">
+  <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
+    <cellStyle name="60% - 强调文字颜色 6" xfId="1" builtinId="52"/>
+    <cellStyle name="20% - 强调文字颜色 4" xfId="2" builtinId="42"/>
+    <cellStyle name="强调文字颜色 4" xfId="3" builtinId="41"/>
+    <cellStyle name="输入" xfId="4" builtinId="20"/>
+    <cellStyle name="40% - 强调文字颜色 3" xfId="5" builtinId="39"/>
+    <cellStyle name="20% - 强调文字颜色 3" xfId="6" builtinId="38"/>
+    <cellStyle name="货币" xfId="7" builtinId="4"/>
+    <cellStyle name="强调文字颜色 3" xfId="8" builtinId="37"/>
+    <cellStyle name="百分比" xfId="9" builtinId="5"/>
+    <cellStyle name="60% - 强调文字颜色 2" xfId="10" builtinId="36"/>
+    <cellStyle name="60% - 强调文字颜色 5" xfId="11" builtinId="48"/>
+    <cellStyle name="强调文字颜色 2" xfId="12" builtinId="33"/>
+    <cellStyle name="60% - 强调文字颜色 1" xfId="13" builtinId="32"/>
+    <cellStyle name="60% - 强调文字颜色 4" xfId="14" builtinId="44"/>
+    <cellStyle name="计算" xfId="15" builtinId="22"/>
+    <cellStyle name="强调文字颜色 1" xfId="16" builtinId="29"/>
+    <cellStyle name="适中" xfId="17" builtinId="28"/>
+    <cellStyle name="20% - 强调文字颜色 5" xfId="18" builtinId="46"/>
+    <cellStyle name="好" xfId="19" builtinId="26"/>
+    <cellStyle name="20% - 强调文字颜色 1" xfId="20" builtinId="30"/>
+    <cellStyle name="汇总" xfId="21" builtinId="25"/>
+    <cellStyle name="差" xfId="22" builtinId="27"/>
+    <cellStyle name="检查单元格" xfId="23" builtinId="23"/>
+    <cellStyle name="输出" xfId="24" builtinId="21"/>
+    <cellStyle name="标题 1" xfId="25" builtinId="16"/>
+    <cellStyle name="解释性文本" xfId="26" builtinId="53"/>
+    <cellStyle name="20% - 强调文字颜色 2" xfId="27" builtinId="34"/>
+    <cellStyle name="标题 4" xfId="28" builtinId="19"/>
+    <cellStyle name="货币[0]" xfId="29" builtinId="7"/>
+    <cellStyle name="40% - 强调文字颜色 4" xfId="30" builtinId="43"/>
+    <cellStyle name="千位分隔" xfId="31" builtinId="3"/>
+    <cellStyle name="已访问的超链接" xfId="32" builtinId="9"/>
+    <cellStyle name="标题" xfId="33" builtinId="15"/>
+    <cellStyle name="40% - 强调文字颜色 2" xfId="34" builtinId="35"/>
+    <cellStyle name="警告文本" xfId="35" builtinId="11"/>
+    <cellStyle name="60% - 强调文字颜色 3" xfId="36" builtinId="40"/>
+    <cellStyle name="注释" xfId="37" builtinId="10"/>
+    <cellStyle name="20% - 强调文字颜色 6" xfId="38" builtinId="50"/>
+    <cellStyle name="强调文字颜色 5" xfId="39" builtinId="45"/>
+    <cellStyle name="40% - 强调文字颜色 6" xfId="40" builtinId="51"/>
+    <cellStyle name="超链接" xfId="41" builtinId="8"/>
+    <cellStyle name="千位分隔[0]" xfId="42" builtinId="6"/>
+    <cellStyle name="标题 2" xfId="43" builtinId="17"/>
+    <cellStyle name="40% - 强调文字颜色 5" xfId="44" builtinId="47"/>
+    <cellStyle name="标题 3" xfId="45" builtinId="18"/>
+    <cellStyle name="强调文字颜色 6" xfId="46" builtinId="49"/>
+    <cellStyle name="40% - 强调文字颜色 1" xfId="47" builtinId="31"/>
+    <cellStyle name="链接单元格" xfId="48" builtinId="24"/>
   </cellStyles>
-  <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
   <extLst>
     <ext xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" uri="{EB79DEF2-80B8-43e5-95BD-54CBDDF9020C}">
       <x14:slicerStyles defaultSlicerStyle="SlicerStyleLight1"/>
-    </ext>
-    <ext xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" uri="{9260A510-F301-46a8-8635-F512D64BE5F5}">
-      <x15:timelineStyles defaultTimelineStyle="TimeSlicerStyleLight1"/>
     </ext>
   </extLst>
 </styleSheet>
@@ -1465,20 +2096,20 @@
     </a:fmtScheme>
   </a:themeElements>
   <a:objectDefaults/>
-  <a:extraClrSchemeLst/>
 </a:theme>
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V23"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="10.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="10.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
     <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1513,7 +2144,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -1537,27 +2168,27 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>22</v>
       </c>
       <c r="C2" t="s">
         <v>23</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="1" t="s">
         <v>24</v>
       </c>
       <c r="E2">
@@ -1578,18 +2209,18 @@
       <c r="O2">
         <v>5</v>
       </c>
-      <c r="Q2" s="3" t="s">
+      <c r="Q2" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:18">
       <c r="A3" t="s">
         <v>26</v>
       </c>
       <c r="C3" t="s">
         <v>27</v>
       </c>
-      <c r="D3" s="2" t="s">
+      <c r="D3" s="1" t="s">
         <v>28</v>
       </c>
       <c r="E3">
@@ -1607,21 +2238,21 @@
       <c r="P3">
         <v>0.03</v>
       </c>
-      <c r="Q3" s="3" t="s">
+      <c r="Q3" s="2" t="s">
         <v>29</v>
       </c>
       <c r="R3" t="s">
         <v>30</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>31</v>
       </c>
       <c r="C4" t="s">
         <v>32</v>
       </c>
-      <c r="D4" s="2" t="s">
+      <c r="D4" s="1" t="s">
         <v>33</v>
       </c>
       <c r="E4">
@@ -1639,18 +2270,18 @@
       <c r="O4">
         <v>5</v>
       </c>
-      <c r="Q4" s="3" t="s">
+      <c r="Q4" s="2" t="s">
         <v>34</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
+    <row r="5" spans="1:18">
       <c r="A5" t="s">
         <v>35</v>
       </c>
       <c r="C5" t="s">
         <v>36</v>
       </c>
-      <c r="D5" s="2" t="s">
+      <c r="D5" s="1" t="s">
         <v>37</v>
       </c>
       <c r="E5">
@@ -1671,21 +2302,21 @@
       <c r="P5">
         <v>0.03</v>
       </c>
-      <c r="Q5" s="3" t="s">
+      <c r="Q5" s="2" t="s">
         <v>38</v>
       </c>
       <c r="R5" t="s">
         <v>39</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
         <v>40</v>
       </c>
       <c r="C6" t="s">
         <v>41</v>
       </c>
-      <c r="D6" s="2" t="s">
+      <c r="D6" s="1" t="s">
         <v>42</v>
       </c>
       <c r="E6">
@@ -1706,18 +2337,18 @@
       <c r="P6">
         <v>0.03</v>
       </c>
-      <c r="Q6" s="3" t="s">
+      <c r="Q6" s="2" t="s">
         <v>43</v>
       </c>
     </row>
-    <row r="7" spans="1:22">
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
         <v>44</v>
       </c>
       <c r="C7" t="s">
         <v>45</v>
       </c>
-      <c r="D7" s="2" t="s">
+      <c r="D7" s="1" t="s">
         <v>46</v>
       </c>
       <c r="E7">
@@ -1732,16 +2363,16 @@
       <c r="O7">
         <v>5</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
         <v>47</v>
       </c>
       <c r="C8" t="s">
         <v>48</v>
       </c>
-      <c r="D8" s="2" t="s">
+      <c r="D8" s="1" t="s">
         <v>49</v>
       </c>
       <c r="E8">
@@ -1762,18 +2393,18 @@
       <c r="P8">
         <v>0.03</v>
       </c>
-      <c r="Q8" s="3" t="s">
+      <c r="Q8" s="2" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:18">
       <c r="A9" t="s">
         <v>51</v>
       </c>
       <c r="C9" t="s">
         <v>52</v>
       </c>
-      <c r="D9" s="2" t="s">
+      <c r="D9" s="1" t="s">
         <v>53</v>
       </c>
       <c r="E9">
@@ -1800,21 +2431,21 @@
       <c r="P9">
         <v>0.05</v>
       </c>
-      <c r="Q9" s="3" t="s">
+      <c r="Q9" s="2" t="s">
         <v>54</v>
       </c>
       <c r="R9" t="s">
         <v>55</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
         <v>56</v>
       </c>
       <c r="C10" t="s">
         <v>57</v>
       </c>
-      <c r="D10" s="2" t="s">
+      <c r="D10" s="1" t="s">
         <v>58</v>
       </c>
       <c r="E10">
@@ -1835,18 +2466,18 @@
       <c r="O10">
         <v>5</v>
       </c>
-      <c r="Q10" s="3" t="s">
+      <c r="Q10" s="2" t="s">
         <v>59</v>
       </c>
     </row>
-    <row r="11" spans="1:22">
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
         <v>60</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="2" t="s">
+      <c r="D11" s="1" t="s">
         <v>62</v>
       </c>
       <c r="E11">
@@ -1876,45 +2507,45 @@
       <c r="O11">
         <v>5</v>
       </c>
-      <c r="Q11" s="3" t="s">
+      <c r="Q11" s="2" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="12" spans="1:22" s="2" customFormat="1">
+    <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" t="s">
         <v>63</v>
       </c>
-      <c r="C12" s="2" t="s">
+      <c r="C12" s="1" t="s">
         <v>64</v>
       </c>
-      <c r="D12" s="2" t="s">
+      <c r="D12" s="1" t="s">
         <v>65</v>
       </c>
       <c r="E12">
         <v>1</v>
       </c>
-      <c r="F12" s="2">
-        <v>5</v>
-      </c>
-      <c r="G12" s="2">
-        <v>5</v>
-      </c>
-      <c r="I12" s="2">
-        <v>5</v>
-      </c>
-      <c r="K12" s="2">
-        <v>5</v>
-      </c>
-      <c r="M12" s="2">
+      <c r="F12" s="1">
+        <v>5</v>
+      </c>
+      <c r="G12" s="1">
+        <v>5</v>
+      </c>
+      <c r="I12" s="1">
+        <v>5</v>
+      </c>
+      <c r="K12" s="1">
+        <v>5</v>
+      </c>
+      <c r="M12" s="1">
         <v>3</v>
       </c>
-      <c r="P12" s="2">
+      <c r="P12" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q12" s="3" t="s">
+      <c r="Q12" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="R12" s="2" t="s">
+      <c r="R12" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S12"/>
@@ -1922,35 +2553,35 @@
       <c r="U12"/>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1">
+    <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" t="s">
         <v>67</v>
       </c>
-      <c r="C13" s="2" t="s">
+      <c r="C13" s="1" t="s">
         <v>68</v>
       </c>
-      <c r="D13" s="2" t="s">
+      <c r="D13" s="1" t="s">
         <v>69</v>
       </c>
       <c r="E13">
         <v>1</v>
       </c>
-      <c r="G13" s="2">
-        <v>5</v>
-      </c>
-      <c r="K13" s="2">
-        <v>5</v>
-      </c>
-      <c r="L13" s="2">
-        <v>5</v>
-      </c>
-      <c r="O13" s="2">
-        <v>5</v>
-      </c>
-      <c r="P13" s="2">
+      <c r="G13" s="1">
+        <v>5</v>
+      </c>
+      <c r="K13" s="1">
+        <v>5</v>
+      </c>
+      <c r="L13" s="1">
+        <v>5</v>
+      </c>
+      <c r="O13" s="1">
+        <v>5</v>
+      </c>
+      <c r="P13" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q13" s="3" t="s">
+      <c r="Q13" s="2" t="s">
         <v>70</v>
       </c>
       <c r="S13"/>
@@ -1958,75 +2589,75 @@
       <c r="U13"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1">
+    <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" t="s">
         <v>71</v>
       </c>
-      <c r="C14" s="2" t="s">
+      <c r="C14" s="1" t="s">
         <v>72</v>
       </c>
-      <c r="D14" s="2" t="s">
+      <c r="D14" s="1" t="s">
         <v>73</v>
       </c>
       <c r="E14">
         <v>1</v>
       </c>
-      <c r="I14" s="2">
-        <v>5</v>
-      </c>
-      <c r="J14" s="2">
-        <v>5</v>
-      </c>
-      <c r="K14" s="2">
-        <v>5</v>
-      </c>
-      <c r="L14" s="2">
-        <v>5</v>
-      </c>
-      <c r="M14" s="2">
+      <c r="I14" s="1">
+        <v>5</v>
+      </c>
+      <c r="J14" s="1">
+        <v>5</v>
+      </c>
+      <c r="K14" s="1">
+        <v>5</v>
+      </c>
+      <c r="L14" s="1">
+        <v>5</v>
+      </c>
+      <c r="M14" s="1">
         <v>3</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="5"/>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1">
+    <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" t="s">
         <v>74</v>
       </c>
-      <c r="C15" s="2" t="s">
+      <c r="C15" s="1" t="s">
         <v>75</v>
       </c>
-      <c r="D15" s="2" t="s">
+      <c r="D15" s="1" t="s">
         <v>76</v>
       </c>
       <c r="E15">
         <v>1</v>
       </c>
-      <c r="F15" s="2">
-        <v>5</v>
-      </c>
-      <c r="I15" s="2">
-        <v>5</v>
-      </c>
-      <c r="K15" s="2">
-        <v>5</v>
-      </c>
-      <c r="L15" s="2">
-        <v>5</v>
-      </c>
-      <c r="M15" s="2">
+      <c r="F15" s="1">
+        <v>5</v>
+      </c>
+      <c r="I15" s="1">
+        <v>5</v>
+      </c>
+      <c r="K15" s="1">
+        <v>5</v>
+      </c>
+      <c r="L15" s="1">
+        <v>5</v>
+      </c>
+      <c r="M15" s="1">
         <v>3</v>
       </c>
-      <c r="O15" s="2">
-        <v>5</v>
-      </c>
-      <c r="P15" s="2">
+      <c r="O15" s="1">
+        <v>5</v>
+      </c>
+      <c r="P15" s="1">
         <v>0.05</v>
       </c>
-      <c r="Q15" s="4" t="s">
+      <c r="Q15" s="5" t="s">
         <v>77</v>
       </c>
       <c r="S15"/>
@@ -2034,38 +2665,38 @@
       <c r="U15"/>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1">
+    <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" t="s">
         <v>78</v>
       </c>
-      <c r="C16" s="2" t="s">
+      <c r="C16" s="1" t="s">
         <v>79</v>
       </c>
-      <c r="D16" s="2" t="s">
+      <c r="D16" s="1" t="s">
         <v>80</v>
       </c>
       <c r="E16">
         <v>1</v>
       </c>
-      <c r="F16" s="2">
-        <v>5</v>
-      </c>
-      <c r="H16" s="2">
-        <v>5</v>
-      </c>
-      <c r="K16" s="2">
-        <v>5</v>
-      </c>
-      <c r="L16" s="2">
+      <c r="F16" s="1">
+        <v>5</v>
+      </c>
+      <c r="H16" s="1">
+        <v>5</v>
+      </c>
+      <c r="K16" s="1">
+        <v>5</v>
+      </c>
+      <c r="L16" s="1">
         <v>10</v>
       </c>
-      <c r="M16" s="2">
-        <v>5</v>
-      </c>
-      <c r="P16" s="2">
+      <c r="M16" s="1">
+        <v>5</v>
+      </c>
+      <c r="P16" s="1">
         <v>0.05</v>
       </c>
-      <c r="Q16" s="4" t="s">
+      <c r="Q16" s="5" t="s">
         <v>81</v>
       </c>
       <c r="S16"/>
@@ -2073,36 +2704,36 @@
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1">
+    <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" t="s">
         <v>82</v>
       </c>
-      <c r="C17" s="2" t="s">
+      <c r="C17" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D17" s="2" t="s">
+      <c r="D17" s="1" t="s">
         <v>84</v>
       </c>
       <c r="E17">
         <v>1</v>
       </c>
-      <c r="F17" s="2">
-        <v>5</v>
-      </c>
-      <c r="H17" s="2">
-        <v>5</v>
-      </c>
-      <c r="K17" s="2">
-        <v>5</v>
-      </c>
-      <c r="L17" s="2">
-        <v>5</v>
-      </c>
-      <c r="P17" s="2">
+      <c r="F17" s="1">
+        <v>5</v>
+      </c>
+      <c r="H17" s="1">
+        <v>5</v>
+      </c>
+      <c r="K17" s="1">
+        <v>5</v>
+      </c>
+      <c r="L17" s="1">
+        <v>5</v>
+      </c>
+      <c r="P17" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q17" s="4"/>
-      <c r="R17" s="2" t="s">
+      <c r="Q17" s="5"/>
+      <c r="R17" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S17"/>
@@ -2110,35 +2741,35 @@
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1">
+    <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" t="s">
         <v>85</v>
       </c>
-      <c r="C18" s="2" t="s">
+      <c r="C18" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D18" s="2" t="s">
+      <c r="D18" s="1" t="s">
         <v>87</v>
       </c>
       <c r="E18">
         <v>1</v>
       </c>
-      <c r="I18" s="2">
-        <v>5</v>
-      </c>
-      <c r="K18" s="2">
-        <v>5</v>
-      </c>
-      <c r="L18" s="2">
-        <v>5</v>
-      </c>
-      <c r="P18" s="2">
+      <c r="I18" s="1">
+        <v>5</v>
+      </c>
+      <c r="K18" s="1">
+        <v>5</v>
+      </c>
+      <c r="L18" s="1">
+        <v>5</v>
+      </c>
+      <c r="P18" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q18" s="4" t="s">
+      <c r="Q18" s="5" t="s">
         <v>88</v>
       </c>
-      <c r="R18" s="2" t="s">
+      <c r="R18" s="1" t="s">
         <v>89</v>
       </c>
       <c r="S18"/>
@@ -2146,35 +2777,35 @@
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1">
+    <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" t="s">
         <v>90</v>
       </c>
-      <c r="C19" s="2" t="s">
+      <c r="C19" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D19" s="2" t="s">
+      <c r="D19" s="1" t="s">
         <v>92</v>
       </c>
       <c r="E19">
         <v>1</v>
       </c>
-      <c r="F19" s="2">
-        <v>5</v>
-      </c>
-      <c r="I19" s="2">
-        <v>5</v>
-      </c>
-      <c r="K19" s="2">
-        <v>5</v>
-      </c>
-      <c r="L19" s="2">
-        <v>5</v>
-      </c>
-      <c r="P19" s="2">
+      <c r="F19" s="1">
+        <v>5</v>
+      </c>
+      <c r="I19" s="1">
+        <v>5</v>
+      </c>
+      <c r="K19" s="1">
+        <v>5</v>
+      </c>
+      <c r="L19" s="1">
+        <v>5</v>
+      </c>
+      <c r="P19" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q19" s="4" t="s">
+      <c r="Q19" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S19"/>
@@ -2182,41 +2813,41 @@
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1">
+    <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" t="s">
         <v>93</v>
       </c>
-      <c r="C20" s="2" t="s">
+      <c r="C20" s="1" t="s">
         <v>94</v>
       </c>
-      <c r="D20" s="2" t="s">
+      <c r="D20" s="1" t="s">
         <v>95</v>
       </c>
       <c r="E20">
         <v>1</v>
       </c>
-      <c r="F20" s="2">
-        <v>5</v>
-      </c>
-      <c r="H20" s="2">
-        <v>5</v>
-      </c>
-      <c r="I20" s="2">
-        <v>5</v>
-      </c>
-      <c r="K20" s="2">
-        <v>5</v>
-      </c>
-      <c r="L20" s="2">
-        <v>5</v>
-      </c>
-      <c r="M20" s="2">
+      <c r="F20" s="1">
+        <v>5</v>
+      </c>
+      <c r="H20" s="1">
+        <v>5</v>
+      </c>
+      <c r="I20" s="1">
+        <v>5</v>
+      </c>
+      <c r="K20" s="1">
+        <v>5</v>
+      </c>
+      <c r="L20" s="1">
+        <v>5</v>
+      </c>
+      <c r="M20" s="1">
         <v>3</v>
       </c>
-      <c r="P20" s="2">
+      <c r="P20" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q20" s="4" t="s">
+      <c r="Q20" s="5" t="s">
         <v>88</v>
       </c>
       <c r="S20"/>
@@ -2224,38 +2855,38 @@
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1">
+    <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" t="s">
         <v>96</v>
       </c>
-      <c r="C21" s="2" t="s">
+      <c r="C21" s="1" t="s">
         <v>97</v>
       </c>
-      <c r="D21" s="2" t="s">
+      <c r="D21" s="1" t="s">
         <v>98</v>
       </c>
       <c r="E21">
         <v>1</v>
       </c>
-      <c r="F21" s="2">
-        <v>5</v>
-      </c>
-      <c r="H21" s="2">
-        <v>5</v>
-      </c>
-      <c r="I21" s="2">
-        <v>5</v>
-      </c>
-      <c r="K21" s="2">
-        <v>5</v>
-      </c>
-      <c r="L21" s="2">
-        <v>5</v>
-      </c>
-      <c r="P21" s="2">
+      <c r="F21" s="1">
+        <v>5</v>
+      </c>
+      <c r="H21" s="1">
+        <v>5</v>
+      </c>
+      <c r="I21" s="1">
+        <v>5</v>
+      </c>
+      <c r="K21" s="1">
+        <v>5</v>
+      </c>
+      <c r="L21" s="1">
+        <v>5</v>
+      </c>
+      <c r="P21" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q21" s="4" t="s">
+      <c r="Q21" s="5" t="s">
         <v>50</v>
       </c>
       <c r="S21"/>
@@ -2263,41 +2894,41 @@
       <c r="U21"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1">
+    <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" t="s">
         <v>99</v>
       </c>
-      <c r="C22" s="2" t="s">
+      <c r="C22" s="1" t="s">
         <v>100</v>
       </c>
-      <c r="D22" s="2" t="s">
+      <c r="D22" s="1" t="s">
         <v>101</v>
       </c>
       <c r="E22">
         <v>1</v>
       </c>
-      <c r="F22" s="2">
-        <v>5</v>
-      </c>
-      <c r="I22" s="2">
-        <v>5</v>
-      </c>
-      <c r="K22" s="2">
-        <v>5</v>
-      </c>
-      <c r="L22" s="2">
-        <v>5</v>
-      </c>
-      <c r="M22" s="2">
+      <c r="F22" s="1">
+        <v>5</v>
+      </c>
+      <c r="I22" s="1">
+        <v>5</v>
+      </c>
+      <c r="K22" s="1">
+        <v>5</v>
+      </c>
+      <c r="L22" s="1">
+        <v>5</v>
+      </c>
+      <c r="M22" s="1">
         <v>3</v>
       </c>
-      <c r="P22" s="2">
+      <c r="P22" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q22" s="4" t="s">
+      <c r="Q22" s="5" t="s">
         <v>29</v>
       </c>
-      <c r="R22" s="2" t="s">
+      <c r="R22" s="1" t="s">
         <v>30</v>
       </c>
       <c r="S22"/>
@@ -2305,41 +2936,41 @@
       <c r="U22"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1">
+    <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" t="s">
         <v>102</v>
       </c>
-      <c r="C23" s="2" t="s">
+      <c r="C23" s="1" t="s">
         <v>103</v>
       </c>
-      <c r="D23" s="2" t="s">
+      <c r="D23" s="1" t="s">
         <v>104</v>
       </c>
       <c r="E23">
         <v>1</v>
       </c>
-      <c r="F23" s="2">
-        <v>5</v>
-      </c>
-      <c r="H23" s="2">
-        <v>5</v>
-      </c>
-      <c r="K23" s="2">
-        <v>5</v>
-      </c>
-      <c r="L23" s="2">
-        <v>5</v>
-      </c>
-      <c r="M23" s="2">
+      <c r="F23" s="1">
+        <v>5</v>
+      </c>
+      <c r="H23" s="1">
+        <v>5</v>
+      </c>
+      <c r="K23" s="1">
+        <v>5</v>
+      </c>
+      <c r="L23" s="1">
+        <v>5</v>
+      </c>
+      <c r="M23" s="1">
         <v>3</v>
       </c>
-      <c r="P23" s="2">
+      <c r="P23" s="1">
         <v>0.03</v>
       </c>
-      <c r="Q23" s="4" t="s">
+      <c r="Q23" s="5" t="s">
         <v>34</v>
       </c>
-      <c r="R23" s="2" t="s">
+      <c r="R23" s="1" t="s">
         <v>89</v>
       </c>
       <c r="S23"/>
@@ -2348,20 +2979,21 @@
       <c r="V23"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
-  <dimension ref="A1:V8"/>
-  <sheetFormatPr baseColWidth="10" defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
+  <dimension ref="A1:V15"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
-    <col min="4" max="4" width="12.33203125" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
+    <col min="4" max="4" width="12.3333333333333" customWidth="1"/>
+    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:22">
@@ -2395,7 +3027,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -2419,20 +3051,20 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
         <v>105</v>
       </c>
@@ -2452,7 +3084,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="3" spans="1:22">
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
         <v>109</v>
       </c>
@@ -2472,7 +3104,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="4" spans="1:22">
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -2492,54 +3124,54 @@
         <v>108</v>
       </c>
     </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>379</v>
+    <row r="5" spans="1:17">
+      <c r="A5" s="7" t="s">
+        <v>115</v>
+      </c>
+      <c r="D5" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="Q5" s="7" t="s">
+        <v>108</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>117</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
-      <c r="D6" s="6" t="s">
-        <v>372</v>
+      <c r="D6" s="7" t="s">
+        <v>118</v>
       </c>
       <c r="V6" t="s">
-        <v>116</v>
-      </c>
-    </row>
-    <row r="7" spans="1:22">
+        <v>119</v>
+      </c>
+    </row>
+    <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>117</v>
+        <v>120</v>
       </c>
       <c r="B7" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S7" s="5" t="b">
+        <v>122</v>
+      </c>
+      <c r="S7" s="4" t="b">
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="C8" s="6" t="s">
-        <v>374</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>373</v>
+    <row r="8" spans="1:20">
+      <c r="A8" s="7" t="s">
+        <v>123</v>
+      </c>
+      <c r="C8" s="7" t="s">
+        <v>124</v>
+      </c>
+      <c r="D8" s="7" t="s">
+        <v>125</v>
       </c>
       <c r="F8">
         <v>53</v>
@@ -2559,8 +3191,8 @@
       <c r="P8">
         <v>0.53</v>
       </c>
-      <c r="Q8" s="6" t="s">
-        <v>376</v>
+      <c r="Q8" s="7" t="s">
+        <v>126</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -2569,22 +3201,139 @@
         <v>1</v>
       </c>
     </row>
+    <row r="9" spans="1:11">
+      <c r="A9" t="s">
+        <v>127</v>
+      </c>
+      <c r="D9" t="s">
+        <v>128</v>
+      </c>
+      <c r="F9">
+        <v>-10</v>
+      </c>
+      <c r="K9">
+        <v>-10</v>
+      </c>
+    </row>
+    <row r="10" spans="1:11">
+      <c r="A10" t="s">
+        <v>129</v>
+      </c>
+      <c r="C10" t="s">
+        <v>83</v>
+      </c>
+      <c r="D10" t="s">
+        <v>130</v>
+      </c>
+      <c r="F10">
+        <v>10</v>
+      </c>
+      <c r="K10">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="11" spans="1:11">
+      <c r="A11" t="s">
+        <v>131</v>
+      </c>
+      <c r="C11" t="s">
+        <v>94</v>
+      </c>
+      <c r="D11" t="s">
+        <v>132</v>
+      </c>
+      <c r="F11">
+        <v>10</v>
+      </c>
+      <c r="K11">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="12" spans="1:11">
+      <c r="A12" t="s">
+        <v>133</v>
+      </c>
+      <c r="C12" t="s">
+        <v>86</v>
+      </c>
+      <c r="D12" t="s">
+        <v>134</v>
+      </c>
+      <c r="F12">
+        <v>-20</v>
+      </c>
+      <c r="K12">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="13" spans="1:12">
+      <c r="A13" t="s">
+        <v>135</v>
+      </c>
+      <c r="C13" t="s">
+        <v>61</v>
+      </c>
+      <c r="D13" t="s">
+        <v>136</v>
+      </c>
+      <c r="H13">
+        <v>-10</v>
+      </c>
+      <c r="L13">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="14" spans="1:12">
+      <c r="A14" t="s">
+        <v>137</v>
+      </c>
+      <c r="C14" t="s">
+        <v>23</v>
+      </c>
+      <c r="D14" t="s">
+        <v>138</v>
+      </c>
+      <c r="H14">
+        <v>-10</v>
+      </c>
+      <c r="L14">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="15" spans="1:11">
+      <c r="A15" t="s">
+        <v>139</v>
+      </c>
+      <c r="C15" t="s">
+        <v>110</v>
+      </c>
+      <c r="D15" t="s">
+        <v>140</v>
+      </c>
+      <c r="F15">
+        <v>10</v>
+      </c>
+      <c r="K15">
+        <v>10</v>
+      </c>
+    </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="30.1640625" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="30.1666666666667" customWidth="1"/>
+    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
     <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -2619,7 +3368,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -2643,662 +3392,662 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
+    <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>120</v>
+        <v>141</v>
       </c>
       <c r="B2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
+        <v>142</v>
+      </c>
+      <c r="D2" s="1" t="s">
+        <v>143</v>
       </c>
       <c r="F2">
         <v>10</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:22">
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>123</v>
+        <v>144</v>
       </c>
       <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
+        <v>145</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>146</v>
       </c>
       <c r="F3">
         <v>7</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:22">
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>147</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>127</v>
+      <c r="D4" s="1" t="s">
+        <v>148</v>
       </c>
       <c r="K4">
         <v>5</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:22">
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>149</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>121</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>150</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
+    <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>130</v>
+        <v>151</v>
       </c>
       <c r="B6" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C6" t="s">
         <v>106</v>
       </c>
-      <c r="D6" s="2" t="s">
-        <v>132</v>
+      <c r="D6" s="1" t="s">
+        <v>153</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:22">
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>154</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>135</v>
+      <c r="D7" s="1" t="s">
+        <v>156</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:22">
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>157</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>155</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>158</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
+    <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>159</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
-      <c r="D9" s="2" t="s">
-        <v>140</v>
+      <c r="D9" s="1" t="s">
+        <v>161</v>
       </c>
       <c r="Q9" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:22">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>142</v>
+        <v>163</v>
       </c>
       <c r="B10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>144</v>
+        <v>164</v>
+      </c>
+      <c r="D10" s="1" t="s">
+        <v>165</v>
       </c>
       <c r="L10">
         <v>7</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:22">
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>166</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
-      <c r="D11" s="2" t="s">
-        <v>146</v>
+      <c r="D11" s="1" t="s">
+        <v>167</v>
       </c>
       <c r="F11">
         <v>7</v>
       </c>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1">
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" t="s">
-        <v>147</v>
-      </c>
-      <c r="B12" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C12" s="2" t="s">
+        <v>168</v>
+      </c>
+      <c r="B12" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C12" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D12" s="2" t="s">
-        <v>148</v>
+      <c r="D12" s="1" t="s">
+        <v>169</v>
       </c>
       <c r="E12"/>
-      <c r="F12" s="2">
+      <c r="F12" s="1">
         <v>10</v>
       </c>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="2"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1">
+    <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" t="s">
-        <v>149</v>
-      </c>
-      <c r="B13" s="2" t="s">
-        <v>131</v>
-      </c>
-      <c r="C13" s="2" t="s">
+        <v>170</v>
+      </c>
+      <c r="B13" s="1" t="s">
+        <v>152</v>
+      </c>
+      <c r="C13" s="1" t="s">
         <v>91</v>
       </c>
-      <c r="D13" s="2" t="s">
-        <v>150</v>
+      <c r="D13" s="1" t="s">
+        <v>171</v>
       </c>
       <c r="E13"/>
-      <c r="H13" s="2">
+      <c r="H13" s="1">
         <v>10</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="2"/>
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1">
+    <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" t="s">
-        <v>151</v>
-      </c>
-      <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>172</v>
+      </c>
+      <c r="B14" s="1" t="s">
+        <v>121</v>
       </c>
       <c r="C14" t="s">
         <v>110</v>
       </c>
-      <c r="D14" s="2" t="s">
-        <v>152</v>
+      <c r="D14" s="1" t="s">
+        <v>173</v>
       </c>
       <c r="E14"/>
-      <c r="F14" s="2">
+      <c r="F14" s="1">
         <v>7</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="5"/>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1">
+    <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" t="s">
-        <v>153</v>
-      </c>
-      <c r="C15" s="2" t="s">
+        <v>174</v>
+      </c>
+      <c r="C15" s="1" t="s">
         <v>113</v>
       </c>
-      <c r="D15" s="2" t="s">
-        <v>154</v>
+      <c r="D15" s="1" t="s">
+        <v>175</v>
       </c>
       <c r="E15"/>
-      <c r="F15" s="2">
+      <c r="F15" s="1">
         <v>7</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="5"/>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1">
+    <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" t="s">
+        <v>176</v>
+      </c>
+      <c r="B16" s="1" t="s">
         <v>155</v>
-      </c>
-      <c r="B16" s="2" t="s">
-        <v>134</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
       </c>
-      <c r="D16" s="2" t="s">
-        <v>156</v>
+      <c r="D16" s="1" t="s">
+        <v>177</v>
       </c>
       <c r="E16"/>
-      <c r="F16" s="2">
+      <c r="F16" s="1">
         <v>7</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="5"/>
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1">
+    <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" t="s">
-        <v>157</v>
-      </c>
-      <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>178</v>
+      </c>
+      <c r="B17" s="1" t="s">
+        <v>142</v>
       </c>
       <c r="C17" t="s">
         <v>106</v>
       </c>
-      <c r="D17" s="2" t="s">
-        <v>158</v>
+      <c r="D17" s="1" t="s">
+        <v>179</v>
       </c>
       <c r="E17"/>
-      <c r="H17" s="2">
+      <c r="H17" s="1">
         <v>10</v>
       </c>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="5"/>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1">
+    <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" t="s">
-        <v>159</v>
-      </c>
-      <c r="B18" s="2" t="s">
-        <v>139</v>
-      </c>
-      <c r="D18" s="2" t="s">
+        <v>180</v>
+      </c>
+      <c r="B18" s="1" t="s">
         <v>160</v>
       </c>
+      <c r="D18" s="1" t="s">
+        <v>181</v>
+      </c>
       <c r="E18"/>
-      <c r="I18" s="2">
+      <c r="I18" s="1">
         <v>7</v>
       </c>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="5"/>
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1">
+    <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" t="s">
-        <v>161</v>
-      </c>
-      <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>182</v>
+      </c>
+      <c r="B19" s="1" t="s">
+        <v>160</v>
       </c>
       <c r="C19" t="s">
         <v>110</v>
       </c>
-      <c r="D19" s="2" t="s">
-        <v>162</v>
+      <c r="D19" s="1" t="s">
+        <v>183</v>
       </c>
       <c r="E19"/>
-      <c r="F19" s="2">
+      <c r="F19" s="1">
         <v>10</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="5"/>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1">
+    <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" t="s">
-        <v>163</v>
-      </c>
-      <c r="B20" s="2" t="s">
-        <v>143</v>
-      </c>
-      <c r="D20" s="2" t="s">
+        <v>184</v>
+      </c>
+      <c r="B20" s="1" t="s">
         <v>164</v>
       </c>
+      <c r="D20" s="1" t="s">
+        <v>185</v>
+      </c>
       <c r="E20"/>
-      <c r="H20" s="2">
+      <c r="H20" s="1">
         <v>10</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="5"/>
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1">
+    <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" t="s">
-        <v>165</v>
-      </c>
-      <c r="B21" s="2" t="s">
-        <v>124</v>
-      </c>
-      <c r="D21" s="2" t="s">
-        <v>166</v>
+        <v>186</v>
+      </c>
+      <c r="B21" s="1" t="s">
+        <v>145</v>
+      </c>
+      <c r="D21" s="1" t="s">
+        <v>187</v>
       </c>
       <c r="E21"/>
-      <c r="K21" s="2">
+      <c r="K21" s="1">
         <v>7</v>
       </c>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="5"/>
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1">
+    <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" t="s">
-        <v>167</v>
-      </c>
-      <c r="C22" s="2" t="s">
+        <v>188</v>
+      </c>
+      <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
-      <c r="D22" s="2" t="s">
-        <v>168</v>
+      <c r="D22" s="1" t="s">
+        <v>189</v>
       </c>
       <c r="E22"/>
-      <c r="N22" s="2">
+      <c r="N22" s="1">
         <v>3</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="5"/>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1">
+    <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" t="s">
-        <v>169</v>
-      </c>
-      <c r="C23" s="2" t="s">
+        <v>190</v>
+      </c>
+      <c r="C23" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D23" s="2" t="s">
-        <v>170</v>
+      <c r="D23" s="1" t="s">
+        <v>191</v>
       </c>
       <c r="E23"/>
-      <c r="K23" s="2">
-        <v>5</v>
-      </c>
-      <c r="Q23" s="4"/>
+      <c r="K23" s="1">
+        <v>5</v>
+      </c>
+      <c r="Q23" s="5"/>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
     </row>
-    <row r="24" spans="1:22">
+    <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>171</v>
-      </c>
-      <c r="C24" s="2" t="s">
+        <v>192</v>
+      </c>
+      <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
-      <c r="D24" s="2" t="s">
-        <v>172</v>
+      <c r="D24" s="1" t="s">
+        <v>193</v>
       </c>
       <c r="K24">
         <v>5</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
+    <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>173</v>
+        <v>194</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>175</v>
+        <v>195</v>
+      </c>
+      <c r="D25" s="1" t="s">
+        <v>196</v>
       </c>
       <c r="Q25" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="26" spans="1:22">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>177</v>
+        <v>198</v>
       </c>
       <c r="B26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>178</v>
+        <v>195</v>
+      </c>
+      <c r="D26" s="1" t="s">
+        <v>199</v>
       </c>
       <c r="Q26" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="27" spans="1:22">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>201</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
-      </c>
-      <c r="C27" s="2" t="s">
+        <v>121</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
-      <c r="D27" s="2" t="s">
-        <v>181</v>
+      <c r="D27" s="1" t="s">
+        <v>202</v>
       </c>
       <c r="F27">
         <v>5</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
+    <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>203</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
-      </c>
-      <c r="D28" s="2" t="s">
-        <v>183</v>
+        <v>152</v>
+      </c>
+      <c r="D28" s="1" t="s">
+        <v>204</v>
       </c>
       <c r="F28">
         <v>5</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
+    <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>205</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
-      </c>
-      <c r="D29" s="2" t="s">
-        <v>185</v>
+        <v>155</v>
+      </c>
+      <c r="D29" s="1" t="s">
+        <v>206</v>
       </c>
       <c r="F29">
         <v>5</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
+    <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>207</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C30" t="s">
         <v>113</v>
       </c>
-      <c r="D30" s="2" t="s">
-        <v>187</v>
+      <c r="D30" s="1" t="s">
+        <v>208</v>
       </c>
       <c r="G30">
         <v>5</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
+    <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>209</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
-      </c>
-      <c r="D31" s="2" t="s">
-        <v>189</v>
+        <v>195</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>210</v>
       </c>
       <c r="L31">
         <v>8</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
+    <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>211</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
-      <c r="D32" s="2" t="s">
-        <v>191</v>
+      <c r="D32" s="1" t="s">
+        <v>212</v>
       </c>
       <c r="N32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:17">
+    <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>213</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C33" t="s">
         <v>86</v>
       </c>
-      <c r="D33" s="2" t="s">
-        <v>193</v>
+      <c r="D33" s="1" t="s">
+        <v>214</v>
       </c>
       <c r="H33">
         <v>7</v>
       </c>
     </row>
-    <row r="34" spans="1:17">
+    <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>215</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
-      </c>
-      <c r="D34" s="2" t="s">
-        <v>195</v>
+        <v>155</v>
+      </c>
+      <c r="D34" s="1" t="s">
+        <v>216</v>
       </c>
       <c r="L34">
         <v>5</v>
       </c>
     </row>
-    <row r="35" spans="1:17">
+    <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>217</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C35" t="s">
         <v>106</v>
       </c>
-      <c r="D35" s="2" t="s">
-        <v>197</v>
+      <c r="D35" s="1" t="s">
+        <v>218</v>
       </c>
       <c r="H35">
         <v>7</v>
       </c>
     </row>
-    <row r="36" spans="1:17">
+    <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>219</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
-      <c r="D36" s="2" t="s">
-        <v>199</v>
+      <c r="D36" s="1" t="s">
+        <v>220</v>
       </c>
       <c r="F36">
         <v>5</v>
       </c>
     </row>
-    <row r="37" spans="1:17">
+    <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>221</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
-      <c r="D37" s="2" t="s">
-        <v>201</v>
+      <c r="D37" s="1" t="s">
+        <v>222</v>
       </c>
       <c r="F37">
         <v>7</v>
       </c>
     </row>
-    <row r="38" spans="1:17">
+    <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>223</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
-      <c r="D38" s="2" t="s">
-        <v>203</v>
+      <c r="D38" s="1" t="s">
+        <v>224</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -3306,64 +4055,64 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>225</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C39" t="s">
         <v>110</v>
       </c>
-      <c r="D39" s="4" t="s">
-        <v>205</v>
+      <c r="D39" s="5" t="s">
+        <v>226</v>
       </c>
       <c r="Q39" t="s">
-        <v>179</v>
-      </c>
-    </row>
-    <row r="40" spans="1:17">
+        <v>200</v>
+      </c>
+    </row>
+    <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>227</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C40" t="s">
         <v>110</v>
       </c>
-      <c r="D40" s="2" t="s">
-        <v>207</v>
+      <c r="D40" s="1" t="s">
+        <v>228</v>
       </c>
       <c r="L40">
         <v>5</v>
       </c>
     </row>
-    <row r="41" spans="1:17">
+    <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>229</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C41" t="s">
         <v>106</v>
       </c>
-      <c r="D41" s="2" t="s">
-        <v>209</v>
+      <c r="D41" s="1" t="s">
+        <v>230</v>
       </c>
       <c r="H41">
         <v>5</v>
       </c>
     </row>
-    <row r="42" spans="1:17">
+    <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>231</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
-      </c>
-      <c r="D42" s="2" t="s">
-        <v>211</v>
+        <v>195</v>
+      </c>
+      <c r="D42" s="1" t="s">
+        <v>232</v>
       </c>
       <c r="F42">
         <v>11</v>
@@ -3371,62 +4120,63 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>233</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
-      </c>
-      <c r="D43" s="2" t="s">
-        <v>213</v>
+        <v>145</v>
+      </c>
+      <c r="D43" s="1" t="s">
+        <v>234</v>
       </c>
       <c r="Q43" t="s">
-        <v>176</v>
-      </c>
-    </row>
-    <row r="44" spans="1:17">
+        <v>197</v>
+      </c>
+    </row>
+    <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>235</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
-      </c>
-      <c r="D44" s="2" t="s">
-        <v>215</v>
+        <v>145</v>
+      </c>
+      <c r="D44" s="1" t="s">
+        <v>236</v>
       </c>
       <c r="H44">
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:17">
+    <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>237</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
-      </c>
-      <c r="D45" s="2" t="s">
-        <v>217</v>
+        <v>142</v>
+      </c>
+      <c r="D45" s="1" t="s">
+        <v>238</v>
       </c>
       <c r="I45">
         <v>7</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V71"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
-    <col min="4" max="4" width="28.6640625" style="3" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="4" max="4" width="28.6666666666667" style="2" customWidth="1"/>
+    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
     <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -3461,7 +4211,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -3485,1172 +4235,1173 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="3" t="s">
-        <v>295</v>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
+        <v>239</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>240</v>
       </c>
       <c r="L2">
         <v>3</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="3" t="s">
-        <v>296</v>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="2" t="s">
+        <v>241</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>242</v>
       </c>
       <c r="F3">
         <v>3</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="3" t="s">
-        <v>297</v>
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="2" t="s">
+        <v>243</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>244</v>
       </c>
       <c r="O4">
         <v>3</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="3" t="s">
-        <v>298</v>
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="1:6">
+      <c r="A5" s="2" t="s">
+        <v>245</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>246</v>
       </c>
       <c r="F5">
         <v>3</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="3" t="s">
-        <v>299</v>
+    <row r="6" spans="1:17">
+      <c r="A6" s="2" t="s">
+        <v>247</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>248</v>
       </c>
       <c r="M6">
         <v>3</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="3" t="s">
-        <v>300</v>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="2" t="s">
+        <v>249</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>250</v>
       </c>
       <c r="G7">
         <v>3</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="3" t="s">
-        <v>301</v>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:13">
+      <c r="A8" s="2" t="s">
+        <v>251</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C8" t="s">
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>224</v>
+        <v>252</v>
       </c>
       <c r="M8">
         <v>3</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="3" t="s">
-        <v>302</v>
+    <row r="9" spans="1:6">
+      <c r="A9" s="2" t="s">
+        <v>253</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>254</v>
       </c>
       <c r="F9">
         <v>3</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
-      <c r="A10" s="3" t="s">
-        <v>303</v>
+    <row r="10" spans="1:17">
+      <c r="A10" s="2" t="s">
+        <v>255</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>256</v>
       </c>
       <c r="K10">
         <v>2</v>
       </c>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="A11" s="3" t="s">
-        <v>304</v>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="1:17">
+      <c r="A11" s="2" t="s">
+        <v>257</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>258</v>
       </c>
       <c r="F11">
         <v>2</v>
       </c>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1">
-      <c r="A12" s="3" t="s">
-        <v>305</v>
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:22">
+      <c r="A12" s="2" t="s">
+        <v>259</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>260</v>
       </c>
       <c r="E12"/>
       <c r="I12">
         <v>3</v>
       </c>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="2"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1">
-      <c r="A13" s="3" t="s">
-        <v>306</v>
+    <row r="13" s="1" customFormat="1" spans="1:22">
+      <c r="A13" s="2" t="s">
+        <v>261</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>262</v>
       </c>
       <c r="E13"/>
       <c r="F13">
         <v>2</v>
       </c>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="2"/>
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1">
-      <c r="A14" s="3" t="s">
-        <v>307</v>
+    <row r="14" s="1" customFormat="1" spans="1:22">
+      <c r="A14" s="2" t="s">
+        <v>263</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>264</v>
       </c>
       <c r="E14"/>
       <c r="G14">
         <v>2</v>
       </c>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="5"/>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1">
-      <c r="A15" s="3" t="s">
-        <v>308</v>
+    <row r="15" s="1" customFormat="1" spans="1:22">
+      <c r="A15" s="2" t="s">
+        <v>265</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>266</v>
       </c>
       <c r="E15"/>
       <c r="F15">
         <v>3</v>
       </c>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="5"/>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1">
-      <c r="A16" s="3" t="s">
-        <v>309</v>
+    <row r="16" s="1" customFormat="1" spans="1:22">
+      <c r="A16" s="2" t="s">
+        <v>267</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>268</v>
       </c>
       <c r="E16"/>
       <c r="L16">
         <v>3</v>
       </c>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="5"/>
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1">
-      <c r="A17" s="3" t="s">
-        <v>310</v>
+    <row r="17" s="1" customFormat="1" spans="1:22">
+      <c r="A17" s="2" t="s">
+        <v>269</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>270</v>
       </c>
       <c r="E17"/>
       <c r="O17">
         <v>1</v>
       </c>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="5"/>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1">
-      <c r="A18" s="3" t="s">
-        <v>311</v>
+    <row r="18" s="1" customFormat="1" spans="1:22">
+      <c r="A18" s="2" t="s">
+        <v>271</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C18" t="s">
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>272</v>
       </c>
       <c r="E18"/>
       <c r="F18">
         <v>2</v>
       </c>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="5"/>
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1">
-      <c r="A19" s="3" t="s">
-        <v>312</v>
+    <row r="19" s="1" customFormat="1" spans="1:22">
+      <c r="A19" s="2" t="s">
+        <v>273</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C19" t="s">
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>274</v>
       </c>
       <c r="E19"/>
       <c r="K19">
         <v>2</v>
       </c>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="5"/>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1">
-      <c r="A20" s="3" t="s">
-        <v>313</v>
+    <row r="20" s="1" customFormat="1" spans="1:22">
+      <c r="A20" s="2" t="s">
+        <v>275</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>276</v>
       </c>
       <c r="E20"/>
       <c r="I20">
         <v>2</v>
       </c>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="5"/>
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1">
-      <c r="A21" s="3" t="s">
-        <v>314</v>
+    <row r="21" s="1" customFormat="1" spans="1:22">
+      <c r="A21" s="2" t="s">
+        <v>277</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>278</v>
       </c>
       <c r="E21"/>
       <c r="I21">
         <v>3</v>
       </c>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="5"/>
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1">
-      <c r="A22" s="3" t="s">
-        <v>315</v>
+    <row r="22" s="1" customFormat="1" spans="1:22">
+      <c r="A22" s="2" t="s">
+        <v>279</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>280</v>
       </c>
       <c r="E22"/>
       <c r="K22">
         <v>2</v>
       </c>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="5"/>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1">
-      <c r="A23" s="3" t="s">
-        <v>316</v>
+    <row r="23" s="1" customFormat="1" spans="1:22">
+      <c r="A23" s="2" t="s">
+        <v>281</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>239</v>
+        <v>282</v>
       </c>
       <c r="E23"/>
       <c r="H23">
         <v>2</v>
       </c>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="5"/>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
     </row>
-    <row r="24" spans="1:22">
-      <c r="A24" s="3" t="s">
-        <v>317</v>
+    <row r="24" spans="1:7">
+      <c r="A24" s="2" t="s">
+        <v>283</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
-      </c>
-      <c r="C24" s="2"/>
+        <v>121</v>
+      </c>
+      <c r="C24" s="1"/>
       <c r="D24" t="s">
-        <v>240</v>
+        <v>284</v>
       </c>
       <c r="G24">
         <v>3</v>
       </c>
     </row>
-    <row r="25" spans="1:22">
-      <c r="A25" s="3" t="s">
-        <v>318</v>
+    <row r="25" spans="1:6">
+      <c r="A25" s="2" t="s">
+        <v>285</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>286</v>
       </c>
       <c r="F25">
         <v>3</v>
       </c>
     </row>
-    <row r="26" spans="1:22">
-      <c r="A26" s="3" t="s">
-        <v>319</v>
+    <row r="26" spans="1:11">
+      <c r="A26" s="2" t="s">
+        <v>287</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>288</v>
       </c>
       <c r="K26">
         <v>3</v>
       </c>
     </row>
-    <row r="27" spans="1:22">
-      <c r="A27" s="3" t="s">
-        <v>320</v>
+    <row r="27" spans="1:6">
+      <c r="A27" s="2" t="s">
+        <v>289</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
-      </c>
-      <c r="C27" s="2" t="s">
+        <v>145</v>
+      </c>
+      <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>290</v>
       </c>
       <c r="F27">
         <v>3</v>
       </c>
     </row>
-    <row r="28" spans="1:22">
-      <c r="A28" s="3" t="s">
-        <v>321</v>
+    <row r="28" spans="1:12">
+      <c r="A28" s="2" t="s">
+        <v>291</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>292</v>
       </c>
       <c r="L28">
         <v>2</v>
       </c>
     </row>
-    <row r="29" spans="1:22">
-      <c r="A29" s="3" t="s">
-        <v>322</v>
+    <row r="29" spans="1:6">
+      <c r="A29" s="2" t="s">
+        <v>293</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>294</v>
       </c>
       <c r="F29">
         <v>2</v>
       </c>
     </row>
-    <row r="30" spans="1:22">
-      <c r="A30" s="3" t="s">
-        <v>323</v>
+    <row r="30" spans="1:11">
+      <c r="A30" s="2" t="s">
+        <v>295</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>246</v>
+        <v>296</v>
       </c>
       <c r="K30">
         <v>2</v>
       </c>
     </row>
-    <row r="31" spans="1:22">
-      <c r="A31" s="3" t="s">
-        <v>324</v>
+    <row r="31" spans="1:7">
+      <c r="A31" s="2" t="s">
+        <v>297</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>298</v>
       </c>
       <c r="G31">
         <v>2</v>
       </c>
     </row>
-    <row r="32" spans="1:22">
-      <c r="A32" s="3" t="s">
-        <v>325</v>
+    <row r="32" spans="1:6">
+      <c r="A32" s="2" t="s">
+        <v>299</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>164</v>
       </c>
       <c r="C32" t="s">
         <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>300</v>
       </c>
       <c r="F32">
         <v>2</v>
       </c>
     </row>
-    <row r="33" spans="1:15">
-      <c r="A33" s="3" t="s">
-        <v>326</v>
+    <row r="33" spans="1:12">
+      <c r="A33" s="2" t="s">
+        <v>301</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D33" t="s">
-        <v>249</v>
+        <v>302</v>
       </c>
       <c r="L33">
         <v>2</v>
       </c>
     </row>
-    <row r="34" spans="1:15">
-      <c r="A34" s="3" t="s">
-        <v>327</v>
+    <row r="34" spans="1:11">
+      <c r="A34" s="2" t="s">
+        <v>303</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D34" t="s">
-        <v>250</v>
+        <v>304</v>
       </c>
       <c r="K34">
         <v>3</v>
       </c>
     </row>
-    <row r="35" spans="1:15">
-      <c r="A35" s="3" t="s">
-        <v>328</v>
+    <row r="35" spans="1:11">
+      <c r="A35" s="2" t="s">
+        <v>305</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>251</v>
+        <v>306</v>
       </c>
       <c r="K35">
         <v>3</v>
       </c>
     </row>
     <row r="36" spans="1:15">
-      <c r="A36" s="3" t="s">
-        <v>329</v>
+      <c r="A36" s="2" t="s">
+        <v>307</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>160</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>308</v>
       </c>
       <c r="O36">
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:15">
-      <c r="A37" s="3" t="s">
-        <v>330</v>
+    <row r="37" spans="1:12">
+      <c r="A37" s="2" t="s">
+        <v>309</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>253</v>
+        <v>310</v>
       </c>
       <c r="L37">
         <v>2</v>
       </c>
     </row>
-    <row r="38" spans="1:15">
-      <c r="A38" s="3" t="s">
-        <v>331</v>
+    <row r="38" spans="1:6">
+      <c r="A38" s="2" t="s">
+        <v>311</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>312</v>
       </c>
       <c r="F38">
         <v>1</v>
       </c>
     </row>
-    <row r="39" spans="1:15">
-      <c r="A39" s="3" t="s">
-        <v>332</v>
+    <row r="39" spans="1:11">
+      <c r="A39" s="2" t="s">
+        <v>313</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C39" t="s">
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>255</v>
+        <v>314</v>
       </c>
       <c r="K39">
         <v>2</v>
       </c>
     </row>
-    <row r="40" spans="1:15">
-      <c r="A40" s="3" t="s">
-        <v>333</v>
+    <row r="40" spans="1:12">
+      <c r="A40" s="2" t="s">
+        <v>315</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C40" t="s">
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>316</v>
       </c>
       <c r="L40">
         <v>2</v>
       </c>
     </row>
-    <row r="41" spans="1:15">
-      <c r="A41" s="3" t="s">
-        <v>334</v>
+    <row r="41" spans="1:6">
+      <c r="A41" s="2" t="s">
+        <v>317</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>257</v>
+        <v>318</v>
       </c>
       <c r="F41">
         <v>2</v>
       </c>
     </row>
-    <row r="42" spans="1:15">
-      <c r="A42" s="3" t="s">
-        <v>335</v>
+    <row r="42" spans="1:11">
+      <c r="A42" s="2" t="s">
+        <v>319</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="D42" t="s">
-        <v>258</v>
+        <v>320</v>
       </c>
       <c r="K42">
         <v>2</v>
       </c>
     </row>
-    <row r="43" spans="1:15">
-      <c r="A43" s="3" t="s">
-        <v>336</v>
+    <row r="43" spans="1:11">
+      <c r="A43" s="2" t="s">
+        <v>321</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>259</v>
+        <v>322</v>
       </c>
       <c r="K43">
         <v>2</v>
       </c>
     </row>
-    <row r="44" spans="1:15">
-      <c r="A44" s="3" t="s">
-        <v>337</v>
+    <row r="44" spans="1:8">
+      <c r="A44" s="2" t="s">
+        <v>323</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>324</v>
       </c>
       <c r="H44">
         <v>2</v>
       </c>
     </row>
-    <row r="45" spans="1:15">
-      <c r="A45" s="3" t="s">
-        <v>338</v>
+    <row r="45" spans="1:6">
+      <c r="A45" s="2" t="s">
+        <v>325</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C45" t="s">
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>261</v>
+        <v>326</v>
       </c>
       <c r="F45">
         <v>5</v>
       </c>
     </row>
-    <row r="46" spans="1:15">
-      <c r="A46" s="3" t="s">
-        <v>339</v>
+    <row r="46" spans="1:6">
+      <c r="A46" s="2" t="s">
+        <v>327</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D46" t="s">
-        <v>262</v>
+        <v>328</v>
       </c>
       <c r="F46">
         <v>5</v>
       </c>
     </row>
-    <row r="47" spans="1:15">
-      <c r="A47" s="3" t="s">
-        <v>340</v>
+    <row r="47" spans="1:6">
+      <c r="A47" s="2" t="s">
+        <v>329</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>142</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>330</v>
       </c>
       <c r="F47">
         <v>3</v>
       </c>
     </row>
     <row r="48" spans="1:15">
-      <c r="A48" s="3" t="s">
-        <v>341</v>
-      </c>
-      <c r="D48" s="3" t="s">
-        <v>264</v>
+      <c r="A48" s="2" t="s">
+        <v>331</v>
+      </c>
+      <c r="D48" s="2" t="s">
+        <v>332</v>
       </c>
       <c r="O48">
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:13">
-      <c r="A49" s="3" t="s">
-        <v>342</v>
+    <row r="49" spans="1:7">
+      <c r="A49" s="2" t="s">
+        <v>333</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>334</v>
       </c>
       <c r="G49">
         <v>3</v>
       </c>
     </row>
-    <row r="50" spans="1:13">
-      <c r="A50" s="3" t="s">
-        <v>343</v>
+    <row r="50" spans="1:8">
+      <c r="A50" s="2" t="s">
+        <v>335</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>336</v>
       </c>
       <c r="H50">
         <v>2</v>
       </c>
     </row>
-    <row r="51" spans="1:13">
-      <c r="A51" s="3" t="s">
-        <v>344</v>
+    <row r="51" spans="1:12">
+      <c r="A51" s="2" t="s">
+        <v>337</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>338</v>
       </c>
       <c r="L51">
         <v>3</v>
       </c>
     </row>
-    <row r="52" spans="1:13">
-      <c r="A52" s="3" t="s">
-        <v>345</v>
+    <row r="52" spans="1:7">
+      <c r="A52" s="2" t="s">
+        <v>339</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>268</v>
+        <v>340</v>
       </c>
       <c r="G52">
         <v>3</v>
       </c>
     </row>
-    <row r="53" spans="1:13">
-      <c r="A53" s="3" t="s">
-        <v>346</v>
+    <row r="53" spans="1:8">
+      <c r="A53" s="2" t="s">
+        <v>341</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>269</v>
+        <v>342</v>
       </c>
       <c r="H53">
         <v>5</v>
       </c>
     </row>
-    <row r="54" spans="1:13">
-      <c r="A54" s="3" t="s">
-        <v>347</v>
+    <row r="54" spans="1:9">
+      <c r="A54" s="2" t="s">
+        <v>343</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D54" t="s">
-        <v>270</v>
+        <v>344</v>
       </c>
       <c r="I54">
         <v>10</v>
       </c>
     </row>
-    <row r="55" spans="1:13">
-      <c r="A55" s="3" t="s">
-        <v>348</v>
+    <row r="55" spans="1:9">
+      <c r="A55" s="2" t="s">
+        <v>345</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>346</v>
       </c>
       <c r="I55">
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:13">
-      <c r="A56" s="3" t="s">
+    <row r="56" spans="1:7">
+      <c r="A56" s="2" t="s">
+        <v>347</v>
+      </c>
+      <c r="B56" t="s">
+        <v>195</v>
+      </c>
+      <c r="D56" t="s">
+        <v>348</v>
+      </c>
+      <c r="G56">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="57" spans="1:9">
+      <c r="A57" s="2" t="s">
         <v>349</v>
       </c>
-      <c r="B56" t="s">
-        <v>174</v>
-      </c>
-      <c r="D56" t="s">
-        <v>272</v>
-      </c>
-      <c r="G56">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="57" spans="1:13">
-      <c r="A57" s="3" t="s">
+      <c r="B57" t="s">
+        <v>155</v>
+      </c>
+      <c r="D57" t="s">
         <v>350</v>
-      </c>
-      <c r="B57" t="s">
-        <v>134</v>
-      </c>
-      <c r="D57" t="s">
-        <v>273</v>
       </c>
       <c r="I57">
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:13">
-      <c r="A58" s="3" t="s">
+    <row r="58" spans="1:9">
+      <c r="A58" s="2" t="s">
         <v>351</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D58" t="s">
-        <v>274</v>
+        <v>352</v>
       </c>
       <c r="I58">
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:13">
-      <c r="A59" s="3" t="s">
-        <v>352</v>
+    <row r="59" spans="1:7">
+      <c r="A59" s="2" t="s">
+        <v>353</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D59" t="s">
-        <v>275</v>
+        <v>354</v>
       </c>
       <c r="G59">
         <v>3</v>
       </c>
     </row>
-    <row r="60" spans="1:13">
-      <c r="A60" s="3" t="s">
-        <v>353</v>
+    <row r="60" spans="1:6">
+      <c r="A60" s="2" t="s">
+        <v>355</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>155</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>356</v>
       </c>
       <c r="F60">
         <v>5</v>
       </c>
     </row>
-    <row r="61" spans="1:13">
-      <c r="A61" s="3" t="s">
-        <v>354</v>
+    <row r="61" spans="1:6">
+      <c r="A61" s="2" t="s">
+        <v>357</v>
       </c>
       <c r="C61" t="s">
         <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>358</v>
       </c>
       <c r="F61">
         <v>3</v>
       </c>
     </row>
     <row r="62" spans="1:13">
-      <c r="A62" s="3" t="s">
-        <v>355</v>
+      <c r="A62" s="2" t="s">
+        <v>359</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>121</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>278</v>
+        <v>360</v>
       </c>
       <c r="M62">
         <v>2</v>
       </c>
     </row>
-    <row r="63" spans="1:13">
-      <c r="A63" s="3" t="s">
-        <v>356</v>
+    <row r="63" spans="1:8">
+      <c r="A63" s="2" t="s">
+        <v>361</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>152</v>
       </c>
       <c r="D63" t="s">
-        <v>279</v>
+        <v>362</v>
       </c>
       <c r="H63">
         <v>5</v>
       </c>
     </row>
-    <row r="64" spans="1:13">
-      <c r="A64" s="3" t="s">
-        <v>357</v>
+    <row r="64" spans="1:7">
+      <c r="A64" s="2" t="s">
+        <v>363</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>280</v>
+        <v>364</v>
       </c>
       <c r="G64">
         <v>5</v>
       </c>
     </row>
-    <row r="65" spans="1:15">
-      <c r="A65" s="3" t="s">
-        <v>358</v>
+    <row r="65" spans="1:8">
+      <c r="A65" s="2" t="s">
+        <v>365</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D65" t="s">
-        <v>281</v>
+        <v>366</v>
       </c>
       <c r="H65">
         <v>5</v>
       </c>
     </row>
     <row r="66" spans="1:15">
-      <c r="A66" s="3" t="s">
-        <v>359</v>
+      <c r="A66" s="2" t="s">
+        <v>367</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D66" t="s">
-        <v>282</v>
+        <v>368</v>
       </c>
       <c r="O66">
         <v>9</v>
       </c>
     </row>
-    <row r="67" spans="1:15">
-      <c r="A67" s="3" t="s">
-        <v>360</v>
+    <row r="67" spans="1:6">
+      <c r="A67" s="2" t="s">
+        <v>369</v>
       </c>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D67" t="s">
-        <v>283</v>
+        <v>370</v>
       </c>
       <c r="F67">
         <v>5</v>
       </c>
     </row>
-    <row r="68" spans="1:15">
-      <c r="A68" s="3" t="s">
-        <v>361</v>
+    <row r="68" spans="1:9">
+      <c r="A68" s="2" t="s">
+        <v>371</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>372</v>
       </c>
       <c r="I68">
         <v>10</v>
       </c>
     </row>
     <row r="69" spans="1:15">
-      <c r="A69" s="3" t="s">
-        <v>362</v>
+      <c r="A69" s="2" t="s">
+        <v>373</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>195</v>
       </c>
       <c r="D69" t="s">
-        <v>285</v>
+        <v>374</v>
       </c>
       <c r="O69">
         <v>6</v>
       </c>
     </row>
-    <row r="70" spans="1:15">
-      <c r="A70" s="3" t="s">
-        <v>363</v>
+    <row r="70" spans="1:8">
+      <c r="A70" s="2" t="s">
+        <v>375</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>145</v>
       </c>
       <c r="D70" t="s">
-        <v>286</v>
+        <v>376</v>
       </c>
       <c r="H70">
         <v>5</v>
       </c>
     </row>
-    <row r="71" spans="1:15">
-      <c r="A71" s="7" t="s">
-        <v>380</v>
-      </c>
-      <c r="B71" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>383</v>
+    <row r="71" spans="1:6">
+      <c r="A71" s="6" t="s">
+        <v>377</v>
+      </c>
+      <c r="B71" s="7" t="s">
+        <v>195</v>
+      </c>
+      <c r="C71" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D71" s="6" t="s">
+        <v>378</v>
       </c>
       <c r="F71">
         <v>8</v>
       </c>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
 
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0400-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
+  <sheetPr/>
   <dimension ref="A1:V45"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
   <cols>
-    <col min="1" max="1" width="17.1640625" customWidth="1"/>
-    <col min="2" max="2" width="5.6640625" customWidth="1"/>
+    <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
+    <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
     <col min="3" max="3" width="9" customWidth="1"/>
     <col min="4" max="4" width="16" customWidth="1"/>
-    <col min="5" max="5" width="5.6640625" customWidth="1"/>
+    <col min="5" max="5" width="5.66666666666667" customWidth="1"/>
     <col min="17" max="17" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -4685,7 +5436,7 @@
       <c r="J1" t="s">
         <v>9</v>
       </c>
-      <c r="K1" s="1" t="s">
+      <c r="K1" s="3" t="s">
         <v>10</v>
       </c>
       <c r="L1" t="s">
@@ -4709,311 +5460,311 @@
       <c r="R1" t="s">
         <v>17</v>
       </c>
-      <c r="S1" s="5" t="s">
+      <c r="S1" s="4" t="s">
         <v>18</v>
       </c>
-      <c r="T1" s="5" t="s">
+      <c r="T1" s="4" t="s">
         <v>19</v>
       </c>
-      <c r="U1" s="5" t="s">
+      <c r="U1" s="4" t="s">
         <v>20</v>
       </c>
-      <c r="V1" s="5" t="s">
+      <c r="V1" s="4" t="s">
         <v>21</v>
       </c>
     </row>
-    <row r="2" spans="1:22">
-      <c r="A2" s="3" t="s">
-        <v>364</v>
+    <row r="2" spans="1:17">
+      <c r="A2" s="2" t="s">
+        <v>379</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
-      <c r="D2" s="2" t="s">
-        <v>287</v>
+      <c r="D2" s="1" t="s">
+        <v>380</v>
       </c>
       <c r="G2">
         <v>5</v>
       </c>
-      <c r="Q2" s="3"/>
-    </row>
-    <row r="3" spans="1:22">
-      <c r="A3" s="3" t="s">
-        <v>365</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>288</v>
+      <c r="Q2" s="2"/>
+    </row>
+    <row r="3" spans="1:17">
+      <c r="A3" s="2" t="s">
+        <v>381</v>
+      </c>
+      <c r="D3" s="1" t="s">
+        <v>382</v>
       </c>
       <c r="N3">
         <v>1</v>
       </c>
-      <c r="Q3" s="3"/>
-    </row>
-    <row r="4" spans="1:22">
-      <c r="A4" s="3" t="s">
-        <v>366</v>
+      <c r="Q3" s="2"/>
+    </row>
+    <row r="4" spans="1:17">
+      <c r="A4" s="2" t="s">
+        <v>383</v>
       </c>
       <c r="C4" t="s">
         <v>106</v>
       </c>
-      <c r="D4" s="2" t="s">
-        <v>289</v>
+      <c r="D4" s="1" t="s">
+        <v>384</v>
       </c>
       <c r="F4">
         <v>5</v>
       </c>
-      <c r="Q4" s="3"/>
-    </row>
-    <row r="5" spans="1:22">
-      <c r="A5" s="3" t="s">
-        <v>367</v>
-      </c>
-      <c r="D5" s="2" t="s">
-        <v>290</v>
+      <c r="Q4" s="2"/>
+    </row>
+    <row r="5" spans="1:15">
+      <c r="A5" s="2" t="s">
+        <v>385</v>
+      </c>
+      <c r="D5" s="1" t="s">
+        <v>386</v>
       </c>
       <c r="O5">
         <v>5</v>
       </c>
     </row>
-    <row r="6" spans="1:22">
-      <c r="A6" s="3" t="s">
-        <v>368</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>291</v>
+    <row r="6" spans="1:17">
+      <c r="A6" s="2" t="s">
+        <v>387</v>
+      </c>
+      <c r="D6" s="1" t="s">
+        <v>388</v>
       </c>
       <c r="I6">
         <v>5</v>
       </c>
-      <c r="Q6" s="3"/>
-    </row>
-    <row r="7" spans="1:22">
-      <c r="A7" s="3" t="s">
-        <v>369</v>
+      <c r="Q6" s="2"/>
+    </row>
+    <row r="7" spans="1:17">
+      <c r="A7" s="2" t="s">
+        <v>389</v>
       </c>
       <c r="C7" t="s">
         <v>106</v>
       </c>
-      <c r="D7" s="2" t="s">
-        <v>292</v>
+      <c r="D7" s="1" t="s">
+        <v>390</v>
       </c>
       <c r="H7">
         <v>7</v>
       </c>
-      <c r="Q7" s="3"/>
-    </row>
-    <row r="8" spans="1:22">
-      <c r="A8" s="3" t="s">
-        <v>370</v>
-      </c>
-      <c r="D8" s="2" t="s">
-        <v>293</v>
+      <c r="Q7" s="2"/>
+    </row>
+    <row r="8" spans="1:12">
+      <c r="A8" s="2" t="s">
+        <v>391</v>
+      </c>
+      <c r="D8" s="1" t="s">
+        <v>392</v>
       </c>
       <c r="L8">
         <v>5</v>
       </c>
     </row>
-    <row r="9" spans="1:22">
-      <c r="A9" s="3" t="s">
-        <v>371</v>
-      </c>
-      <c r="D9" s="2" t="s">
-        <v>294</v>
+    <row r="9" spans="1:11">
+      <c r="A9" s="2" t="s">
+        <v>393</v>
+      </c>
+      <c r="D9" s="1" t="s">
+        <v>394</v>
       </c>
       <c r="K9">
         <v>5</v>
       </c>
     </row>
-    <row r="10" spans="1:22">
-      <c r="D10" s="2"/>
-      <c r="Q10" s="3"/>
-    </row>
-    <row r="11" spans="1:22">
-      <c r="D11" s="2"/>
-      <c r="Q11" s="3"/>
-    </row>
-    <row r="12" spans="1:22" s="2" customFormat="1">
+    <row r="10" spans="4:17">
+      <c r="D10" s="1"/>
+      <c r="Q10" s="2"/>
+    </row>
+    <row r="11" spans="4:17">
+      <c r="D11" s="1"/>
+      <c r="Q11" s="2"/>
+    </row>
+    <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12"/>
       <c r="E12"/>
-      <c r="Q12" s="3"/>
+      <c r="Q12" s="2"/>
       <c r="S12"/>
       <c r="T12"/>
       <c r="U12"/>
       <c r="V12"/>
     </row>
-    <row r="13" spans="1:22" s="2" customFormat="1">
+    <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13"/>
       <c r="E13"/>
-      <c r="Q13" s="3"/>
+      <c r="Q13" s="2"/>
       <c r="S13"/>
       <c r="T13"/>
       <c r="U13"/>
       <c r="V13"/>
     </row>
-    <row r="14" spans="1:22" s="2" customFormat="1">
+    <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14"/>
       <c r="C14"/>
       <c r="E14"/>
-      <c r="Q14" s="4"/>
+      <c r="Q14" s="5"/>
       <c r="S14"/>
       <c r="T14"/>
       <c r="U14"/>
       <c r="V14"/>
     </row>
-    <row r="15" spans="1:22" s="2" customFormat="1">
+    <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15"/>
       <c r="E15"/>
-      <c r="Q15" s="4"/>
+      <c r="Q15" s="5"/>
       <c r="S15"/>
       <c r="T15"/>
       <c r="U15"/>
       <c r="V15"/>
     </row>
-    <row r="16" spans="1:22" s="2" customFormat="1">
+    <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16"/>
       <c r="C16"/>
       <c r="E16"/>
-      <c r="Q16" s="4"/>
+      <c r="Q16" s="5"/>
       <c r="S16"/>
       <c r="T16"/>
       <c r="U16"/>
       <c r="V16"/>
     </row>
-    <row r="17" spans="1:22" s="2" customFormat="1">
+    <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17"/>
       <c r="C17"/>
       <c r="E17"/>
-      <c r="Q17" s="4"/>
+      <c r="Q17" s="5"/>
       <c r="S17"/>
       <c r="T17"/>
       <c r="U17"/>
       <c r="V17"/>
     </row>
-    <row r="18" spans="1:22" s="2" customFormat="1">
+    <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18"/>
       <c r="E18"/>
-      <c r="Q18" s="4"/>
+      <c r="Q18" s="5"/>
       <c r="S18"/>
       <c r="T18"/>
       <c r="U18"/>
       <c r="V18"/>
     </row>
-    <row r="19" spans="1:22" s="2" customFormat="1">
+    <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19"/>
       <c r="C19"/>
       <c r="E19"/>
-      <c r="Q19" s="4"/>
+      <c r="Q19" s="5"/>
       <c r="S19"/>
       <c r="T19"/>
       <c r="U19"/>
       <c r="V19"/>
     </row>
-    <row r="20" spans="1:22" s="2" customFormat="1">
+    <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20"/>
       <c r="E20"/>
-      <c r="Q20" s="4"/>
+      <c r="Q20" s="5"/>
       <c r="S20"/>
       <c r="T20"/>
       <c r="U20"/>
       <c r="V20"/>
     </row>
-    <row r="21" spans="1:22" s="2" customFormat="1">
+    <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21"/>
       <c r="E21"/>
-      <c r="Q21" s="4"/>
+      <c r="Q21" s="5"/>
       <c r="S21"/>
       <c r="T21"/>
       <c r="U21"/>
       <c r="V21"/>
     </row>
-    <row r="22" spans="1:22" s="2" customFormat="1">
+    <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22"/>
       <c r="E22"/>
-      <c r="Q22" s="4"/>
+      <c r="Q22" s="5"/>
       <c r="S22"/>
       <c r="T22"/>
       <c r="U22"/>
       <c r="V22"/>
     </row>
-    <row r="23" spans="1:22" s="2" customFormat="1">
+    <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23"/>
       <c r="E23"/>
-      <c r="Q23" s="4"/>
+      <c r="Q23" s="5"/>
       <c r="S23"/>
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
     </row>
-    <row r="24" spans="1:22">
-      <c r="C24" s="2"/>
-      <c r="D24" s="2"/>
-    </row>
-    <row r="25" spans="1:22">
-      <c r="D25" s="2"/>
-    </row>
-    <row r="26" spans="1:22">
-      <c r="D26" s="2"/>
-    </row>
-    <row r="27" spans="1:22">
-      <c r="C27" s="2"/>
-      <c r="D27" s="2"/>
-    </row>
-    <row r="28" spans="1:22">
-      <c r="D28" s="2"/>
-    </row>
-    <row r="29" spans="1:22">
-      <c r="D29" s="2"/>
-    </row>
-    <row r="30" spans="1:22">
-      <c r="D30" s="2"/>
-    </row>
-    <row r="31" spans="1:22">
-      <c r="D31" s="2"/>
-    </row>
-    <row r="32" spans="1:22">
-      <c r="D32" s="2"/>
+    <row r="24" spans="3:4">
+      <c r="C24" s="1"/>
+      <c r="D24" s="1"/>
+    </row>
+    <row r="25" spans="4:4">
+      <c r="D25" s="1"/>
+    </row>
+    <row r="26" spans="4:4">
+      <c r="D26" s="1"/>
+    </row>
+    <row r="27" spans="3:4">
+      <c r="C27" s="1"/>
+      <c r="D27" s="1"/>
+    </row>
+    <row r="28" spans="4:4">
+      <c r="D28" s="1"/>
+    </row>
+    <row r="29" spans="4:4">
+      <c r="D29" s="1"/>
+    </row>
+    <row r="30" spans="4:4">
+      <c r="D30" s="1"/>
+    </row>
+    <row r="31" spans="4:4">
+      <c r="D31" s="1"/>
+    </row>
+    <row r="32" spans="4:4">
+      <c r="D32" s="1"/>
     </row>
     <row r="33" spans="4:4">
-      <c r="D33" s="2"/>
+      <c r="D33" s="1"/>
     </row>
     <row r="34" spans="4:4">
-      <c r="D34" s="2"/>
+      <c r="D34" s="1"/>
     </row>
     <row r="35" spans="4:4">
-      <c r="D35" s="2"/>
+      <c r="D35" s="1"/>
     </row>
     <row r="36" spans="4:4">
-      <c r="D36" s="2"/>
+      <c r="D36" s="1"/>
     </row>
     <row r="37" spans="4:4">
-      <c r="D37" s="2"/>
+      <c r="D37" s="1"/>
     </row>
     <row r="38" spans="4:4">
-      <c r="D38" s="2"/>
+      <c r="D38" s="1"/>
     </row>
     <row r="39" spans="4:4">
-      <c r="D39" s="2"/>
+      <c r="D39" s="1"/>
     </row>
     <row r="40" spans="4:4">
-      <c r="D40" s="2"/>
+      <c r="D40" s="1"/>
     </row>
     <row r="41" spans="4:4">
-      <c r="D41" s="2"/>
+      <c r="D41" s="1"/>
     </row>
     <row r="42" spans="4:4">
-      <c r="D42" s="2"/>
+      <c r="D42" s="1"/>
     </row>
     <row r="43" spans="4:4">
-      <c r="D43" s="2"/>
+      <c r="D43" s="1"/>
     </row>
     <row r="44" spans="4:4">
-      <c r="D44" s="2"/>
+      <c r="D44" s="1"/>
     </row>
     <row r="45" spans="4:4">
-      <c r="D45" s="2"/>
+      <c r="D45" s="1"/>
     </row>
   </sheetData>
-  <phoneticPr fontId="2" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <headerFooter/>
 </worksheet>
 </file>
--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="662" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="401">
   <si>
     <t>名称</t>
   </si>
@@ -441,6 +441,24 @@
   </si>
   <si>
     <t>中型火命+10</t>
+  </si>
+  <si>
+    <t>E1_evasion</t>
+  </si>
+  <si>
+    <t>全体回避-40，暴击+25%</t>
+  </si>
+  <si>
+    <t>E1_fire</t>
+  </si>
+  <si>
+    <t>全体火力-40，鱼雷+20，命中+20</t>
+  </si>
+  <si>
+    <t>E1_hit</t>
+  </si>
+  <si>
+    <t>全体命中-40，回避+40</t>
   </si>
   <si>
     <t>Dish_I_Fire</t>
@@ -1210,10 +1228,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1229,7 +1247,21 @@
     </font>
     <font>
       <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
       <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="0"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1237,9 +1269,9 @@
     <font>
       <b/>
       <sz val="11"/>
-      <color theme="3"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
-      <charset val="134"/>
+      <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
@@ -1266,15 +1298,33 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
+      <i/>
       <sz val="11"/>
-      <color theme="0"/>
+      <color rgb="FF7F7F7F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1288,14 +1338,6 @@
     </font>
     <font>
       <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
       <sz val="15"/>
       <color theme="3"/>
       <name val="Calibri"/>
@@ -1303,9 +1345,8 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF9C6500"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1314,27 +1355,6 @@
       <b/>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1356,17 +1376,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <i/>
       <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1388,13 +1406,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1406,97 +1478,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
         <fgColor theme="7" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1514,7 +1502,55 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor theme="6"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC6EFCE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1526,7 +1562,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1538,37 +1574,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="4"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFC7CE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1585,8 +1603,23 @@
       <left/>
       <right/>
       <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1615,21 +1648,6 @@
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
       <left/>
       <right/>
       <top style="thin">
@@ -1637,15 +1655,6 @@
       </top>
       <bottom style="double">
         <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1679,151 +1688,160 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="8" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="31" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="10" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="20" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="12" fillId="10" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="9" borderId="3" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="41" fontId="5" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -2987,7 +3005,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V15"/>
+  <dimension ref="A1:V18"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
@@ -3315,6 +3333,51 @@
       </c>
       <c r="K15">
         <v>10</v>
+      </c>
+    </row>
+    <row r="16" spans="1:16">
+      <c r="A16" t="s">
+        <v>141</v>
+      </c>
+      <c r="D16" t="s">
+        <v>142</v>
+      </c>
+      <c r="L16">
+        <v>-40</v>
+      </c>
+      <c r="P16">
+        <v>0.25</v>
+      </c>
+    </row>
+    <row r="17" spans="1:11">
+      <c r="A17" t="s">
+        <v>143</v>
+      </c>
+      <c r="D17" t="s">
+        <v>144</v>
+      </c>
+      <c r="F17">
+        <v>-40</v>
+      </c>
+      <c r="G17">
+        <v>20</v>
+      </c>
+      <c r="K17">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="18" spans="1:12">
+      <c r="A18" t="s">
+        <v>145</v>
+      </c>
+      <c r="D18" t="s">
+        <v>146</v>
+      </c>
+      <c r="K18">
+        <v>-40</v>
+      </c>
+      <c r="L18">
+        <v>40</v>
       </c>
     </row>
   </sheetData>
@@ -3407,13 +3470,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="B2" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>143</v>
+        <v>149</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -3422,13 +3485,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>144</v>
+        <v>150</v>
       </c>
       <c r="B3" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>146</v>
+        <v>152</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -3437,13 +3500,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>148</v>
+        <v>154</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -3452,13 +3515,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>149</v>
+        <v>155</v>
       </c>
       <c r="B5" t="s">
         <v>121</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>150</v>
+        <v>156</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
@@ -3466,16 +3529,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>151</v>
+        <v>157</v>
       </c>
       <c r="B6" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C6" t="s">
         <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>153</v>
+        <v>159</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -3484,16 +3547,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>154</v>
+        <v>160</v>
       </c>
       <c r="B7" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>156</v>
+        <v>162</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -3502,13 +3565,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>157</v>
+        <v>163</v>
       </c>
       <c r="B8" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>158</v>
+        <v>164</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -3516,30 +3579,30 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>159</v>
+        <v>165</v>
       </c>
       <c r="B9" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>161</v>
+        <v>167</v>
       </c>
       <c r="Q9" t="s">
-        <v>162</v>
+        <v>168</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>163</v>
+        <v>169</v>
       </c>
       <c r="B10" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>165</v>
+        <v>171</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -3548,13 +3611,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>166</v>
+        <v>172</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>167</v>
+        <v>173</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -3563,16 +3626,16 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" t="s">
-        <v>168</v>
+        <v>174</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>169</v>
+        <v>175</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="1">
@@ -3586,16 +3649,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" t="s">
-        <v>170</v>
+        <v>176</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>171</v>
+        <v>177</v>
       </c>
       <c r="E13"/>
       <c r="H13" s="1">
@@ -3609,7 +3672,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" t="s">
-        <v>172</v>
+        <v>178</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>121</v>
@@ -3618,7 +3681,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>173</v>
+        <v>179</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="1">
@@ -3632,13 +3695,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" t="s">
-        <v>174</v>
+        <v>180</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>175</v>
+        <v>181</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="1">
@@ -3652,16 +3715,16 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" t="s">
-        <v>176</v>
+        <v>182</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>177</v>
+        <v>183</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="1">
@@ -3675,16 +3738,16 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" t="s">
-        <v>178</v>
+        <v>184</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C17" t="s">
         <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>179</v>
+        <v>185</v>
       </c>
       <c r="E17"/>
       <c r="H17" s="1">
@@ -3698,13 +3761,13 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" t="s">
-        <v>180</v>
+        <v>186</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>181</v>
+        <v>187</v>
       </c>
       <c r="E18"/>
       <c r="I18" s="1">
@@ -3718,16 +3781,16 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" t="s">
-        <v>182</v>
+        <v>188</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C19" t="s">
         <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>183</v>
+        <v>189</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="1">
@@ -3741,13 +3804,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" t="s">
-        <v>184</v>
+        <v>190</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>185</v>
+        <v>191</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="1">
@@ -3761,13 +3824,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" t="s">
-        <v>186</v>
+        <v>192</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>187</v>
+        <v>193</v>
       </c>
       <c r="E21"/>
       <c r="K21" s="1">
@@ -3781,13 +3844,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" t="s">
-        <v>188</v>
+        <v>194</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>189</v>
+        <v>195</v>
       </c>
       <c r="E22"/>
       <c r="N22" s="1">
@@ -3801,13 +3864,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" t="s">
-        <v>190</v>
+        <v>196</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>191</v>
+        <v>197</v>
       </c>
       <c r="E23"/>
       <c r="K23" s="1">
@@ -3821,13 +3884,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>192</v>
+        <v>198</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>193</v>
+        <v>199</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -3835,35 +3898,35 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>194</v>
+        <v>200</v>
       </c>
       <c r="B25" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>196</v>
+        <v>202</v>
       </c>
       <c r="Q25" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>198</v>
+        <v>204</v>
       </c>
       <c r="B26" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>199</v>
+        <v>205</v>
       </c>
       <c r="Q26" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>201</v>
+        <v>207</v>
       </c>
       <c r="B27" t="s">
         <v>121</v>
@@ -3872,7 +3935,7 @@
         <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>202</v>
+        <v>208</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -3880,13 +3943,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>203</v>
+        <v>209</v>
       </c>
       <c r="B28" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>204</v>
+        <v>210</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3894,13 +3957,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>205</v>
+        <v>211</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>206</v>
+        <v>212</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -3908,16 +3971,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>207</v>
+        <v>213</v>
       </c>
       <c r="B30" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C30" t="s">
         <v>113</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>208</v>
+        <v>214</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3925,13 +3988,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>209</v>
+        <v>215</v>
       </c>
       <c r="B31" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>210</v>
+        <v>216</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -3939,16 +4002,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>211</v>
+        <v>217</v>
       </c>
       <c r="B32" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>212</v>
+        <v>218</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -3956,7 +4019,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>213</v>
+        <v>219</v>
       </c>
       <c r="B33" t="s">
         <v>121</v>
@@ -3965,7 +4028,7 @@
         <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>214</v>
+        <v>220</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -3973,13 +4036,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>215</v>
+        <v>221</v>
       </c>
       <c r="B34" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>216</v>
+        <v>222</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -3987,16 +4050,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>217</v>
+        <v>223</v>
       </c>
       <c r="B35" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C35" t="s">
         <v>106</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>218</v>
+        <v>224</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -4004,16 +4067,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>219</v>
+        <v>225</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>220</v>
+        <v>226</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -4021,7 +4084,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>221</v>
+        <v>227</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -4030,7 +4093,7 @@
         <v>61</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>222</v>
+        <v>228</v>
       </c>
       <c r="F37">
         <v>7</v>
@@ -4038,16 +4101,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>223</v>
+        <v>229</v>
       </c>
       <c r="B38" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>224</v>
+        <v>230</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -4055,33 +4118,33 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>225</v>
+        <v>231</v>
       </c>
       <c r="B39" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C39" t="s">
         <v>110</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>226</v>
+        <v>232</v>
       </c>
       <c r="Q39" t="s">
-        <v>200</v>
+        <v>206</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>227</v>
+        <v>233</v>
       </c>
       <c r="B40" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C40" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>228</v>
+        <v>234</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -4089,7 +4152,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>229</v>
+        <v>235</v>
       </c>
       <c r="B41" t="s">
         <v>121</v>
@@ -4098,7 +4161,7 @@
         <v>106</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>230</v>
+        <v>236</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -4106,13 +4169,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>231</v>
+        <v>237</v>
       </c>
       <c r="B42" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>232</v>
+        <v>238</v>
       </c>
       <c r="F42">
         <v>11</v>
@@ -4120,27 +4183,27 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>233</v>
+        <v>239</v>
       </c>
       <c r="B43" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>234</v>
+        <v>240</v>
       </c>
       <c r="Q43" t="s">
-        <v>197</v>
+        <v>203</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>235</v>
+        <v>241</v>
       </c>
       <c r="B44" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>236</v>
+        <v>242</v>
       </c>
       <c r="H44">
         <v>10</v>
@@ -4148,13 +4211,13 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>237</v>
+        <v>243</v>
       </c>
       <c r="B45" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>238</v>
+        <v>244</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -4250,16 +4313,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>239</v>
+        <v>245</v>
       </c>
       <c r="B2" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>240</v>
+        <v>246</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -4268,16 +4331,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>241</v>
+        <v>247</v>
       </c>
       <c r="B3" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>242</v>
+        <v>248</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -4286,13 +4349,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>243</v>
+        <v>249</v>
       </c>
       <c r="B4" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D4" t="s">
-        <v>244</v>
+        <v>250</v>
       </c>
       <c r="O4">
         <v>3</v>
@@ -4301,16 +4364,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>245</v>
+        <v>251</v>
       </c>
       <c r="B5" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>246</v>
+        <v>252</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -4318,7 +4381,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>247</v>
+        <v>253</v>
       </c>
       <c r="B6" t="s">
         <v>121</v>
@@ -4327,7 +4390,7 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>248</v>
+        <v>254</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -4336,16 +4399,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>249</v>
+        <v>255</v>
       </c>
       <c r="B7" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>250</v>
+        <v>256</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -4354,7 +4417,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>251</v>
+        <v>257</v>
       </c>
       <c r="B8" t="s">
         <v>121</v>
@@ -4363,7 +4426,7 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>252</v>
+        <v>258</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -4371,13 +4434,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>253</v>
+        <v>259</v>
       </c>
       <c r="B9" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D9" t="s">
-        <v>254</v>
+        <v>260</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -4385,13 +4448,13 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>255</v>
+        <v>261</v>
       </c>
       <c r="B10" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D10" t="s">
-        <v>256</v>
+        <v>262</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -4400,13 +4463,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>257</v>
+        <v>263</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>258</v>
+        <v>264</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -4415,7 +4478,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" s="2" t="s">
-        <v>259</v>
+        <v>265</v>
       </c>
       <c r="B12" t="s">
         <v>121</v>
@@ -4424,7 +4487,7 @@
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>260</v>
+        <v>266</v>
       </c>
       <c r="E12"/>
       <c r="I12">
@@ -4438,16 +4501,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>261</v>
+        <v>267</v>
       </c>
       <c r="B13" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>262</v>
+        <v>268</v>
       </c>
       <c r="E13"/>
       <c r="F13">
@@ -4461,16 +4524,16 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>263</v>
+        <v>269</v>
       </c>
       <c r="B14" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>264</v>
+        <v>270</v>
       </c>
       <c r="E14"/>
       <c r="G14">
@@ -4484,13 +4547,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" s="2" t="s">
-        <v>265</v>
+        <v>271</v>
       </c>
       <c r="B15" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D15" t="s">
-        <v>266</v>
+        <v>272</v>
       </c>
       <c r="E15"/>
       <c r="F15">
@@ -4504,14 +4567,14 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" s="2" t="s">
-        <v>267</v>
+        <v>273</v>
       </c>
       <c r="B16" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>268</v>
+        <v>274</v>
       </c>
       <c r="E16"/>
       <c r="L16">
@@ -4525,11 +4588,11 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" s="2" t="s">
-        <v>269</v>
+        <v>275</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>270</v>
+        <v>276</v>
       </c>
       <c r="E17"/>
       <c r="O17">
@@ -4543,16 +4606,16 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" s="2" t="s">
-        <v>271</v>
+        <v>277</v>
       </c>
       <c r="B18" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C18" t="s">
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>272</v>
+        <v>278</v>
       </c>
       <c r="E18"/>
       <c r="F18">
@@ -4566,7 +4629,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>273</v>
+        <v>279</v>
       </c>
       <c r="B19" t="s">
         <v>121</v>
@@ -4575,7 +4638,7 @@
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>274</v>
+        <v>280</v>
       </c>
       <c r="E19"/>
       <c r="K19">
@@ -4589,13 +4652,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" s="2" t="s">
-        <v>275</v>
+        <v>281</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>276</v>
+        <v>282</v>
       </c>
       <c r="E20"/>
       <c r="I20">
@@ -4609,13 +4672,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" s="2" t="s">
-        <v>277</v>
+        <v>283</v>
       </c>
       <c r="B21" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D21" t="s">
-        <v>278</v>
+        <v>284</v>
       </c>
       <c r="E21"/>
       <c r="I21">
@@ -4629,13 +4692,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" s="2" t="s">
-        <v>279</v>
+        <v>285</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>280</v>
+        <v>286</v>
       </c>
       <c r="E22"/>
       <c r="K22">
@@ -4649,13 +4712,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" s="2" t="s">
-        <v>281</v>
+        <v>287</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>282</v>
+        <v>288</v>
       </c>
       <c r="E23"/>
       <c r="H23">
@@ -4669,14 +4732,14 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>283</v>
+        <v>289</v>
       </c>
       <c r="B24" t="s">
         <v>121</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" t="s">
-        <v>284</v>
+        <v>290</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -4684,16 +4747,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>285</v>
+        <v>291</v>
       </c>
       <c r="B25" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>286</v>
+        <v>292</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -4701,13 +4764,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>287</v>
+        <v>293</v>
       </c>
       <c r="B26" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D26" t="s">
-        <v>288</v>
+        <v>294</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -4715,16 +4778,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>289</v>
+        <v>295</v>
       </c>
       <c r="B27" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>290</v>
+        <v>296</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -4732,16 +4795,16 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>291</v>
+        <v>297</v>
       </c>
       <c r="B28" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>292</v>
+        <v>298</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -4749,16 +4812,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>293</v>
+        <v>299</v>
       </c>
       <c r="B29" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>294</v>
+        <v>300</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -4766,13 +4829,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>295</v>
+        <v>301</v>
       </c>
       <c r="B30" t="s">
         <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>296</v>
+        <v>302</v>
       </c>
       <c r="K30">
         <v>2</v>
@@ -4780,13 +4843,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>297</v>
+        <v>303</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>298</v>
+        <v>304</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -4794,16 +4857,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>299</v>
+        <v>305</v>
       </c>
       <c r="B32" t="s">
-        <v>164</v>
+        <v>170</v>
       </c>
       <c r="C32" t="s">
         <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>300</v>
+        <v>306</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -4811,13 +4874,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
-        <v>301</v>
+        <v>307</v>
       </c>
       <c r="B33" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D33" t="s">
-        <v>302</v>
+        <v>308</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -4825,13 +4888,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>303</v>
+        <v>309</v>
       </c>
       <c r="B34" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D34" t="s">
-        <v>304</v>
+        <v>310</v>
       </c>
       <c r="K34">
         <v>3</v>
@@ -4839,16 +4902,16 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>305</v>
+        <v>311</v>
       </c>
       <c r="B35" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>306</v>
+        <v>312</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -4856,13 +4919,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>307</v>
+        <v>313</v>
       </c>
       <c r="B36" t="s">
-        <v>160</v>
+        <v>166</v>
       </c>
       <c r="D36" t="s">
-        <v>308</v>
+        <v>314</v>
       </c>
       <c r="O36">
         <v>2</v>
@@ -4870,7 +4933,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
-        <v>309</v>
+        <v>315</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -4879,7 +4942,7 @@
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>310</v>
+        <v>316</v>
       </c>
       <c r="L37">
         <v>2</v>
@@ -4887,13 +4950,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>311</v>
+        <v>317</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>312</v>
+        <v>318</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -4901,7 +4964,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2" t="s">
-        <v>313</v>
+        <v>319</v>
       </c>
       <c r="B39" t="s">
         <v>121</v>
@@ -4910,7 +4973,7 @@
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>314</v>
+        <v>320</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -4918,7 +4981,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="2" t="s">
-        <v>315</v>
+        <v>321</v>
       </c>
       <c r="B40" t="s">
         <v>121</v>
@@ -4927,7 +4990,7 @@
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>316</v>
+        <v>322</v>
       </c>
       <c r="L40">
         <v>2</v>
@@ -4935,16 +4998,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>317</v>
+        <v>323</v>
       </c>
       <c r="B41" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>318</v>
+        <v>324</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -4952,13 +5015,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2" t="s">
-        <v>319</v>
+        <v>325</v>
       </c>
       <c r="B42" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D42" t="s">
-        <v>320</v>
+        <v>326</v>
       </c>
       <c r="K42">
         <v>2</v>
@@ -4966,13 +5029,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2" t="s">
-        <v>321</v>
+        <v>327</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>322</v>
+        <v>328</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -4980,13 +5043,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>323</v>
+        <v>329</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>324</v>
+        <v>330</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -4994,16 +5057,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
-        <v>325</v>
+        <v>331</v>
       </c>
       <c r="B45" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C45" t="s">
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>326</v>
+        <v>332</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -5011,13 +5074,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>327</v>
+        <v>333</v>
       </c>
       <c r="B46" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D46" t="s">
-        <v>328</v>
+        <v>334</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -5025,13 +5088,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>329</v>
+        <v>335</v>
       </c>
       <c r="B47" t="s">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="D47" t="s">
-        <v>330</v>
+        <v>336</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -5039,10 +5102,10 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="2" t="s">
-        <v>331</v>
+        <v>337</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>332</v>
+        <v>338</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -5050,13 +5113,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>333</v>
+        <v>339</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>334</v>
+        <v>340</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -5064,13 +5127,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>335</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D50" t="s">
-        <v>336</v>
+        <v>342</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -5078,13 +5141,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>337</v>
+        <v>343</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>338</v>
+        <v>344</v>
       </c>
       <c r="L51">
         <v>3</v>
@@ -5092,13 +5155,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>339</v>
+        <v>345</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>340</v>
+        <v>346</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -5106,16 +5169,16 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>341</v>
+        <v>347</v>
       </c>
       <c r="B53" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>342</v>
+        <v>348</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -5123,13 +5186,13 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>343</v>
+        <v>349</v>
       </c>
       <c r="B54" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D54" t="s">
-        <v>344</v>
+        <v>350</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -5137,13 +5200,13 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>345</v>
+        <v>351</v>
       </c>
       <c r="B55" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D55" t="s">
-        <v>346</v>
+        <v>352</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -5151,13 +5214,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>347</v>
+        <v>353</v>
       </c>
       <c r="B56" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D56" t="s">
-        <v>348</v>
+        <v>354</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5165,13 +5228,13 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>349</v>
+        <v>355</v>
       </c>
       <c r="B57" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="D57" t="s">
-        <v>350</v>
+        <v>356</v>
       </c>
       <c r="I57">
         <v>10</v>
@@ -5179,13 +5242,13 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>351</v>
+        <v>357</v>
       </c>
       <c r="B58" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D58" t="s">
-        <v>352</v>
+        <v>358</v>
       </c>
       <c r="I58">
         <v>10</v>
@@ -5193,13 +5256,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>353</v>
+        <v>359</v>
       </c>
       <c r="B59" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D59" t="s">
-        <v>354</v>
+        <v>360</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -5207,16 +5270,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>355</v>
+        <v>361</v>
       </c>
       <c r="B60" t="s">
-        <v>155</v>
+        <v>161</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>356</v>
+        <v>362</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -5224,13 +5287,13 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>357</v>
+        <v>363</v>
       </c>
       <c r="C61" t="s">
         <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>358</v>
+        <v>364</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -5238,7 +5301,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2" t="s">
-        <v>359</v>
+        <v>365</v>
       </c>
       <c r="B62" t="s">
         <v>121</v>
@@ -5247,7 +5310,7 @@
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>360</v>
+        <v>366</v>
       </c>
       <c r="M62">
         <v>2</v>
@@ -5255,13 +5318,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>361</v>
+        <v>367</v>
       </c>
       <c r="B63" t="s">
-        <v>152</v>
+        <v>158</v>
       </c>
       <c r="D63" t="s">
-        <v>362</v>
+        <v>368</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -5269,16 +5332,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>363</v>
+        <v>369</v>
       </c>
       <c r="B64" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>364</v>
+        <v>370</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -5286,13 +5349,13 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>365</v>
+        <v>371</v>
       </c>
       <c r="B65" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D65" t="s">
-        <v>366</v>
+        <v>372</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -5300,13 +5363,13 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="2" t="s">
-        <v>367</v>
+        <v>373</v>
       </c>
       <c r="B66" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D66" t="s">
-        <v>368</v>
+        <v>374</v>
       </c>
       <c r="O66">
         <v>9</v>
@@ -5314,13 +5377,13 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>369</v>
+        <v>375</v>
       </c>
       <c r="B67" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D67" t="s">
-        <v>370</v>
+        <v>376</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -5328,13 +5391,13 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>371</v>
+        <v>377</v>
       </c>
       <c r="B68" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D68" t="s">
-        <v>372</v>
+        <v>378</v>
       </c>
       <c r="I68">
         <v>10</v>
@@ -5342,13 +5405,13 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="2" t="s">
-        <v>373</v>
+        <v>379</v>
       </c>
       <c r="B69" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="D69" t="s">
-        <v>374</v>
+        <v>380</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5356,13 +5419,13 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>375</v>
+        <v>381</v>
       </c>
       <c r="B70" t="s">
-        <v>145</v>
+        <v>151</v>
       </c>
       <c r="D70" t="s">
-        <v>376</v>
+        <v>382</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5370,16 +5433,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>377</v>
+        <v>383</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>195</v>
+        <v>201</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>378</v>
+        <v>384</v>
       </c>
       <c r="F71">
         <v>8</v>
@@ -5475,13 +5538,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>379</v>
+        <v>385</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>380</v>
+        <v>386</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5490,10 +5553,10 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>381</v>
+        <v>387</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>382</v>
+        <v>388</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -5502,13 +5565,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>383</v>
+        <v>389</v>
       </c>
       <c r="C4" t="s">
         <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>384</v>
+        <v>390</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5517,10 +5580,10 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>385</v>
+        <v>391</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>386</v>
+        <v>392</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -5528,10 +5591,10 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>387</v>
+        <v>393</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>388</v>
+        <v>394</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -5540,13 +5603,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>389</v>
+        <v>395</v>
       </c>
       <c r="C7" t="s">
         <v>106</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>390</v>
+        <v>396</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -5555,10 +5618,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>391</v>
+        <v>397</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>392</v>
+        <v>398</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -5566,10 +5629,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
-        <v>393</v>
+        <v>399</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>394</v>
+        <v>400</v>
       </c>
       <c r="K9">
         <v>5</v>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="668" uniqueCount="401">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="409">
   <si>
     <t>名称</t>
   </si>
@@ -459,6 +459,30 @@
   </si>
   <si>
     <t>全体命中-40，回避+40</t>
+  </si>
+  <si>
+    <t>Strike_Rainy_1</t>
+  </si>
+  <si>
+    <t>骤雨1</t>
+  </si>
+  <si>
+    <t>Strike_Rainy_2</t>
+  </si>
+  <si>
+    <t>骤雨2</t>
+  </si>
+  <si>
+    <t>Strike_Rainy_3</t>
+  </si>
+  <si>
+    <t>骤雨3</t>
+  </si>
+  <si>
+    <t>Strike_Rainy_4</t>
+  </si>
+  <si>
+    <t>骤雨4</t>
   </si>
   <si>
     <t>Dish_I_Fire</t>
@@ -1228,10 +1252,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
     <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
   </numFmts>
   <fonts count="22">
     <font>
@@ -1244,13 +1268,6 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1267,32 +1284,15 @@
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
       <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
+      <color rgb="FF3F3F76"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
       <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF0000FF"/>
+      <color rgb="FF006100"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1308,15 +1308,45 @@
     <font>
       <b/>
       <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
       <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
     </font>
     <font>
-      <u/>
+      <b/>
       <sz val="11"/>
-      <color rgb="FF800080"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1346,7 +1376,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF9C6500"/>
+      <color rgb="FF9C0006"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1360,9 +1390,16 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
       <b/>
       <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
+      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1376,22 +1413,9 @@
       <scheme val="minor"/>
     </font>
     <font>
+      <u/>
       <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF3F3F76"/>
+      <color rgb="FF0000FF"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1406,7 +1430,13 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
+        <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1418,43 +1448,31 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
+        <fgColor rgb="FFFFCC99"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
+        <fgColor rgb="FFC6EFCE"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
+        <fgColor rgb="FFA5A5A5"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
+        <fgColor theme="9" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1472,7 +1490,67 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1484,7 +1562,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
+        <fgColor theme="8" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1496,7 +1574,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
+        <fgColor theme="9" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1508,43 +1586,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFC6EFCE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.599993896298105"/>
+        <fgColor theme="9" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1556,37 +1598,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
+        <fgColor theme="5" tint="0.399975585192419"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.399975585192419"/>
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFCC99"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1600,25 +1624,31 @@
       <diagonal/>
     </border>
     <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
+      <left style="thin">
+        <color rgb="FF7F7F7F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF7F7F7F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF7F7F7F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF7F7F7F"/>
       </bottom>
       <diagonal/>
     </border>
     <border>
-      <left style="thin">
+      <left style="double">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="thin">
+      <right style="double">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="thin">
+      <top style="double">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="thin">
+      <bottom style="double">
         <color rgb="FF3F3F3F"/>
       </bottom>
       <diagonal/>
@@ -1650,6 +1680,24 @@
     <border>
       <left/>
       <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
       <top style="thin">
         <color theme="4"/>
       </top>
@@ -1659,189 +1707,165 @@
       <diagonal/>
     </border>
     <border>
-      <left style="double">
+      <left style="thin">
         <color rgb="FF3F3F3F"/>
       </left>
-      <right style="double">
+      <right style="thin">
         <color rgb="FF3F3F3F"/>
       </right>
-      <top style="double">
+      <top style="thin">
         <color rgb="FF3F3F3F"/>
       </top>
-      <bottom style="double">
+      <bottom style="thin">
         <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF7F7F7F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF7F7F7F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF7F7F7F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF7F7F7F"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
       </bottom>
       <diagonal/>
     </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="4" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="21" fillId="32" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="5" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="20" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="17" fillId="22" borderId="6" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="5" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="42" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="12" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
@@ -3005,7 +3029,7 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V18"/>
+  <dimension ref="A1:V22"/>
   <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
@@ -3378,6 +3402,74 @@
       </c>
       <c r="L18">
         <v>40</v>
+      </c>
+    </row>
+    <row r="19" spans="1:12">
+      <c r="A19" t="s">
+        <v>147</v>
+      </c>
+      <c r="D19" t="s">
+        <v>148</v>
+      </c>
+      <c r="H19">
+        <v>-10</v>
+      </c>
+      <c r="K19">
+        <v>-10</v>
+      </c>
+      <c r="L19">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="20" spans="1:11">
+      <c r="A20" t="s">
+        <v>149</v>
+      </c>
+      <c r="C20" t="s">
+        <v>36</v>
+      </c>
+      <c r="D20" t="s">
+        <v>150</v>
+      </c>
+      <c r="H20">
+        <v>10</v>
+      </c>
+      <c r="K20">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="21" spans="1:11">
+      <c r="A21" t="s">
+        <v>151</v>
+      </c>
+      <c r="C21" t="s">
+        <v>41</v>
+      </c>
+      <c r="D21" t="s">
+        <v>152</v>
+      </c>
+      <c r="H21">
+        <v>10</v>
+      </c>
+      <c r="K21">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="22" spans="1:11">
+      <c r="A22" t="s">
+        <v>153</v>
+      </c>
+      <c r="C22" t="s">
+        <v>48</v>
+      </c>
+      <c r="D22" t="s">
+        <v>154</v>
+      </c>
+      <c r="H22">
+        <v>10</v>
+      </c>
+      <c r="K22">
+        <v>10</v>
       </c>
     </row>
   </sheetData>
@@ -3470,13 +3562,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>147</v>
+        <v>155</v>
       </c>
       <c r="B2" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>149</v>
+        <v>157</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -3485,13 +3577,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>150</v>
+        <v>158</v>
       </c>
       <c r="B3" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>152</v>
+        <v>160</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -3500,13 +3592,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>153</v>
+        <v>161</v>
       </c>
       <c r="C4" t="s">
         <v>110</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>154</v>
+        <v>162</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -3515,13 +3607,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>155</v>
+        <v>163</v>
       </c>
       <c r="B5" t="s">
         <v>121</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>156</v>
+        <v>164</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
@@ -3529,16 +3621,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>157</v>
+        <v>165</v>
       </c>
       <c r="B6" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C6" t="s">
         <v>106</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>159</v>
+        <v>167</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -3547,16 +3639,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>160</v>
+        <v>168</v>
       </c>
       <c r="B7" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>162</v>
+        <v>170</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -3565,13 +3657,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>163</v>
+        <v>171</v>
       </c>
       <c r="B8" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>164</v>
+        <v>172</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -3579,30 +3671,30 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>165</v>
+        <v>173</v>
       </c>
       <c r="B9" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>167</v>
+        <v>175</v>
       </c>
       <c r="Q9" t="s">
-        <v>168</v>
+        <v>176</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>169</v>
+        <v>177</v>
       </c>
       <c r="B10" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>171</v>
+        <v>179</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -3611,13 +3703,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>172</v>
+        <v>180</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>173</v>
+        <v>181</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -3626,16 +3718,16 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" t="s">
-        <v>174</v>
+        <v>182</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C12" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>175</v>
+        <v>183</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="1">
@@ -3649,16 +3741,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" t="s">
-        <v>176</v>
+        <v>184</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>177</v>
+        <v>185</v>
       </c>
       <c r="E13"/>
       <c r="H13" s="1">
@@ -3672,7 +3764,7 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" t="s">
-        <v>178</v>
+        <v>186</v>
       </c>
       <c r="B14" s="1" t="s">
         <v>121</v>
@@ -3681,7 +3773,7 @@
         <v>110</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>179</v>
+        <v>187</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="1">
@@ -3695,13 +3787,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" t="s">
-        <v>180</v>
+        <v>188</v>
       </c>
       <c r="C15" s="1" t="s">
         <v>113</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>181</v>
+        <v>189</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="1">
@@ -3715,16 +3807,16 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" t="s">
-        <v>182</v>
+        <v>190</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C16" t="s">
         <v>110</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>183</v>
+        <v>191</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="1">
@@ -3738,16 +3830,16 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" t="s">
-        <v>184</v>
+        <v>192</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C17" t="s">
         <v>106</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>185</v>
+        <v>193</v>
       </c>
       <c r="E17"/>
       <c r="H17" s="1">
@@ -3761,13 +3853,13 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" t="s">
-        <v>186</v>
+        <v>194</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>187</v>
+        <v>195</v>
       </c>
       <c r="E18"/>
       <c r="I18" s="1">
@@ -3781,16 +3873,16 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" t="s">
-        <v>188</v>
+        <v>196</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C19" t="s">
         <v>110</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>189</v>
+        <v>197</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="1">
@@ -3804,13 +3896,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" t="s">
-        <v>190</v>
+        <v>198</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>191</v>
+        <v>199</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="1">
@@ -3824,13 +3916,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" t="s">
-        <v>192</v>
+        <v>200</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>193</v>
+        <v>201</v>
       </c>
       <c r="E21"/>
       <c r="K21" s="1">
@@ -3844,13 +3936,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" t="s">
-        <v>194</v>
+        <v>202</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>195</v>
+        <v>203</v>
       </c>
       <c r="E22"/>
       <c r="N22" s="1">
@@ -3864,13 +3956,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" t="s">
-        <v>196</v>
+        <v>204</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>197</v>
+        <v>205</v>
       </c>
       <c r="E23"/>
       <c r="K23" s="1">
@@ -3884,13 +3976,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>198</v>
+        <v>206</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>199</v>
+        <v>207</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -3898,35 +3990,35 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>200</v>
+        <v>208</v>
       </c>
       <c r="B25" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>202</v>
+        <v>210</v>
       </c>
       <c r="Q25" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>204</v>
+        <v>212</v>
       </c>
       <c r="B26" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>205</v>
+        <v>213</v>
       </c>
       <c r="Q26" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>207</v>
+        <v>215</v>
       </c>
       <c r="B27" t="s">
         <v>121</v>
@@ -3935,7 +4027,7 @@
         <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>208</v>
+        <v>216</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -3943,13 +4035,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>209</v>
+        <v>217</v>
       </c>
       <c r="B28" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>210</v>
+        <v>218</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3957,13 +4049,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>211</v>
+        <v>219</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>212</v>
+        <v>220</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -3971,16 +4063,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>213</v>
+        <v>221</v>
       </c>
       <c r="B30" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C30" t="s">
         <v>113</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>214</v>
+        <v>222</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3988,13 +4080,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>215</v>
+        <v>223</v>
       </c>
       <c r="B31" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>216</v>
+        <v>224</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -4002,16 +4094,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>217</v>
+        <v>225</v>
       </c>
       <c r="B32" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C32" t="s">
         <v>106</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>218</v>
+        <v>226</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -4019,7 +4111,7 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>219</v>
+        <v>227</v>
       </c>
       <c r="B33" t="s">
         <v>121</v>
@@ -4028,7 +4120,7 @@
         <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>220</v>
+        <v>228</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4036,13 +4128,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>221</v>
+        <v>229</v>
       </c>
       <c r="B34" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>222</v>
+        <v>230</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -4050,16 +4142,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>223</v>
+        <v>231</v>
       </c>
       <c r="B35" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C35" t="s">
         <v>106</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>224</v>
+        <v>232</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -4067,16 +4159,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>225</v>
+        <v>233</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C36" t="s">
         <v>106</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>226</v>
+        <v>234</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -4084,7 +4176,7 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>227</v>
+        <v>235</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -4093,7 +4185,7 @@
         <v>61</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>228</v>
+        <v>236</v>
       </c>
       <c r="F37">
         <v>7</v>
@@ -4101,16 +4193,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>229</v>
+        <v>237</v>
       </c>
       <c r="B38" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>230</v>
+        <v>238</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -4118,33 +4210,33 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>231</v>
+        <v>239</v>
       </c>
       <c r="B39" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C39" t="s">
         <v>110</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>232</v>
+        <v>240</v>
       </c>
       <c r="Q39" t="s">
-        <v>206</v>
+        <v>214</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>233</v>
+        <v>241</v>
       </c>
       <c r="B40" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C40" t="s">
         <v>110</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>234</v>
+        <v>242</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -4152,7 +4244,7 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>235</v>
+        <v>243</v>
       </c>
       <c r="B41" t="s">
         <v>121</v>
@@ -4161,7 +4253,7 @@
         <v>106</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>236</v>
+        <v>244</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -4169,13 +4261,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>237</v>
+        <v>245</v>
       </c>
       <c r="B42" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>238</v>
+        <v>246</v>
       </c>
       <c r="F42">
         <v>11</v>
@@ -4183,27 +4275,27 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>239</v>
+        <v>247</v>
       </c>
       <c r="B43" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>240</v>
+        <v>248</v>
       </c>
       <c r="Q43" t="s">
-        <v>203</v>
+        <v>211</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>241</v>
+        <v>249</v>
       </c>
       <c r="B44" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>242</v>
+        <v>250</v>
       </c>
       <c r="H44">
         <v>10</v>
@@ -4211,13 +4303,13 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>243</v>
+        <v>251</v>
       </c>
       <c r="B45" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>244</v>
+        <v>252</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -4313,16 +4405,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>245</v>
+        <v>253</v>
       </c>
       <c r="B2" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>246</v>
+        <v>254</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -4331,16 +4423,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>247</v>
+        <v>255</v>
       </c>
       <c r="B3" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>248</v>
+        <v>256</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -4349,13 +4441,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>249</v>
+        <v>257</v>
       </c>
       <c r="B4" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D4" t="s">
-        <v>250</v>
+        <v>258</v>
       </c>
       <c r="O4">
         <v>3</v>
@@ -4364,16 +4456,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>251</v>
+        <v>259</v>
       </c>
       <c r="B5" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>252</v>
+        <v>260</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -4381,7 +4473,7 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>253</v>
+        <v>261</v>
       </c>
       <c r="B6" t="s">
         <v>121</v>
@@ -4390,7 +4482,7 @@
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>254</v>
+        <v>262</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -4399,16 +4491,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>255</v>
+        <v>263</v>
       </c>
       <c r="B7" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>256</v>
+        <v>264</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -4417,7 +4509,7 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>257</v>
+        <v>265</v>
       </c>
       <c r="B8" t="s">
         <v>121</v>
@@ -4426,7 +4518,7 @@
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>258</v>
+        <v>266</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -4434,13 +4526,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>259</v>
+        <v>267</v>
       </c>
       <c r="B9" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D9" t="s">
-        <v>260</v>
+        <v>268</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -4448,13 +4540,13 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>261</v>
+        <v>269</v>
       </c>
       <c r="B10" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D10" t="s">
-        <v>262</v>
+        <v>270</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -4463,13 +4555,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>263</v>
+        <v>271</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>264</v>
+        <v>272</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -4478,7 +4570,7 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" s="2" t="s">
-        <v>265</v>
+        <v>273</v>
       </c>
       <c r="B12" t="s">
         <v>121</v>
@@ -4487,7 +4579,7 @@
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>266</v>
+        <v>274</v>
       </c>
       <c r="E12"/>
       <c r="I12">
@@ -4501,16 +4593,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>267</v>
+        <v>275</v>
       </c>
       <c r="B13" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>268</v>
+        <v>276</v>
       </c>
       <c r="E13"/>
       <c r="F13">
@@ -4524,16 +4616,16 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>269</v>
+        <v>277</v>
       </c>
       <c r="B14" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>270</v>
+        <v>278</v>
       </c>
       <c r="E14"/>
       <c r="G14">
@@ -4547,13 +4639,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" s="2" t="s">
-        <v>271</v>
+        <v>279</v>
       </c>
       <c r="B15" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D15" t="s">
-        <v>272</v>
+        <v>280</v>
       </c>
       <c r="E15"/>
       <c r="F15">
@@ -4567,14 +4659,14 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" s="2" t="s">
-        <v>273</v>
+        <v>281</v>
       </c>
       <c r="B16" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>274</v>
+        <v>282</v>
       </c>
       <c r="E16"/>
       <c r="L16">
@@ -4588,11 +4680,11 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" s="2" t="s">
-        <v>275</v>
+        <v>283</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>276</v>
+        <v>284</v>
       </c>
       <c r="E17"/>
       <c r="O17">
@@ -4606,16 +4698,16 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" s="2" t="s">
-        <v>277</v>
+        <v>285</v>
       </c>
       <c r="B18" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C18" t="s">
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>278</v>
+        <v>286</v>
       </c>
       <c r="E18"/>
       <c r="F18">
@@ -4629,7 +4721,7 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>279</v>
+        <v>287</v>
       </c>
       <c r="B19" t="s">
         <v>121</v>
@@ -4638,7 +4730,7 @@
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>280</v>
+        <v>288</v>
       </c>
       <c r="E19"/>
       <c r="K19">
@@ -4652,13 +4744,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" s="2" t="s">
-        <v>281</v>
+        <v>289</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>282</v>
+        <v>290</v>
       </c>
       <c r="E20"/>
       <c r="I20">
@@ -4672,13 +4764,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" s="2" t="s">
-        <v>283</v>
+        <v>291</v>
       </c>
       <c r="B21" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D21" t="s">
-        <v>284</v>
+        <v>292</v>
       </c>
       <c r="E21"/>
       <c r="I21">
@@ -4692,13 +4784,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" s="2" t="s">
-        <v>285</v>
+        <v>293</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>286</v>
+        <v>294</v>
       </c>
       <c r="E22"/>
       <c r="K22">
@@ -4712,13 +4804,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" s="2" t="s">
-        <v>287</v>
+        <v>295</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>288</v>
+        <v>296</v>
       </c>
       <c r="E23"/>
       <c r="H23">
@@ -4732,14 +4824,14 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>289</v>
+        <v>297</v>
       </c>
       <c r="B24" t="s">
         <v>121</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" t="s">
-        <v>290</v>
+        <v>298</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -4747,16 +4839,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>291</v>
+        <v>299</v>
       </c>
       <c r="B25" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>292</v>
+        <v>300</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -4764,13 +4856,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>293</v>
+        <v>301</v>
       </c>
       <c r="B26" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D26" t="s">
-        <v>294</v>
+        <v>302</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -4778,16 +4870,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>295</v>
+        <v>303</v>
       </c>
       <c r="B27" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>296</v>
+        <v>304</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -4795,16 +4887,16 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>297</v>
+        <v>305</v>
       </c>
       <c r="B28" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>298</v>
+        <v>306</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -4812,16 +4904,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>299</v>
+        <v>307</v>
       </c>
       <c r="B29" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>300</v>
+        <v>308</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -4829,13 +4921,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>301</v>
+        <v>309</v>
       </c>
       <c r="B30" t="s">
         <v>121</v>
       </c>
       <c r="D30" t="s">
-        <v>302</v>
+        <v>310</v>
       </c>
       <c r="K30">
         <v>2</v>
@@ -4843,13 +4935,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>303</v>
+        <v>311</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>304</v>
+        <v>312</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -4857,16 +4949,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>305</v>
+        <v>313</v>
       </c>
       <c r="B32" t="s">
-        <v>170</v>
+        <v>178</v>
       </c>
       <c r="C32" t="s">
         <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>306</v>
+        <v>314</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -4874,13 +4966,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
-        <v>307</v>
+        <v>315</v>
       </c>
       <c r="B33" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D33" t="s">
-        <v>308</v>
+        <v>316</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -4888,13 +4980,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>309</v>
+        <v>317</v>
       </c>
       <c r="B34" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D34" t="s">
-        <v>310</v>
+        <v>318</v>
       </c>
       <c r="K34">
         <v>3</v>
@@ -4902,16 +4994,16 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>311</v>
+        <v>319</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>312</v>
+        <v>320</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -4919,13 +5011,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>313</v>
+        <v>321</v>
       </c>
       <c r="B36" t="s">
-        <v>166</v>
+        <v>174</v>
       </c>
       <c r="D36" t="s">
-        <v>314</v>
+        <v>322</v>
       </c>
       <c r="O36">
         <v>2</v>
@@ -4933,7 +5025,7 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
-        <v>315</v>
+        <v>323</v>
       </c>
       <c r="B37" t="s">
         <v>121</v>
@@ -4942,7 +5034,7 @@
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>316</v>
+        <v>324</v>
       </c>
       <c r="L37">
         <v>2</v>
@@ -4950,13 +5042,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>317</v>
+        <v>325</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>318</v>
+        <v>326</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -4964,7 +5056,7 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2" t="s">
-        <v>319</v>
+        <v>327</v>
       </c>
       <c r="B39" t="s">
         <v>121</v>
@@ -4973,7 +5065,7 @@
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>320</v>
+        <v>328</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -4981,7 +5073,7 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="2" t="s">
-        <v>321</v>
+        <v>329</v>
       </c>
       <c r="B40" t="s">
         <v>121</v>
@@ -4990,7 +5082,7 @@
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>322</v>
+        <v>330</v>
       </c>
       <c r="L40">
         <v>2</v>
@@ -4998,16 +5090,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>323</v>
+        <v>331</v>
       </c>
       <c r="B41" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>324</v>
+        <v>332</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -5015,13 +5107,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2" t="s">
-        <v>325</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D42" t="s">
-        <v>326</v>
+        <v>334</v>
       </c>
       <c r="K42">
         <v>2</v>
@@ -5029,13 +5121,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2" t="s">
-        <v>327</v>
+        <v>335</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>328</v>
+        <v>336</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -5043,13 +5135,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>329</v>
+        <v>337</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>330</v>
+        <v>338</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -5057,16 +5149,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
-        <v>331</v>
+        <v>339</v>
       </c>
       <c r="B45" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C45" t="s">
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>332</v>
+        <v>340</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -5074,13 +5166,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>333</v>
+        <v>341</v>
       </c>
       <c r="B46" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D46" t="s">
-        <v>334</v>
+        <v>342</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -5088,13 +5180,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>335</v>
+        <v>343</v>
       </c>
       <c r="B47" t="s">
-        <v>148</v>
+        <v>156</v>
       </c>
       <c r="D47" t="s">
-        <v>336</v>
+        <v>344</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -5102,10 +5194,10 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="2" t="s">
-        <v>337</v>
+        <v>345</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>338</v>
+        <v>346</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -5113,13 +5205,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>339</v>
+        <v>347</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>340</v>
+        <v>348</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -5127,13 +5219,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>341</v>
+        <v>349</v>
       </c>
       <c r="B50" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D50" t="s">
-        <v>342</v>
+        <v>350</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -5141,13 +5233,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>343</v>
+        <v>351</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>344</v>
+        <v>352</v>
       </c>
       <c r="L51">
         <v>3</v>
@@ -5155,13 +5247,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>345</v>
+        <v>353</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>346</v>
+        <v>354</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -5169,16 +5261,16 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>347</v>
+        <v>355</v>
       </c>
       <c r="B53" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>348</v>
+        <v>356</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -5186,13 +5278,13 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>349</v>
+        <v>357</v>
       </c>
       <c r="B54" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D54" t="s">
-        <v>350</v>
+        <v>358</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -5200,13 +5292,13 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>351</v>
+        <v>359</v>
       </c>
       <c r="B55" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D55" t="s">
-        <v>352</v>
+        <v>360</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -5214,13 +5306,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>353</v>
+        <v>361</v>
       </c>
       <c r="B56" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D56" t="s">
-        <v>354</v>
+        <v>362</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5228,13 +5320,13 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>355</v>
+        <v>363</v>
       </c>
       <c r="B57" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="D57" t="s">
-        <v>356</v>
+        <v>364</v>
       </c>
       <c r="I57">
         <v>10</v>
@@ -5242,13 +5334,13 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>357</v>
+        <v>365</v>
       </c>
       <c r="B58" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D58" t="s">
-        <v>358</v>
+        <v>366</v>
       </c>
       <c r="I58">
         <v>10</v>
@@ -5256,13 +5348,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>359</v>
+        <v>367</v>
       </c>
       <c r="B59" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D59" t="s">
-        <v>360</v>
+        <v>368</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -5270,16 +5362,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>361</v>
+        <v>369</v>
       </c>
       <c r="B60" t="s">
-        <v>161</v>
+        <v>169</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>362</v>
+        <v>370</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -5287,13 +5379,13 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>363</v>
+        <v>371</v>
       </c>
       <c r="C61" t="s">
         <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>364</v>
+        <v>372</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -5301,7 +5393,7 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2" t="s">
-        <v>365</v>
+        <v>373</v>
       </c>
       <c r="B62" t="s">
         <v>121</v>
@@ -5310,7 +5402,7 @@
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>366</v>
+        <v>374</v>
       </c>
       <c r="M62">
         <v>2</v>
@@ -5318,13 +5410,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>367</v>
+        <v>375</v>
       </c>
       <c r="B63" t="s">
-        <v>158</v>
+        <v>166</v>
       </c>
       <c r="D63" t="s">
-        <v>368</v>
+        <v>376</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -5332,16 +5424,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>369</v>
+        <v>377</v>
       </c>
       <c r="B64" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>370</v>
+        <v>378</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -5349,13 +5441,13 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>371</v>
+        <v>379</v>
       </c>
       <c r="B65" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D65" t="s">
-        <v>372</v>
+        <v>380</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -5363,13 +5455,13 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="2" t="s">
-        <v>373</v>
+        <v>381</v>
       </c>
       <c r="B66" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D66" t="s">
-        <v>374</v>
+        <v>382</v>
       </c>
       <c r="O66">
         <v>9</v>
@@ -5377,13 +5469,13 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>375</v>
+        <v>383</v>
       </c>
       <c r="B67" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D67" t="s">
-        <v>376</v>
+        <v>384</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -5391,13 +5483,13 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>377</v>
+        <v>385</v>
       </c>
       <c r="B68" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D68" t="s">
-        <v>378</v>
+        <v>386</v>
       </c>
       <c r="I68">
         <v>10</v>
@@ -5405,13 +5497,13 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="2" t="s">
-        <v>379</v>
+        <v>387</v>
       </c>
       <c r="B69" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="D69" t="s">
-        <v>380</v>
+        <v>388</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5419,13 +5511,13 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>381</v>
+        <v>389</v>
       </c>
       <c r="B70" t="s">
-        <v>151</v>
+        <v>159</v>
       </c>
       <c r="D70" t="s">
-        <v>382</v>
+        <v>390</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5433,16 +5525,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>383</v>
+        <v>391</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>201</v>
+        <v>209</v>
       </c>
       <c r="C71" s="7" t="s">
         <v>113</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>384</v>
+        <v>392</v>
       </c>
       <c r="F71">
         <v>8</v>
@@ -5538,13 +5630,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>385</v>
+        <v>393</v>
       </c>
       <c r="C2" t="s">
         <v>113</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>386</v>
+        <v>394</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5553,10 +5645,10 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>387</v>
+        <v>395</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>388</v>
+        <v>396</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -5565,13 +5657,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>389</v>
+        <v>397</v>
       </c>
       <c r="C4" t="s">
         <v>106</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>390</v>
+        <v>398</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5580,10 +5672,10 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>391</v>
+        <v>399</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>392</v>
+        <v>400</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -5591,10 +5683,10 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>393</v>
+        <v>401</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>394</v>
+        <v>402</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -5603,13 +5695,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>395</v>
+        <v>403</v>
       </c>
       <c r="C7" t="s">
         <v>106</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>396</v>
+        <v>404</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -5618,10 +5710,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>397</v>
+        <v>405</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>398</v>
+        <v>406</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -5629,10 +5721,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
-        <v>399</v>
+        <v>407</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>400</v>
+        <v>408</v>
       </c>
       <c r="K9">
         <v>5</v>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Volumes/LING-hard/Codes/WSGR/depend/environment/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB69C9F5-7824-EF4C-A9A8-68A65BE12C68}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{2B58EA48-80A0-8C4E-AF3D-13068A96AC18}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-34980" yWindow="-500" windowWidth="29400" windowHeight="18380" activeTab="2" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="740" windowWidth="29400" windowHeight="17160" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="工程局" sheetId="1" r:id="rId1"/>
@@ -24,7 +24,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="642" uniqueCount="384">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="647" uniqueCount="390">
   <si>
     <t>名称</t>
   </si>
@@ -330,12 +330,6 @@
   </si>
   <si>
     <t>导战</t>
-  </si>
-  <si>
-    <t>Engineering_BG</t>
-  </si>
-  <si>
-    <t>BG</t>
   </si>
   <si>
     <t>大巡</t>
@@ -1187,6 +1181,38 @@
   </si>
   <si>
     <t>某新型主炮(C国小型船火力+8)</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineering_CBG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>CBG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>Engineering_BG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>BG</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>防战</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>ShellingPhase:0.05</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>AirPhase:-0.15;ShellingPhase:-0.15</t>
+    <phoneticPr fontId="2" type="noConversion"/>
+  </si>
+  <si>
+    <t>SecondMissilePhase:0.1;NightPhase:0.1</t>
     <phoneticPr fontId="2" type="noConversion"/>
   </si>
 </sst>
@@ -1240,7 +1266,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
@@ -1259,6 +1285,16 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="fill"/>
     </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1471,7 +1507,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:V23"/>
+  <dimension ref="A1:V24"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="15"/>
   <cols>
     <col min="1" max="1" width="17.1640625" customWidth="1"/>
@@ -2255,8 +2291,8 @@
       <c r="P21" s="2">
         <v>0.03</v>
       </c>
-      <c r="Q21" s="4" t="s">
-        <v>50</v>
+      <c r="Q21" s="10" t="s">
+        <v>387</v>
       </c>
       <c r="S21"/>
       <c r="T21"/>
@@ -2306,14 +2342,14 @@
       <c r="V22"/>
     </row>
     <row r="23" spans="1:22" s="2" customFormat="1">
-      <c r="A23" t="s">
+      <c r="A23" s="6" t="s">
+        <v>382</v>
+      </c>
+      <c r="C23" s="8" t="s">
+        <v>383</v>
+      </c>
+      <c r="D23" s="2" t="s">
         <v>102</v>
-      </c>
-      <c r="C23" s="2" t="s">
-        <v>103</v>
-      </c>
-      <c r="D23" s="2" t="s">
-        <v>104</v>
       </c>
       <c r="E23">
         <v>1</v>
@@ -2346,6 +2382,50 @@
       <c r="T23"/>
       <c r="U23"/>
       <c r="V23"/>
+    </row>
+    <row r="24" spans="1:22">
+      <c r="A24" s="6" t="s">
+        <v>384</v>
+      </c>
+      <c r="C24" s="8" t="s">
+        <v>385</v>
+      </c>
+      <c r="D24" s="9" t="s">
+        <v>386</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="2">
+        <v>5</v>
+      </c>
+      <c r="H24" s="2">
+        <v>5</v>
+      </c>
+      <c r="I24" s="2">
+        <v>5</v>
+      </c>
+      <c r="K24" s="2">
+        <v>5</v>
+      </c>
+      <c r="L24" s="2">
+        <v>5</v>
+      </c>
+      <c r="M24" s="2">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>5</v>
+      </c>
+      <c r="P24" s="2">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" s="10" t="s">
+        <v>389</v>
+      </c>
+      <c r="R24" s="8" t="s">
+        <v>388</v>
+      </c>
     </row>
   </sheetData>
   <phoneticPr fontId="2" type="noConversion"/>
@@ -2434,13 +2514,13 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
+        <v>103</v>
+      </c>
+      <c r="C2" t="s">
+        <v>104</v>
+      </c>
+      <c r="D2" t="s">
         <v>105</v>
-      </c>
-      <c r="C2" t="s">
-        <v>106</v>
-      </c>
-      <c r="D2" t="s">
-        <v>107</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -2449,18 +2529,18 @@
         <v>0.3</v>
       </c>
       <c r="Q2" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
+        <v>107</v>
+      </c>
+      <c r="C3" t="s">
+        <v>108</v>
+      </c>
+      <c r="D3" t="s">
         <v>109</v>
-      </c>
-      <c r="C3" t="s">
-        <v>110</v>
-      </c>
-      <c r="D3" t="s">
-        <v>111</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -2469,18 +2549,18 @@
         <v>0.3</v>
       </c>
       <c r="Q3" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
+        <v>110</v>
+      </c>
+      <c r="C4" t="s">
+        <v>111</v>
+      </c>
+      <c r="D4" t="s">
         <v>112</v>
-      </c>
-      <c r="C4" t="s">
-        <v>113</v>
-      </c>
-      <c r="D4" t="s">
-        <v>114</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -2489,57 +2569,57 @@
         <v>0.3</v>
       </c>
       <c r="Q4" t="s">
-        <v>108</v>
+        <v>106</v>
       </c>
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="6" t="s">
+        <v>375</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>376</v>
+      </c>
+      <c r="Q5" s="6" t="s">
         <v>377</v>
-      </c>
-      <c r="D5" s="6" t="s">
-        <v>378</v>
-      </c>
-      <c r="Q5" s="6" t="s">
-        <v>379</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>115</v>
+        <v>113</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="6" t="s">
-        <v>372</v>
+        <v>370</v>
       </c>
       <c r="V6" t="s">
-        <v>116</v>
+        <v>114</v>
       </c>
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
+        <v>115</v>
+      </c>
+      <c r="B7" t="s">
+        <v>116</v>
+      </c>
+      <c r="D7" t="s">
         <v>117</v>
       </c>
-      <c r="B7" t="s">
-        <v>118</v>
-      </c>
-      <c r="D7" t="s">
-        <v>119</v>
-      </c>
-      <c r="S7" s="5" t="b">
+      <c r="S7" s="11" t="b">
         <v>1</v>
       </c>
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="6" t="s">
-        <v>375</v>
+        <v>373</v>
       </c>
       <c r="C8" s="6" t="s">
-        <v>374</v>
+        <v>372</v>
       </c>
       <c r="D8" s="6" t="s">
-        <v>373</v>
+        <v>371</v>
       </c>
       <c r="F8">
         <v>53</v>
@@ -2560,7 +2640,7 @@
         <v>0.53</v>
       </c>
       <c r="Q8" s="6" t="s">
-        <v>376</v>
+        <v>374</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -2658,13 +2738,13 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" t="s">
+        <v>118</v>
+      </c>
+      <c r="B2" t="s">
+        <v>119</v>
+      </c>
+      <c r="D2" s="2" t="s">
         <v>120</v>
-      </c>
-      <c r="B2" t="s">
-        <v>121</v>
-      </c>
-      <c r="D2" s="2" t="s">
-        <v>122</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -2673,13 +2753,13 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" t="s">
+        <v>121</v>
+      </c>
+      <c r="B3" t="s">
+        <v>122</v>
+      </c>
+      <c r="D3" s="2" t="s">
         <v>123</v>
-      </c>
-      <c r="B3" t="s">
-        <v>124</v>
-      </c>
-      <c r="D3" s="2" t="s">
-        <v>125</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -2688,13 +2768,13 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" t="s">
-        <v>126</v>
+        <v>124</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>127</v>
+        <v>125</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -2703,13 +2783,13 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" t="s">
-        <v>128</v>
+        <v>126</v>
       </c>
       <c r="B5" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>129</v>
+        <v>127</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
@@ -2717,16 +2797,16 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
+        <v>128</v>
+      </c>
+      <c r="B6" t="s">
+        <v>129</v>
+      </c>
+      <c r="C6" t="s">
+        <v>104</v>
+      </c>
+      <c r="D6" s="2" t="s">
         <v>130</v>
-      </c>
-      <c r="B6" t="s">
-        <v>131</v>
-      </c>
-      <c r="C6" t="s">
-        <v>106</v>
-      </c>
-      <c r="D6" s="2" t="s">
-        <v>132</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -2735,16 +2815,16 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" t="s">
-        <v>133</v>
+        <v>131</v>
       </c>
       <c r="B7" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>135</v>
+        <v>133</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -2753,13 +2833,13 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" t="s">
-        <v>136</v>
+        <v>134</v>
       </c>
       <c r="B8" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>137</v>
+        <v>135</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -2767,30 +2847,30 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" t="s">
-        <v>138</v>
+        <v>136</v>
       </c>
       <c r="B9" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>140</v>
+        <v>138</v>
       </c>
       <c r="Q9" t="s">
-        <v>141</v>
+        <v>139</v>
       </c>
     </row>
     <row r="10" spans="1:22">
       <c r="A10" t="s">
+        <v>140</v>
+      </c>
+      <c r="B10" t="s">
+        <v>141</v>
+      </c>
+      <c r="D10" s="2" t="s">
         <v>142</v>
-      </c>
-      <c r="B10" t="s">
-        <v>143</v>
-      </c>
-      <c r="D10" s="2" t="s">
-        <v>144</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -2799,13 +2879,13 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" t="s">
-        <v>145</v>
+        <v>143</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="2" t="s">
-        <v>146</v>
+        <v>144</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -2814,16 +2894,16 @@
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1">
       <c r="A12" t="s">
-        <v>147</v>
+        <v>145</v>
       </c>
       <c r="B12" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C12" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D12" s="2" t="s">
-        <v>148</v>
+        <v>146</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="2">
@@ -2837,16 +2917,16 @@
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1">
       <c r="A13" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="B13" s="2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C13" s="2" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="2" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E13"/>
       <c r="H13" s="2">
@@ -2860,16 +2940,16 @@
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1">
       <c r="A14" t="s">
-        <v>151</v>
+        <v>149</v>
       </c>
       <c r="B14" s="2" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D14" s="2" t="s">
-        <v>152</v>
+        <v>150</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="2">
@@ -2883,13 +2963,13 @@
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1">
       <c r="A15" t="s">
-        <v>153</v>
+        <v>151</v>
       </c>
       <c r="C15" s="2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D15" s="2" t="s">
-        <v>154</v>
+        <v>152</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="2">
@@ -2903,16 +2983,16 @@
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1">
       <c r="A16" t="s">
-        <v>155</v>
+        <v>153</v>
       </c>
       <c r="B16" s="2" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D16" s="2" t="s">
-        <v>156</v>
+        <v>154</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="2">
@@ -2926,16 +3006,16 @@
     </row>
     <row r="17" spans="1:22" s="2" customFormat="1">
       <c r="A17" t="s">
-        <v>157</v>
+        <v>155</v>
       </c>
       <c r="B17" s="2" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D17" s="2" t="s">
-        <v>158</v>
+        <v>156</v>
       </c>
       <c r="E17"/>
       <c r="H17" s="2">
@@ -2949,13 +3029,13 @@
     </row>
     <row r="18" spans="1:22" s="2" customFormat="1">
       <c r="A18" t="s">
-        <v>159</v>
+        <v>157</v>
       </c>
       <c r="B18" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D18" s="2" t="s">
-        <v>160</v>
+        <v>158</v>
       </c>
       <c r="E18"/>
       <c r="I18" s="2">
@@ -2969,16 +3049,16 @@
     </row>
     <row r="19" spans="1:22" s="2" customFormat="1">
       <c r="A19" t="s">
-        <v>161</v>
+        <v>159</v>
       </c>
       <c r="B19" s="2" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D19" s="2" t="s">
-        <v>162</v>
+        <v>160</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="2">
@@ -2992,13 +3072,13 @@
     </row>
     <row r="20" spans="1:22" s="2" customFormat="1">
       <c r="A20" t="s">
-        <v>163</v>
+        <v>161</v>
       </c>
       <c r="B20" s="2" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="D20" s="2" t="s">
-        <v>164</v>
+        <v>162</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="2">
@@ -3012,13 +3092,13 @@
     </row>
     <row r="21" spans="1:22" s="2" customFormat="1">
       <c r="A21" t="s">
-        <v>165</v>
+        <v>163</v>
       </c>
       <c r="B21" s="2" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D21" s="2" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="E21"/>
       <c r="K21" s="2">
@@ -3032,13 +3112,13 @@
     </row>
     <row r="22" spans="1:22" s="2" customFormat="1">
       <c r="A22" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="C22" s="2" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="2" t="s">
-        <v>168</v>
+        <v>166</v>
       </c>
       <c r="E22"/>
       <c r="N22" s="2">
@@ -3052,13 +3132,13 @@
     </row>
     <row r="23" spans="1:22" s="2" customFormat="1">
       <c r="A23" t="s">
-        <v>169</v>
+        <v>167</v>
       </c>
       <c r="C23" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="2" t="s">
-        <v>170</v>
+        <v>168</v>
       </c>
       <c r="E23"/>
       <c r="K23" s="2">
@@ -3072,13 +3152,13 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" t="s">
-        <v>171</v>
+        <v>169</v>
       </c>
       <c r="C24" s="2" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="2" t="s">
-        <v>172</v>
+        <v>170</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -3086,44 +3166,44 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" t="s">
+        <v>171</v>
+      </c>
+      <c r="B25" t="s">
+        <v>172</v>
+      </c>
+      <c r="D25" s="2" t="s">
         <v>173</v>
       </c>
-      <c r="B25" t="s">
+      <c r="Q25" t="s">
         <v>174</v>
-      </c>
-      <c r="D25" s="2" t="s">
-        <v>175</v>
-      </c>
-      <c r="Q25" t="s">
-        <v>176</v>
       </c>
     </row>
     <row r="26" spans="1:22">
       <c r="A26" t="s">
+        <v>175</v>
+      </c>
+      <c r="B26" t="s">
+        <v>172</v>
+      </c>
+      <c r="D26" s="2" t="s">
+        <v>176</v>
+      </c>
+      <c r="Q26" t="s">
         <v>177</v>
-      </c>
-      <c r="B26" t="s">
-        <v>174</v>
-      </c>
-      <c r="D26" s="2" t="s">
-        <v>178</v>
-      </c>
-      <c r="Q26" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="27" spans="1:22">
       <c r="A27" t="s">
-        <v>180</v>
+        <v>178</v>
       </c>
       <c r="B27" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>83</v>
       </c>
       <c r="D27" s="2" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -3131,13 +3211,13 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" t="s">
-        <v>182</v>
+        <v>180</v>
       </c>
       <c r="B28" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D28" s="2" t="s">
-        <v>183</v>
+        <v>181</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -3145,13 +3225,13 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" t="s">
-        <v>184</v>
+        <v>182</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D29" s="2" t="s">
-        <v>185</v>
+        <v>183</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -3159,16 +3239,16 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" t="s">
-        <v>186</v>
+        <v>184</v>
       </c>
       <c r="B30" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D30" s="2" t="s">
-        <v>187</v>
+        <v>185</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -3176,13 +3256,13 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" t="s">
-        <v>188</v>
+        <v>186</v>
       </c>
       <c r="B31" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D31" s="2" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -3190,16 +3270,16 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="B32" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D32" s="2" t="s">
-        <v>191</v>
+        <v>189</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -3207,16 +3287,16 @@
     </row>
     <row r="33" spans="1:17">
       <c r="A33" t="s">
-        <v>192</v>
+        <v>190</v>
       </c>
       <c r="B33" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C33" t="s">
         <v>86</v>
       </c>
       <c r="D33" s="2" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -3224,13 +3304,13 @@
     </row>
     <row r="34" spans="1:17">
       <c r="A34" t="s">
-        <v>194</v>
+        <v>192</v>
       </c>
       <c r="B34" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D34" s="2" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -3238,16 +3318,16 @@
     </row>
     <row r="35" spans="1:17">
       <c r="A35" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="B35" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D35" s="2" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -3255,16 +3335,16 @@
     </row>
     <row r="36" spans="1:17">
       <c r="A36" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D36" s="2" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -3272,16 +3352,16 @@
     </row>
     <row r="37" spans="1:17">
       <c r="A37" t="s">
-        <v>200</v>
+        <v>198</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="2" t="s">
-        <v>201</v>
+        <v>199</v>
       </c>
       <c r="F37">
         <v>7</v>
@@ -3289,16 +3369,16 @@
     </row>
     <row r="38" spans="1:17">
       <c r="A38" t="s">
-        <v>202</v>
+        <v>200</v>
       </c>
       <c r="B38" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="2" t="s">
-        <v>203</v>
+        <v>201</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -3306,33 +3386,33 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="B39" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D39" s="4" t="s">
-        <v>205</v>
+        <v>203</v>
       </c>
       <c r="Q39" t="s">
-        <v>179</v>
+        <v>177</v>
       </c>
     </row>
     <row r="40" spans="1:17">
       <c r="A40" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="B40" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>108</v>
       </c>
       <c r="D40" s="2" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -3340,16 +3420,16 @@
     </row>
     <row r="41" spans="1:17">
       <c r="A41" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="B41" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D41" s="2" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -3357,13 +3437,13 @@
     </row>
     <row r="42" spans="1:17">
       <c r="A42" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
       <c r="B42" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D42" s="2" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F42">
         <v>11</v>
@@ -3371,27 +3451,27 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="B43" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D43" s="2" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="Q43" t="s">
-        <v>176</v>
+        <v>174</v>
       </c>
     </row>
     <row r="44" spans="1:17">
       <c r="A44" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
       <c r="B44" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D44" s="2" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
       <c r="H44">
         <v>10</v>
@@ -3399,13 +3479,13 @@
     </row>
     <row r="45" spans="1:17">
       <c r="A45" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="B45" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D45" s="2" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -3500,16 +3580,16 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="3" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
       <c r="B2" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>218</v>
+        <v>216</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -3518,16 +3598,16 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="3" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="B3" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -3536,13 +3616,13 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="3" t="s">
-        <v>297</v>
+        <v>295</v>
       </c>
       <c r="B4" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D4" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="O4">
         <v>3</v>
@@ -3551,16 +3631,16 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="3" t="s">
-        <v>298</v>
+        <v>296</v>
       </c>
       <c r="B5" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -3568,16 +3648,16 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="3" t="s">
-        <v>299</v>
+        <v>297</v>
       </c>
       <c r="B6" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -3586,16 +3666,16 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="3" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -3604,16 +3684,16 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="3" t="s">
-        <v>301</v>
+        <v>299</v>
       </c>
       <c r="B8" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C8" t="s">
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>224</v>
+        <v>222</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -3621,13 +3701,13 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="3" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
       <c r="B9" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D9" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -3635,13 +3715,13 @@
     </row>
     <row r="10" spans="1:22">
       <c r="A10" s="3" t="s">
-        <v>303</v>
+        <v>301</v>
       </c>
       <c r="B10" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D10" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -3650,13 +3730,13 @@
     </row>
     <row r="11" spans="1:22">
       <c r="A11" s="3" t="s">
-        <v>304</v>
+        <v>302</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -3665,16 +3745,16 @@
     </row>
     <row r="12" spans="1:22" s="2" customFormat="1">
       <c r="A12" s="3" t="s">
-        <v>305</v>
+        <v>303</v>
       </c>
       <c r="B12" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="E12"/>
       <c r="I12">
@@ -3688,16 +3768,16 @@
     </row>
     <row r="13" spans="1:22" s="2" customFormat="1">
       <c r="A13" s="3" t="s">
-        <v>306</v>
+        <v>304</v>
       </c>
       <c r="B13" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="E13"/>
       <c r="F13">
@@ -3711,16 +3791,16 @@
     </row>
     <row r="14" spans="1:22" s="2" customFormat="1">
       <c r="A14" s="3" t="s">
-        <v>307</v>
+        <v>305</v>
       </c>
       <c r="B14" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
       <c r="E14"/>
       <c r="G14">
@@ -3734,13 +3814,13 @@
     </row>
     <row r="15" spans="1:22" s="2" customFormat="1">
       <c r="A15" s="3" t="s">
-        <v>308</v>
+        <v>306</v>
       </c>
       <c r="B15" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D15" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E15"/>
       <c r="F15">
@@ -3754,14 +3834,14 @@
     </row>
     <row r="16" spans="1:22" s="2" customFormat="1">
       <c r="A16" s="3" t="s">
-        <v>309</v>
+        <v>307</v>
       </c>
       <c r="B16" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E16"/>
       <c r="L16">
@@ -3775,11 +3855,11 @@
     </row>
     <row r="17" spans="1:22" s="2" customFormat="1">
       <c r="A17" s="3" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E17"/>
       <c r="O17">
@@ -3793,16 +3873,16 @@
     </row>
     <row r="18" spans="1:22" s="2" customFormat="1">
       <c r="A18" s="3" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="B18" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C18" t="s">
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E18"/>
       <c r="F18">
@@ -3816,16 +3896,16 @@
     </row>
     <row r="19" spans="1:22" s="2" customFormat="1">
       <c r="A19" s="3" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="B19" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C19" t="s">
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E19"/>
       <c r="K19">
@@ -3839,13 +3919,13 @@
     </row>
     <row r="20" spans="1:22" s="2" customFormat="1">
       <c r="A20" s="3" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E20"/>
       <c r="I20">
@@ -3859,13 +3939,13 @@
     </row>
     <row r="21" spans="1:22" s="2" customFormat="1">
       <c r="A21" s="3" t="s">
-        <v>314</v>
+        <v>312</v>
       </c>
       <c r="B21" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D21" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E21"/>
       <c r="I21">
@@ -3879,13 +3959,13 @@
     </row>
     <row r="22" spans="1:22" s="2" customFormat="1">
       <c r="A22" s="3" t="s">
-        <v>315</v>
+        <v>313</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="E22"/>
       <c r="K22">
@@ -3899,13 +3979,13 @@
     </row>
     <row r="23" spans="1:22" s="2" customFormat="1">
       <c r="A23" s="3" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
       <c r="E23"/>
       <c r="H23">
@@ -3919,14 +3999,14 @@
     </row>
     <row r="24" spans="1:22">
       <c r="A24" s="3" t="s">
-        <v>317</v>
+        <v>315</v>
       </c>
       <c r="B24" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C24" s="2"/>
       <c r="D24" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -3934,16 +4014,16 @@
     </row>
     <row r="25" spans="1:22">
       <c r="A25" s="3" t="s">
-        <v>318</v>
+        <v>316</v>
       </c>
       <c r="B25" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -3951,13 +4031,13 @@
     </row>
     <row r="26" spans="1:22">
       <c r="A26" s="3" t="s">
-        <v>319</v>
+        <v>317</v>
       </c>
       <c r="B26" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D26" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -3965,16 +4045,16 @@
     </row>
     <row r="27" spans="1:22">
       <c r="A27" s="3" t="s">
-        <v>320</v>
+        <v>318</v>
       </c>
       <c r="B27" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C27" s="2" t="s">
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -3982,16 +4062,16 @@
     </row>
     <row r="28" spans="1:22">
       <c r="A28" s="3" t="s">
-        <v>321</v>
+        <v>319</v>
       </c>
       <c r="B28" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -3999,16 +4079,16 @@
     </row>
     <row r="29" spans="1:22">
       <c r="A29" s="3" t="s">
-        <v>322</v>
+        <v>320</v>
       </c>
       <c r="B29" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -4016,13 +4096,13 @@
     </row>
     <row r="30" spans="1:22">
       <c r="A30" s="3" t="s">
-        <v>323</v>
+        <v>321</v>
       </c>
       <c r="B30" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="D30" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="K30">
         <v>2</v>
@@ -4030,13 +4110,13 @@
     </row>
     <row r="31" spans="1:22">
       <c r="A31" s="3" t="s">
-        <v>324</v>
+        <v>322</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -4044,16 +4124,16 @@
     </row>
     <row r="32" spans="1:22">
       <c r="A32" s="3" t="s">
-        <v>325</v>
+        <v>323</v>
       </c>
       <c r="B32" t="s">
-        <v>143</v>
+        <v>141</v>
       </c>
       <c r="C32" t="s">
         <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -4061,13 +4141,13 @@
     </row>
     <row r="33" spans="1:15">
       <c r="A33" s="3" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
       <c r="B33" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D33" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -4075,13 +4155,13 @@
     </row>
     <row r="34" spans="1:15">
       <c r="A34" s="3" t="s">
-        <v>327</v>
+        <v>325</v>
       </c>
       <c r="B34" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D34" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="K34">
         <v>3</v>
@@ -4089,16 +4169,16 @@
     </row>
     <row r="35" spans="1:15">
       <c r="A35" s="3" t="s">
-        <v>328</v>
+        <v>326</v>
       </c>
       <c r="B35" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -4106,13 +4186,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="3" t="s">
-        <v>329</v>
+        <v>327</v>
       </c>
       <c r="B36" t="s">
-        <v>139</v>
+        <v>137</v>
       </c>
       <c r="D36" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="O36">
         <v>2</v>
@@ -4120,16 +4200,16 @@
     </row>
     <row r="37" spans="1:15">
       <c r="A37" s="3" t="s">
-        <v>330</v>
+        <v>328</v>
       </c>
       <c r="B37" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="L37">
         <v>2</v>
@@ -4137,13 +4217,13 @@
     </row>
     <row r="38" spans="1:15">
       <c r="A38" s="3" t="s">
-        <v>331</v>
+        <v>329</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -4151,16 +4231,16 @@
     </row>
     <row r="39" spans="1:15">
       <c r="A39" s="3" t="s">
-        <v>332</v>
+        <v>330</v>
       </c>
       <c r="B39" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C39" t="s">
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -4168,16 +4248,16 @@
     </row>
     <row r="40" spans="1:15">
       <c r="A40" s="3" t="s">
-        <v>333</v>
+        <v>331</v>
       </c>
       <c r="B40" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C40" t="s">
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="L40">
         <v>2</v>
@@ -4185,16 +4265,16 @@
     </row>
     <row r="41" spans="1:15">
       <c r="A41" s="3" t="s">
-        <v>334</v>
+        <v>332</v>
       </c>
       <c r="B41" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -4202,13 +4282,13 @@
     </row>
     <row r="42" spans="1:15">
       <c r="A42" s="3" t="s">
-        <v>335</v>
+        <v>333</v>
       </c>
       <c r="B42" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D42" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="K42">
         <v>2</v>
@@ -4216,13 +4296,13 @@
     </row>
     <row r="43" spans="1:15">
       <c r="A43" s="3" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -4230,13 +4310,13 @@
     </row>
     <row r="44" spans="1:15">
       <c r="A44" s="3" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -4244,16 +4324,16 @@
     </row>
     <row r="45" spans="1:15">
       <c r="A45" s="3" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="B45" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C45" t="s">
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -4261,13 +4341,13 @@
     </row>
     <row r="46" spans="1:15">
       <c r="A46" s="3" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="B46" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D46" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -4275,13 +4355,13 @@
     </row>
     <row r="47" spans="1:15">
       <c r="A47" s="3" t="s">
-        <v>340</v>
+        <v>338</v>
       </c>
       <c r="B47" t="s">
-        <v>121</v>
+        <v>119</v>
       </c>
       <c r="D47" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -4289,10 +4369,10 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="3" t="s">
-        <v>341</v>
+        <v>339</v>
       </c>
       <c r="D48" s="3" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -4300,13 +4380,13 @@
     </row>
     <row r="49" spans="1:13">
       <c r="A49" s="3" t="s">
-        <v>342</v>
+        <v>340</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>265</v>
+        <v>263</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -4314,13 +4394,13 @@
     </row>
     <row r="50" spans="1:13">
       <c r="A50" s="3" t="s">
-        <v>343</v>
+        <v>341</v>
       </c>
       <c r="B50" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D50" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -4328,13 +4408,13 @@
     </row>
     <row r="51" spans="1:13">
       <c r="A51" s="3" t="s">
-        <v>344</v>
+        <v>342</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="L51">
         <v>3</v>
@@ -4342,13 +4422,13 @@
     </row>
     <row r="52" spans="1:13">
       <c r="A52" s="3" t="s">
-        <v>345</v>
+        <v>343</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -4356,16 +4436,16 @@
     </row>
     <row r="53" spans="1:13">
       <c r="A53" s="3" t="s">
-        <v>346</v>
+        <v>344</v>
       </c>
       <c r="B53" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -4373,13 +4453,13 @@
     </row>
     <row r="54" spans="1:13">
       <c r="A54" s="3" t="s">
-        <v>347</v>
+        <v>345</v>
       </c>
       <c r="B54" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D54" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -4387,13 +4467,13 @@
     </row>
     <row r="55" spans="1:13">
       <c r="A55" s="3" t="s">
-        <v>348</v>
+        <v>346</v>
       </c>
       <c r="B55" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D55" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -4401,13 +4481,13 @@
     </row>
     <row r="56" spans="1:13">
       <c r="A56" s="3" t="s">
-        <v>349</v>
+        <v>347</v>
       </c>
       <c r="B56" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D56" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -4415,13 +4495,13 @@
     </row>
     <row r="57" spans="1:13">
       <c r="A57" s="3" t="s">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="B57" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="D57" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
       <c r="I57">
         <v>10</v>
@@ -4429,13 +4509,13 @@
     </row>
     <row r="58" spans="1:13">
       <c r="A58" s="3" t="s">
-        <v>351</v>
+        <v>349</v>
       </c>
       <c r="B58" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D58" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="I58">
         <v>10</v>
@@ -4443,13 +4523,13 @@
     </row>
     <row r="59" spans="1:13">
       <c r="A59" s="3" t="s">
-        <v>352</v>
+        <v>350</v>
       </c>
       <c r="B59" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D59" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -4457,16 +4537,16 @@
     </row>
     <row r="60" spans="1:13">
       <c r="A60" s="3" t="s">
-        <v>353</v>
+        <v>351</v>
       </c>
       <c r="B60" t="s">
-        <v>134</v>
+        <v>132</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -4474,13 +4554,13 @@
     </row>
     <row r="61" spans="1:13">
       <c r="A61" s="3" t="s">
-        <v>354</v>
+        <v>352</v>
       </c>
       <c r="C61" t="s">
         <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -4488,16 +4568,16 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="3" t="s">
-        <v>355</v>
+        <v>353</v>
       </c>
       <c r="B62" t="s">
-        <v>118</v>
+        <v>116</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="M62">
         <v>2</v>
@@ -4505,13 +4585,13 @@
     </row>
     <row r="63" spans="1:13">
       <c r="A63" s="3" t="s">
-        <v>356</v>
+        <v>354</v>
       </c>
       <c r="B63" t="s">
-        <v>131</v>
+        <v>129</v>
       </c>
       <c r="D63" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -4519,16 +4599,16 @@
     </row>
     <row r="64" spans="1:13">
       <c r="A64" s="3" t="s">
-        <v>357</v>
+        <v>355</v>
       </c>
       <c r="B64" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -4536,13 +4616,13 @@
     </row>
     <row r="65" spans="1:15">
       <c r="A65" s="3" t="s">
-        <v>358</v>
+        <v>356</v>
       </c>
       <c r="B65" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D65" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -4550,13 +4630,13 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="3" t="s">
-        <v>359</v>
+        <v>357</v>
       </c>
       <c r="B66" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D66" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
       <c r="O66">
         <v>9</v>
@@ -4564,13 +4644,13 @@
     </row>
     <row r="67" spans="1:15">
       <c r="A67" s="3" t="s">
-        <v>360</v>
+        <v>358</v>
       </c>
       <c r="B67" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D67" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -4578,13 +4658,13 @@
     </row>
     <row r="68" spans="1:15">
       <c r="A68" s="3" t="s">
-        <v>361</v>
+        <v>359</v>
       </c>
       <c r="B68" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D68" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="I68">
         <v>10</v>
@@ -4592,13 +4672,13 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="3" t="s">
-        <v>362</v>
+        <v>360</v>
       </c>
       <c r="B69" t="s">
-        <v>174</v>
+        <v>172</v>
       </c>
       <c r="D69" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -4606,13 +4686,13 @@
     </row>
     <row r="70" spans="1:15">
       <c r="A70" s="3" t="s">
-        <v>363</v>
+        <v>361</v>
       </c>
       <c r="B70" t="s">
-        <v>124</v>
+        <v>122</v>
       </c>
       <c r="D70" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -4620,16 +4700,16 @@
     </row>
     <row r="71" spans="1:15">
       <c r="A71" s="7" t="s">
+        <v>378</v>
+      </c>
+      <c r="B71" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="C71" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="B71" s="6" t="s">
+      <c r="D71" s="7" t="s">
         <v>381</v>
-      </c>
-      <c r="C71" s="6" t="s">
-        <v>382</v>
-      </c>
-      <c r="D71" s="7" t="s">
-        <v>383</v>
       </c>
       <c r="F71">
         <v>8</v>
@@ -4724,13 +4804,13 @@
     </row>
     <row r="2" spans="1:22">
       <c r="A2" s="3" t="s">
-        <v>364</v>
+        <v>362</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>111</v>
       </c>
       <c r="D2" s="2" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -4739,10 +4819,10 @@
     </row>
     <row r="3" spans="1:22">
       <c r="A3" s="3" t="s">
-        <v>365</v>
+        <v>363</v>
       </c>
       <c r="D3" s="2" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -4751,13 +4831,13 @@
     </row>
     <row r="4" spans="1:22">
       <c r="A4" s="3" t="s">
-        <v>366</v>
+        <v>364</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D4" s="2" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -4766,10 +4846,10 @@
     </row>
     <row r="5" spans="1:22">
       <c r="A5" s="3" t="s">
-        <v>367</v>
+        <v>365</v>
       </c>
       <c r="D5" s="2" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -4777,10 +4857,10 @@
     </row>
     <row r="6" spans="1:22">
       <c r="A6" s="3" t="s">
-        <v>368</v>
+        <v>366</v>
       </c>
       <c r="D6" s="2" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -4789,13 +4869,13 @@
     </row>
     <row r="7" spans="1:22">
       <c r="A7" s="3" t="s">
-        <v>369</v>
+        <v>367</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>104</v>
       </c>
       <c r="D7" s="2" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -4804,10 +4884,10 @@
     </row>
     <row r="8" spans="1:22">
       <c r="A8" s="3" t="s">
-        <v>370</v>
+        <v>368</v>
       </c>
       <c r="D8" s="2" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -4815,10 +4895,10 @@
     </row>
     <row r="9" spans="1:22">
       <c r="A9" s="3" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="D9" s="2" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="K9">
         <v>5</v>

--- a/depend/environment/environment.xlsx
+++ b/depend/environment/environment.xlsx
@@ -4,7 +4,7 @@
   <fileVersion appName="xl" lastEdited="3" lowestEdited="5" rupBuild="9302"/>
   <workbookPr/>
   <bookViews>
-    <workbookView windowWidth="19095" windowHeight="7470" activeTab="1"/>
+    <workbookView windowWidth="18615" windowHeight="7455"/>
   </bookViews>
   <sheets>
     <sheet name="工程局" sheetId="1" r:id="rId1"/>
@@ -18,7 +18,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="679" uniqueCount="409">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="684" uniqueCount="413">
   <si>
     <t>名称</t>
   </si>
@@ -326,13 +326,25 @@
     <t>导战</t>
   </si>
   <si>
+    <t>Engineering_CBG</t>
+  </si>
+  <si>
+    <t>BG</t>
+  </si>
+  <si>
+    <t>大巡</t>
+  </si>
+  <si>
     <t>Engineering_BG</t>
   </si>
   <si>
-    <t>BG</t>
-  </si>
-  <si>
-    <t>大巡</t>
+    <t>防战</t>
+  </si>
+  <si>
+    <t>SecondMissilePhase:0.1;NightPhase:0.1</t>
+  </si>
+  <si>
+    <t>AirPhase:-0.15;ShellingPhase:-0.15</t>
   </si>
   <si>
     <t>Event_Large</t>
@@ -1252,12 +1264,12 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <numFmts count="4">
+    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
+    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
+    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
     <numFmt numFmtId="44" formatCode="_ &quot;￥&quot;* #,##0.00_ ;_ &quot;￥&quot;* \-#,##0.00_ ;_ &quot;￥&quot;* &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="43" formatCode="_ * #,##0.00_ ;_ * \-#,##0.00_ ;_ * &quot;-&quot;??_ ;_ @_ "/>
-    <numFmt numFmtId="42" formatCode="_ &quot;￥&quot;* #,##0_ ;_ &quot;￥&quot;* \-#,##0_ ;_ &quot;￥&quot;* &quot;-&quot;_ ;_ @_ "/>
-    <numFmt numFmtId="41" formatCode="_ * #,##0_ ;_ * \-#,##0_ ;_ * &quot;-&quot;_ ;_ @_ "/>
   </numFmts>
-  <fonts count="22">
+  <fonts count="23">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1268,6 +1280,36 @@
       <sz val="11"/>
       <name val="等线"/>
       <charset val="134"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="等线"/>
+      <charset val="134"/>
+    </font>
+    <font>
+      <i/>
+      <sz val="11"/>
+      <color rgb="FF7F7F7F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
     </font>
     <font>
       <sz val="11"/>
@@ -1285,91 +1327,7 @@
     </font>
     <font>
       <sz val="11"/>
-      <color rgb="FF3F3F76"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF006100"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="18"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FFFFFFFF"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="11"/>
-      <color rgb="FF800080"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
       <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="13"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="3"/>
-      <name val="Calibri"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFA7D00"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <i/>
-      <sz val="11"/>
-      <color rgb="FF7F7F7F"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="15"/>
-      <color theme="3"/>
       <name val="Calibri"/>
       <charset val="134"/>
       <scheme val="minor"/>
@@ -1377,29 +1335,6 @@
     <font>
       <sz val="11"/>
       <color rgb="FF9C0006"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color theme="1"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF9C6500"/>
-      <name val="Calibri"/>
-      <charset val="0"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF3F3F3F"/>
       <name val="Calibri"/>
       <charset val="0"/>
       <scheme val="minor"/>
@@ -1420,6 +1355,89 @@
       <charset val="0"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FF3F3F3F"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="18"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF9C6500"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFA7D00"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <u/>
+      <sz val="11"/>
+      <color rgb="FF800080"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FFFF0000"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color rgb="FFFFFFFF"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF3F3F76"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="15"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF006100"/>
+      <name val="Calibri"/>
+      <charset val="0"/>
+      <scheme val="minor"/>
+    </font>
+    <font>
+      <b/>
+      <sz val="13"/>
+      <color theme="3"/>
+      <name val="Calibri"/>
+      <charset val="134"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="33">
     <fill>
@@ -1430,7 +1448,73 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="9" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFC7CE"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor theme="4" tint="0.599993896298105"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="8" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.799981688894314"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFF2F2F2"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1442,7 +1526,43 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9"/>
+        <fgColor rgb="FFFFFFCC"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFFEB9C"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="6" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="0.599993896298105"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1454,7 +1574,37 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
+        <fgColor theme="5" tint="0.399975585192419"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFA5A5A5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
         <fgColor rgb="FFFFCC99"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="4" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1466,151 +1616,19 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFA5A5A5"/>
+        <fgColor theme="6"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFFCC"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.799981688894314"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFC7CE"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFEB9C"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFF2F2F2"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="8" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5"/>
+        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
     <fill>
       <patternFill patternType="solid">
         <fgColor theme="9" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="9" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="4" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="5" tint="0.399975585192419"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="6" tint="0.599993896298105"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor theme="7" tint="0.799981688894314"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1621,6 +1639,26 @@
       <right/>
       <top/>
       <bottom/>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top style="thin">
+        <color theme="4"/>
+      </top>
+      <bottom style="double">
+        <color theme="4"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="medium">
+        <color theme="4" tint="0.499984740745262"/>
+      </bottom>
       <diagonal/>
     </border>
     <border>
@@ -1635,6 +1673,45 @@
       </top>
       <bottom style="thin">
         <color rgb="FF7F7F7F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FF3F3F3F"/>
+      </left>
+      <right style="thin">
+        <color rgb="FF3F3F3F"/>
+      </right>
+      <top style="thin">
+        <color rgb="FF3F3F3F"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FF3F3F3F"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFB2B2B2"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFB2B2B2"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFB2B2B2"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFB2B2B2"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left/>
+      <right/>
+      <top/>
+      <bottom style="double">
+        <color rgb="FFFF8001"/>
       </bottom>
       <diagonal/>
     </border>
@@ -1662,214 +1739,155 @@
       </bottom>
       <diagonal/>
     </border>
-    <border>
-      <left style="thin">
-        <color rgb="FFB2B2B2"/>
-      </left>
-      <right style="thin">
-        <color rgb="FFB2B2B2"/>
-      </right>
-      <top style="thin">
-        <color rgb="FFB2B2B2"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FFB2B2B2"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="medium">
-        <color theme="4" tint="0.499984740745262"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top/>
-      <bottom style="double">
-        <color rgb="FFFF8001"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left/>
-      <right/>
-      <top style="thin">
-        <color theme="4"/>
-      </top>
-      <bottom style="double">
-        <color theme="4"/>
-      </bottom>
-      <diagonal/>
-    </border>
-    <border>
-      <left style="thin">
-        <color rgb="FF3F3F3F"/>
-      </left>
-      <right style="thin">
-        <color rgb="FF3F3F3F"/>
-      </right>
-      <top style="thin">
-        <color rgb="FF3F3F3F"/>
-      </top>
-      <bottom style="thin">
-        <color rgb="FF3F3F3F"/>
-      </bottom>
-      <diagonal/>
-    </border>
   </borders>
   <cellStyleXfs count="49">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="3" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="32" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="15" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="26" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="4" fillId="6" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="19" fillId="27" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="31" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="8" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="44" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="44" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="27" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="9" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="9" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="30" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="25" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="24" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="18" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="23" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="20" fillId="21" borderId="1" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="10" fillId="12" borderId="3" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="18" fillId="20" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="14" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="21" fillId="29" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="10" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="17" fillId="0" borderId="7" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="4" fillId="0" borderId="1" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="16" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="9" fillId="7" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="8" borderId="2" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="18" fillId="25" borderId="7" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="19" fillId="21" borderId="8" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="12" fillId="12" borderId="4" applyNumberFormat="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="15" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="20" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="42" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="21" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="16" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="13" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="13" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="22" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="17" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="19" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="8" fillId="15" borderId="5" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="6" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="7" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="3" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="42" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="41" fontId="8" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="11" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="22" fillId="0" borderId="8" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="43" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="7" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="5" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="6" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="14" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="17" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="12" borderId="4" applyNumberFormat="0" applyFont="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="9" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="14" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="28" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="21" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="41" fontId="9" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="3" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="16" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="0" borderId="5" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="4" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0">
-      <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
+    <xf numFmtId="0" fontId="15" fillId="0" borderId="6" applyNumberFormat="0" applyFill="0" applyAlignment="0" applyProtection="0">
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="12">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1888,6 +1906,16 @@
       <alignment horizontal="fill"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+      <alignment horizontal="fill" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -1954,7 +1982,7 @@
   <a:themeElements>
     <a:clrScheme name="Office">
       <a:dk1>
-        <a:sysClr val="windowText" lastClr="000000"/>
+        <a:sysClr val="windowText" lastClr="4C4C4C"/>
       </a:dk1>
       <a:lt1>
         <a:sysClr val="window" lastClr="FFFFFF"/>
@@ -2144,8 +2172,8 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:V23"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
+  <dimension ref="A1:V24"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
@@ -3020,6 +3048,50 @@
       <c r="U23"/>
       <c r="V23"/>
     </row>
+    <row r="24" spans="1:18">
+      <c r="A24" s="8" t="s">
+        <v>105</v>
+      </c>
+      <c r="C24" s="9" t="s">
+        <v>103</v>
+      </c>
+      <c r="D24" s="10" t="s">
+        <v>106</v>
+      </c>
+      <c r="E24">
+        <v>1</v>
+      </c>
+      <c r="F24" s="1">
+        <v>5</v>
+      </c>
+      <c r="H24" s="1">
+        <v>5</v>
+      </c>
+      <c r="I24" s="1">
+        <v>5</v>
+      </c>
+      <c r="K24" s="1">
+        <v>5</v>
+      </c>
+      <c r="L24" s="1">
+        <v>5</v>
+      </c>
+      <c r="M24" s="1">
+        <v>5</v>
+      </c>
+      <c r="O24">
+        <v>5</v>
+      </c>
+      <c r="P24" s="1">
+        <v>0.05</v>
+      </c>
+      <c r="Q24" s="11" t="s">
+        <v>107</v>
+      </c>
+      <c r="R24" s="9" t="s">
+        <v>108</v>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <headerFooter/>
@@ -3030,7 +3102,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V22"/>
-  <sheetFormatPr defaultColWidth="11" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="11" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
@@ -3108,13 +3180,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>105</v>
+        <v>109</v>
       </c>
       <c r="C2" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D2" t="s">
-        <v>107</v>
+        <v>111</v>
       </c>
       <c r="F2">
         <v>15</v>
@@ -3123,18 +3195,18 @@
         <v>0.3</v>
       </c>
       <c r="Q2" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>109</v>
+        <v>113</v>
       </c>
       <c r="C3" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D3" t="s">
-        <v>111</v>
+        <v>115</v>
       </c>
       <c r="F3">
         <v>20</v>
@@ -3143,18 +3215,18 @@
         <v>0.3</v>
       </c>
       <c r="Q3" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>112</v>
+        <v>116</v>
       </c>
       <c r="C4" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D4" t="s">
-        <v>114</v>
+        <v>118</v>
       </c>
       <c r="F4">
         <v>25</v>
@@ -3163,43 +3235,43 @@
         <v>0.3</v>
       </c>
       <c r="Q4" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="5" spans="1:17">
       <c r="A5" s="7" t="s">
-        <v>115</v>
+        <v>119</v>
       </c>
       <c r="D5" s="7" t="s">
-        <v>116</v>
+        <v>120</v>
       </c>
       <c r="Q5" s="7" t="s">
-        <v>108</v>
+        <v>112</v>
       </c>
     </row>
     <row r="6" spans="1:22">
       <c r="A6" t="s">
-        <v>117</v>
+        <v>121</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" s="7" t="s">
-        <v>118</v>
+        <v>122</v>
       </c>
       <c r="V6" t="s">
-        <v>119</v>
+        <v>123</v>
       </c>
     </row>
     <row r="7" spans="1:19">
       <c r="A7" t="s">
-        <v>120</v>
+        <v>124</v>
       </c>
       <c r="B7" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D7" t="s">
-        <v>122</v>
+        <v>126</v>
       </c>
       <c r="S7" s="4" t="b">
         <v>1</v>
@@ -3207,13 +3279,13 @@
     </row>
     <row r="8" spans="1:20">
       <c r="A8" s="7" t="s">
-        <v>123</v>
+        <v>127</v>
       </c>
       <c r="C8" s="7" t="s">
-        <v>124</v>
+        <v>128</v>
       </c>
       <c r="D8" s="7" t="s">
-        <v>125</v>
+        <v>129</v>
       </c>
       <c r="F8">
         <v>53</v>
@@ -3234,7 +3306,7 @@
         <v>0.53</v>
       </c>
       <c r="Q8" s="7" t="s">
-        <v>126</v>
+        <v>130</v>
       </c>
       <c r="S8" t="b">
         <v>1</v>
@@ -3245,10 +3317,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" t="s">
-        <v>127</v>
+        <v>131</v>
       </c>
       <c r="D9" t="s">
-        <v>128</v>
+        <v>132</v>
       </c>
       <c r="F9">
         <v>-10</v>
@@ -3259,13 +3331,13 @@
     </row>
     <row r="10" spans="1:11">
       <c r="A10" t="s">
-        <v>129</v>
+        <v>133</v>
       </c>
       <c r="C10" t="s">
         <v>83</v>
       </c>
       <c r="D10" t="s">
-        <v>130</v>
+        <v>134</v>
       </c>
       <c r="F10">
         <v>10</v>
@@ -3276,13 +3348,13 @@
     </row>
     <row r="11" spans="1:11">
       <c r="A11" t="s">
-        <v>131</v>
+        <v>135</v>
       </c>
       <c r="C11" t="s">
         <v>94</v>
       </c>
       <c r="D11" t="s">
-        <v>132</v>
+        <v>136</v>
       </c>
       <c r="F11">
         <v>10</v>
@@ -3293,13 +3365,13 @@
     </row>
     <row r="12" spans="1:11">
       <c r="A12" t="s">
-        <v>133</v>
+        <v>137</v>
       </c>
       <c r="C12" t="s">
         <v>86</v>
       </c>
       <c r="D12" t="s">
-        <v>134</v>
+        <v>138</v>
       </c>
       <c r="F12">
         <v>-20</v>
@@ -3310,13 +3382,13 @@
     </row>
     <row r="13" spans="1:12">
       <c r="A13" t="s">
-        <v>135</v>
+        <v>139</v>
       </c>
       <c r="C13" t="s">
         <v>61</v>
       </c>
       <c r="D13" t="s">
-        <v>136</v>
+        <v>140</v>
       </c>
       <c r="H13">
         <v>-10</v>
@@ -3327,13 +3399,13 @@
     </row>
     <row r="14" spans="1:12">
       <c r="A14" t="s">
-        <v>137</v>
+        <v>141</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>138</v>
+        <v>142</v>
       </c>
       <c r="H14">
         <v>-10</v>
@@ -3344,13 +3416,13 @@
     </row>
     <row r="15" spans="1:11">
       <c r="A15" t="s">
-        <v>139</v>
+        <v>143</v>
       </c>
       <c r="C15" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D15" t="s">
-        <v>140</v>
+        <v>144</v>
       </c>
       <c r="F15">
         <v>10</v>
@@ -3361,10 +3433,10 @@
     </row>
     <row r="16" spans="1:16">
       <c r="A16" t="s">
-        <v>141</v>
+        <v>145</v>
       </c>
       <c r="D16" t="s">
-        <v>142</v>
+        <v>146</v>
       </c>
       <c r="L16">
         <v>-40</v>
@@ -3375,10 +3447,10 @@
     </row>
     <row r="17" spans="1:11">
       <c r="A17" t="s">
-        <v>143</v>
+        <v>147</v>
       </c>
       <c r="D17" t="s">
-        <v>144</v>
+        <v>148</v>
       </c>
       <c r="F17">
         <v>-40</v>
@@ -3392,10 +3464,10 @@
     </row>
     <row r="18" spans="1:12">
       <c r="A18" t="s">
-        <v>145</v>
+        <v>149</v>
       </c>
       <c r="D18" t="s">
-        <v>146</v>
+        <v>150</v>
       </c>
       <c r="K18">
         <v>-40</v>
@@ -3406,10 +3478,10 @@
     </row>
     <row r="19" spans="1:12">
       <c r="A19" t="s">
-        <v>147</v>
+        <v>151</v>
       </c>
       <c r="D19" t="s">
-        <v>148</v>
+        <v>152</v>
       </c>
       <c r="H19">
         <v>-10</v>
@@ -3423,13 +3495,13 @@
     </row>
     <row r="20" spans="1:11">
       <c r="A20" t="s">
-        <v>149</v>
+        <v>153</v>
       </c>
       <c r="C20" t="s">
         <v>36</v>
       </c>
       <c r="D20" t="s">
-        <v>150</v>
+        <v>154</v>
       </c>
       <c r="H20">
         <v>10</v>
@@ -3440,13 +3512,13 @@
     </row>
     <row r="21" spans="1:11">
       <c r="A21" t="s">
-        <v>151</v>
+        <v>155</v>
       </c>
       <c r="C21" t="s">
         <v>41</v>
       </c>
       <c r="D21" t="s">
-        <v>152</v>
+        <v>156</v>
       </c>
       <c r="H21">
         <v>10</v>
@@ -3457,13 +3529,13 @@
     </row>
     <row r="22" spans="1:11">
       <c r="A22" t="s">
-        <v>153</v>
+        <v>157</v>
       </c>
       <c r="C22" t="s">
         <v>48</v>
       </c>
       <c r="D22" t="s">
-        <v>154</v>
+        <v>158</v>
       </c>
       <c r="H22">
         <v>10</v>
@@ -3482,7 +3554,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V45"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
@@ -3562,13 +3634,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" t="s">
-        <v>155</v>
+        <v>159</v>
       </c>
       <c r="B2" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>157</v>
+        <v>161</v>
       </c>
       <c r="F2">
         <v>10</v>
@@ -3577,13 +3649,13 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" t="s">
-        <v>158</v>
+        <v>162</v>
       </c>
       <c r="B3" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>160</v>
+        <v>164</v>
       </c>
       <c r="F3">
         <v>7</v>
@@ -3592,13 +3664,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" t="s">
-        <v>161</v>
+        <v>165</v>
       </c>
       <c r="C4" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>162</v>
+        <v>166</v>
       </c>
       <c r="K4">
         <v>5</v>
@@ -3607,13 +3679,13 @@
     </row>
     <row r="5" spans="1:17">
       <c r="A5" t="s">
-        <v>163</v>
+        <v>167</v>
       </c>
       <c r="B5" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>164</v>
+        <v>168</v>
       </c>
       <c r="Q5" t="s">
         <v>50</v>
@@ -3621,16 +3693,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" t="s">
-        <v>165</v>
+        <v>169</v>
       </c>
       <c r="B6" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C6" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>167</v>
+        <v>171</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -3639,16 +3711,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" t="s">
-        <v>168</v>
+        <v>172</v>
       </c>
       <c r="B7" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C7" t="s">
         <v>83</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>170</v>
+        <v>174</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -3657,13 +3729,13 @@
     </row>
     <row r="8" spans="1:17">
       <c r="A8" t="s">
-        <v>171</v>
+        <v>175</v>
       </c>
       <c r="B8" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>172</v>
+        <v>176</v>
       </c>
       <c r="Q8" t="s">
         <v>25</v>
@@ -3671,30 +3743,30 @@
     </row>
     <row r="9" spans="1:17">
       <c r="A9" t="s">
-        <v>173</v>
+        <v>177</v>
       </c>
       <c r="B9" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C9" t="s">
         <v>23</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>175</v>
+        <v>179</v>
       </c>
       <c r="Q9" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
     </row>
     <row r="10" spans="1:17">
       <c r="A10" t="s">
-        <v>177</v>
+        <v>181</v>
       </c>
       <c r="B10" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D10" s="1" t="s">
-        <v>179</v>
+        <v>183</v>
       </c>
       <c r="L10">
         <v>7</v>
@@ -3703,13 +3775,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" t="s">
-        <v>180</v>
+        <v>184</v>
       </c>
       <c r="C11" t="s">
         <v>61</v>
       </c>
       <c r="D11" s="1" t="s">
-        <v>181</v>
+        <v>185</v>
       </c>
       <c r="F11">
         <v>7</v>
@@ -3718,16 +3790,16 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" t="s">
-        <v>182</v>
+        <v>186</v>
       </c>
       <c r="B12" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C12" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D12" s="1" t="s">
-        <v>183</v>
+        <v>187</v>
       </c>
       <c r="E12"/>
       <c r="F12" s="1">
@@ -3741,16 +3813,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" t="s">
-        <v>184</v>
+        <v>188</v>
       </c>
       <c r="B13" s="1" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C13" s="1" t="s">
         <v>91</v>
       </c>
       <c r="D13" s="1" t="s">
-        <v>185</v>
+        <v>189</v>
       </c>
       <c r="E13"/>
       <c r="H13" s="1">
@@ -3764,16 +3836,16 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" t="s">
-        <v>186</v>
+        <v>190</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C14" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D14" s="1" t="s">
-        <v>187</v>
+        <v>191</v>
       </c>
       <c r="E14"/>
       <c r="F14" s="1">
@@ -3787,13 +3859,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" t="s">
-        <v>188</v>
+        <v>192</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D15" s="1" t="s">
-        <v>189</v>
+        <v>193</v>
       </c>
       <c r="E15"/>
       <c r="F15" s="1">
@@ -3807,16 +3879,16 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" t="s">
-        <v>190</v>
+        <v>194</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C16" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>191</v>
+        <v>195</v>
       </c>
       <c r="E16"/>
       <c r="F16" s="1">
@@ -3830,16 +3902,16 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" t="s">
-        <v>192</v>
+        <v>196</v>
       </c>
       <c r="B17" s="1" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C17" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D17" s="1" t="s">
-        <v>193</v>
+        <v>197</v>
       </c>
       <c r="E17"/>
       <c r="H17" s="1">
@@ -3853,13 +3925,13 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" t="s">
-        <v>194</v>
+        <v>198</v>
       </c>
       <c r="B18" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D18" s="1" t="s">
-        <v>195</v>
+        <v>199</v>
       </c>
       <c r="E18"/>
       <c r="I18" s="1">
@@ -3873,16 +3945,16 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" t="s">
-        <v>196</v>
+        <v>200</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C19" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D19" s="1" t="s">
-        <v>197</v>
+        <v>201</v>
       </c>
       <c r="E19"/>
       <c r="F19" s="1">
@@ -3896,13 +3968,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" t="s">
-        <v>198</v>
+        <v>202</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="D20" s="1" t="s">
-        <v>199</v>
+        <v>203</v>
       </c>
       <c r="E20"/>
       <c r="H20" s="1">
@@ -3916,13 +3988,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" t="s">
-        <v>200</v>
+        <v>204</v>
       </c>
       <c r="B21" s="1" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D21" s="1" t="s">
-        <v>201</v>
+        <v>205</v>
       </c>
       <c r="E21"/>
       <c r="K21" s="1">
@@ -3936,13 +4008,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" t="s">
-        <v>202</v>
+        <v>206</v>
       </c>
       <c r="C22" s="1" t="s">
         <v>23</v>
       </c>
       <c r="D22" s="1" t="s">
-        <v>203</v>
+        <v>207</v>
       </c>
       <c r="E22"/>
       <c r="N22" s="1">
@@ -3956,13 +4028,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" t="s">
-        <v>204</v>
+        <v>208</v>
       </c>
       <c r="C23" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D23" s="1" t="s">
-        <v>205</v>
+        <v>209</v>
       </c>
       <c r="E23"/>
       <c r="K23" s="1">
@@ -3976,13 +4048,13 @@
     </row>
     <row r="24" spans="1:11">
       <c r="A24" t="s">
-        <v>206</v>
+        <v>210</v>
       </c>
       <c r="C24" s="1" t="s">
         <v>86</v>
       </c>
       <c r="D24" s="1" t="s">
-        <v>207</v>
+        <v>211</v>
       </c>
       <c r="K24">
         <v>5</v>
@@ -3990,44 +4062,44 @@
     </row>
     <row r="25" spans="1:17">
       <c r="A25" t="s">
-        <v>208</v>
+        <v>212</v>
       </c>
       <c r="B25" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D25" s="1" t="s">
-        <v>210</v>
+        <v>214</v>
       </c>
       <c r="Q25" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="26" spans="1:17">
       <c r="A26" t="s">
-        <v>212</v>
+        <v>216</v>
       </c>
       <c r="B26" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D26" s="1" t="s">
-        <v>213</v>
+        <v>217</v>
       </c>
       <c r="Q26" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="27" spans="1:6">
       <c r="A27" t="s">
-        <v>215</v>
+        <v>219</v>
       </c>
       <c r="B27" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>83</v>
       </c>
       <c r="D27" s="1" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F27">
         <v>5</v>
@@ -4035,13 +4107,13 @@
     </row>
     <row r="28" spans="1:6">
       <c r="A28" t="s">
-        <v>217</v>
+        <v>221</v>
       </c>
       <c r="B28" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D28" s="1" t="s">
-        <v>218</v>
+        <v>222</v>
       </c>
       <c r="F28">
         <v>5</v>
@@ -4049,13 +4121,13 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" t="s">
-        <v>219</v>
+        <v>223</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D29" s="1" t="s">
-        <v>220</v>
+        <v>224</v>
       </c>
       <c r="F29">
         <v>5</v>
@@ -4063,16 +4135,16 @@
     </row>
     <row r="30" spans="1:7">
       <c r="A30" t="s">
-        <v>221</v>
+        <v>225</v>
       </c>
       <c r="B30" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C30" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D30" s="1" t="s">
-        <v>222</v>
+        <v>226</v>
       </c>
       <c r="G30">
         <v>5</v>
@@ -4080,13 +4152,13 @@
     </row>
     <row r="31" spans="1:12">
       <c r="A31" t="s">
-        <v>223</v>
+        <v>227</v>
       </c>
       <c r="B31" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D31" s="1" t="s">
-        <v>224</v>
+        <v>228</v>
       </c>
       <c r="L31">
         <v>8</v>
@@ -4094,16 +4166,16 @@
     </row>
     <row r="32" spans="1:14">
       <c r="A32" t="s">
-        <v>225</v>
+        <v>229</v>
       </c>
       <c r="B32" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C32" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D32" s="1" t="s">
-        <v>226</v>
+        <v>230</v>
       </c>
       <c r="N32">
         <v>2</v>
@@ -4111,16 +4183,16 @@
     </row>
     <row r="33" spans="1:8">
       <c r="A33" t="s">
-        <v>227</v>
+        <v>231</v>
       </c>
       <c r="B33" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C33" t="s">
         <v>86</v>
       </c>
       <c r="D33" s="1" t="s">
-        <v>228</v>
+        <v>232</v>
       </c>
       <c r="H33">
         <v>7</v>
@@ -4128,13 +4200,13 @@
     </row>
     <row r="34" spans="1:12">
       <c r="A34" t="s">
-        <v>229</v>
+        <v>233</v>
       </c>
       <c r="B34" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D34" s="1" t="s">
-        <v>230</v>
+        <v>234</v>
       </c>
       <c r="L34">
         <v>5</v>
@@ -4142,16 +4214,16 @@
     </row>
     <row r="35" spans="1:8">
       <c r="A35" t="s">
-        <v>231</v>
+        <v>235</v>
       </c>
       <c r="B35" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C35" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D35" s="1" t="s">
-        <v>232</v>
+        <v>236</v>
       </c>
       <c r="H35">
         <v>7</v>
@@ -4159,16 +4231,16 @@
     </row>
     <row r="36" spans="1:6">
       <c r="A36" t="s">
-        <v>233</v>
+        <v>237</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C36" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D36" s="1" t="s">
-        <v>234</v>
+        <v>238</v>
       </c>
       <c r="F36">
         <v>5</v>
@@ -4176,16 +4248,16 @@
     </row>
     <row r="37" spans="1:6">
       <c r="A37" t="s">
-        <v>235</v>
+        <v>239</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
       <c r="D37" s="1" t="s">
-        <v>236</v>
+        <v>240</v>
       </c>
       <c r="F37">
         <v>7</v>
@@ -4193,16 +4265,16 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" t="s">
-        <v>237</v>
+        <v>241</v>
       </c>
       <c r="B38" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" s="1" t="s">
-        <v>238</v>
+        <v>242</v>
       </c>
       <c r="F38">
         <v>7</v>
@@ -4210,33 +4282,33 @@
     </row>
     <row r="39" spans="1:17">
       <c r="A39" t="s">
-        <v>239</v>
+        <v>243</v>
       </c>
       <c r="B39" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C39" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D39" s="5" t="s">
-        <v>240</v>
+        <v>244</v>
       </c>
       <c r="Q39" t="s">
-        <v>214</v>
+        <v>218</v>
       </c>
     </row>
     <row r="40" spans="1:12">
       <c r="A40" t="s">
-        <v>241</v>
+        <v>245</v>
       </c>
       <c r="B40" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C40" t="s">
-        <v>110</v>
+        <v>114</v>
       </c>
       <c r="D40" s="1" t="s">
-        <v>242</v>
+        <v>246</v>
       </c>
       <c r="L40">
         <v>5</v>
@@ -4244,16 +4316,16 @@
     </row>
     <row r="41" spans="1:8">
       <c r="A41" t="s">
-        <v>243</v>
+        <v>247</v>
       </c>
       <c r="B41" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C41" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D41" s="1" t="s">
-        <v>244</v>
+        <v>248</v>
       </c>
       <c r="H41">
         <v>5</v>
@@ -4261,13 +4333,13 @@
     </row>
     <row r="42" spans="1:6">
       <c r="A42" t="s">
-        <v>245</v>
+        <v>249</v>
       </c>
       <c r="B42" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D42" s="1" t="s">
-        <v>246</v>
+        <v>250</v>
       </c>
       <c r="F42">
         <v>11</v>
@@ -4275,27 +4347,27 @@
     </row>
     <row r="43" spans="1:17">
       <c r="A43" t="s">
-        <v>247</v>
+        <v>251</v>
       </c>
       <c r="B43" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D43" s="1" t="s">
-        <v>248</v>
+        <v>252</v>
       </c>
       <c r="Q43" t="s">
-        <v>211</v>
+        <v>215</v>
       </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" t="s">
-        <v>249</v>
+        <v>253</v>
       </c>
       <c r="B44" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D44" s="1" t="s">
-        <v>250</v>
+        <v>254</v>
       </c>
       <c r="H44">
         <v>10</v>
@@ -4303,13 +4375,13 @@
     </row>
     <row r="45" spans="1:9">
       <c r="A45" t="s">
-        <v>251</v>
+        <v>255</v>
       </c>
       <c r="B45" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D45" s="1" t="s">
-        <v>252</v>
+        <v>256</v>
       </c>
       <c r="I45">
         <v>7</v>
@@ -4325,7 +4397,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V71"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
@@ -4405,16 +4477,16 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>253</v>
+        <v>257</v>
       </c>
       <c r="B2" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C2" t="s">
         <v>83</v>
       </c>
       <c r="D2" t="s">
-        <v>254</v>
+        <v>258</v>
       </c>
       <c r="L2">
         <v>3</v>
@@ -4423,16 +4495,16 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>255</v>
+        <v>259</v>
       </c>
       <c r="B3" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C3" t="s">
         <v>23</v>
       </c>
       <c r="D3" t="s">
-        <v>256</v>
+        <v>260</v>
       </c>
       <c r="F3">
         <v>3</v>
@@ -4441,13 +4513,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>257</v>
+        <v>261</v>
       </c>
       <c r="B4" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D4" t="s">
-        <v>258</v>
+        <v>262</v>
       </c>
       <c r="O4">
         <v>3</v>
@@ -4456,16 +4528,16 @@
     </row>
     <row r="5" spans="1:6">
       <c r="A5" s="2" t="s">
-        <v>259</v>
+        <v>263</v>
       </c>
       <c r="B5" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C5" t="s">
         <v>23</v>
       </c>
       <c r="D5" t="s">
-        <v>260</v>
+        <v>264</v>
       </c>
       <c r="F5">
         <v>3</v>
@@ -4473,16 +4545,16 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>261</v>
+        <v>265</v>
       </c>
       <c r="B6" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C6" t="s">
         <v>23</v>
       </c>
       <c r="D6" t="s">
-        <v>262</v>
+        <v>266</v>
       </c>
       <c r="M6">
         <v>3</v>
@@ -4491,16 +4563,16 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>263</v>
+        <v>267</v>
       </c>
       <c r="B7" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C7" t="s">
         <v>23</v>
       </c>
       <c r="D7" t="s">
-        <v>264</v>
+        <v>268</v>
       </c>
       <c r="G7">
         <v>3</v>
@@ -4509,16 +4581,16 @@
     </row>
     <row r="8" spans="1:13">
       <c r="A8" s="2" t="s">
-        <v>265</v>
+        <v>269</v>
       </c>
       <c r="B8" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C8" t="s">
         <v>61</v>
       </c>
       <c r="D8" t="s">
-        <v>266</v>
+        <v>270</v>
       </c>
       <c r="M8">
         <v>3</v>
@@ -4526,13 +4598,13 @@
     </row>
     <row r="9" spans="1:6">
       <c r="A9" s="2" t="s">
-        <v>267</v>
+        <v>271</v>
       </c>
       <c r="B9" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D9" t="s">
-        <v>268</v>
+        <v>272</v>
       </c>
       <c r="F9">
         <v>3</v>
@@ -4540,13 +4612,13 @@
     </row>
     <row r="10" spans="1:17">
       <c r="A10" s="2" t="s">
-        <v>269</v>
+        <v>273</v>
       </c>
       <c r="B10" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D10" t="s">
-        <v>270</v>
+        <v>274</v>
       </c>
       <c r="K10">
         <v>2</v>
@@ -4555,13 +4627,13 @@
     </row>
     <row r="11" spans="1:17">
       <c r="A11" s="2" t="s">
-        <v>271</v>
+        <v>275</v>
       </c>
       <c r="C11" t="s">
         <v>83</v>
       </c>
       <c r="D11" t="s">
-        <v>272</v>
+        <v>276</v>
       </c>
       <c r="F11">
         <v>2</v>
@@ -4570,16 +4642,16 @@
     </row>
     <row r="12" s="1" customFormat="1" spans="1:22">
       <c r="A12" s="2" t="s">
-        <v>273</v>
+        <v>277</v>
       </c>
       <c r="B12" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C12" t="s">
         <v>64</v>
       </c>
       <c r="D12" t="s">
-        <v>274</v>
+        <v>278</v>
       </c>
       <c r="E12"/>
       <c r="I12">
@@ -4593,16 +4665,16 @@
     </row>
     <row r="13" s="1" customFormat="1" spans="1:22">
       <c r="A13" s="2" t="s">
-        <v>275</v>
+        <v>279</v>
       </c>
       <c r="B13" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="C13" t="s">
         <v>91</v>
       </c>
       <c r="D13" t="s">
-        <v>276</v>
+        <v>280</v>
       </c>
       <c r="E13"/>
       <c r="F13">
@@ -4616,16 +4688,16 @@
     </row>
     <row r="14" s="1" customFormat="1" spans="1:22">
       <c r="A14" s="2" t="s">
-        <v>277</v>
+        <v>281</v>
       </c>
       <c r="B14" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C14" t="s">
         <v>23</v>
       </c>
       <c r="D14" t="s">
-        <v>278</v>
+        <v>282</v>
       </c>
       <c r="E14"/>
       <c r="G14">
@@ -4639,13 +4711,13 @@
     </row>
     <row r="15" s="1" customFormat="1" spans="1:22">
       <c r="A15" s="2" t="s">
-        <v>279</v>
+        <v>283</v>
       </c>
       <c r="B15" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D15" t="s">
-        <v>280</v>
+        <v>284</v>
       </c>
       <c r="E15"/>
       <c r="F15">
@@ -4659,14 +4731,14 @@
     </row>
     <row r="16" s="1" customFormat="1" spans="1:22">
       <c r="A16" s="2" t="s">
-        <v>281</v>
+        <v>285</v>
       </c>
       <c r="B16" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="C16"/>
       <c r="D16" t="s">
-        <v>282</v>
+        <v>286</v>
       </c>
       <c r="E16"/>
       <c r="L16">
@@ -4680,11 +4752,11 @@
     </row>
     <row r="17" s="1" customFormat="1" spans="1:22">
       <c r="A17" s="2" t="s">
-        <v>283</v>
+        <v>287</v>
       </c>
       <c r="C17"/>
       <c r="D17" t="s">
-        <v>284</v>
+        <v>288</v>
       </c>
       <c r="E17"/>
       <c r="O17">
@@ -4698,16 +4770,16 @@
     </row>
     <row r="18" s="1" customFormat="1" spans="1:22">
       <c r="A18" s="2" t="s">
-        <v>285</v>
+        <v>289</v>
       </c>
       <c r="B18" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C18" t="s">
         <v>91</v>
       </c>
       <c r="D18" t="s">
-        <v>286</v>
+        <v>290</v>
       </c>
       <c r="E18"/>
       <c r="F18">
@@ -4721,16 +4793,16 @@
     </row>
     <row r="19" s="1" customFormat="1" spans="1:22">
       <c r="A19" s="2" t="s">
-        <v>287</v>
+        <v>291</v>
       </c>
       <c r="B19" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C19" t="s">
         <v>86</v>
       </c>
       <c r="D19" t="s">
-        <v>288</v>
+        <v>292</v>
       </c>
       <c r="E19"/>
       <c r="K19">
@@ -4744,13 +4816,13 @@
     </row>
     <row r="20" s="1" customFormat="1" spans="1:22">
       <c r="A20" s="2" t="s">
-        <v>289</v>
+        <v>293</v>
       </c>
       <c r="C20" t="s">
         <v>83</v>
       </c>
       <c r="D20" t="s">
-        <v>290</v>
+        <v>294</v>
       </c>
       <c r="E20"/>
       <c r="I20">
@@ -4764,13 +4836,13 @@
     </row>
     <row r="21" s="1" customFormat="1" spans="1:22">
       <c r="A21" s="2" t="s">
-        <v>291</v>
+        <v>295</v>
       </c>
       <c r="B21" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D21" t="s">
-        <v>292</v>
+        <v>296</v>
       </c>
       <c r="E21"/>
       <c r="I21">
@@ -4784,13 +4856,13 @@
     </row>
     <row r="22" s="1" customFormat="1" spans="1:22">
       <c r="A22" s="2" t="s">
-        <v>293</v>
+        <v>297</v>
       </c>
       <c r="C22" t="s">
         <v>91</v>
       </c>
       <c r="D22" t="s">
-        <v>294</v>
+        <v>298</v>
       </c>
       <c r="E22"/>
       <c r="K22">
@@ -4804,13 +4876,13 @@
     </row>
     <row r="23" s="1" customFormat="1" spans="1:22">
       <c r="A23" s="2" t="s">
-        <v>295</v>
+        <v>299</v>
       </c>
       <c r="C23" t="s">
         <v>83</v>
       </c>
       <c r="D23" t="s">
-        <v>296</v>
+        <v>300</v>
       </c>
       <c r="E23"/>
       <c r="H23">
@@ -4824,14 +4896,14 @@
     </row>
     <row r="24" spans="1:7">
       <c r="A24" s="2" t="s">
-        <v>297</v>
+        <v>301</v>
       </c>
       <c r="B24" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C24" s="1"/>
       <c r="D24" t="s">
-        <v>298</v>
+        <v>302</v>
       </c>
       <c r="G24">
         <v>3</v>
@@ -4839,16 +4911,16 @@
     </row>
     <row r="25" spans="1:6">
       <c r="A25" s="2" t="s">
-        <v>299</v>
+        <v>303</v>
       </c>
       <c r="B25" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C25" t="s">
         <v>83</v>
       </c>
       <c r="D25" t="s">
-        <v>300</v>
+        <v>304</v>
       </c>
       <c r="F25">
         <v>3</v>
@@ -4856,13 +4928,13 @@
     </row>
     <row r="26" spans="1:11">
       <c r="A26" s="2" t="s">
-        <v>301</v>
+        <v>305</v>
       </c>
       <c r="B26" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D26" t="s">
-        <v>302</v>
+        <v>306</v>
       </c>
       <c r="K26">
         <v>3</v>
@@ -4870,16 +4942,16 @@
     </row>
     <row r="27" spans="1:6">
       <c r="A27" s="2" t="s">
-        <v>303</v>
+        <v>307</v>
       </c>
       <c r="B27" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C27" s="1" t="s">
         <v>61</v>
       </c>
       <c r="D27" t="s">
-        <v>304</v>
+        <v>308</v>
       </c>
       <c r="F27">
         <v>3</v>
@@ -4887,16 +4959,16 @@
     </row>
     <row r="28" spans="1:12">
       <c r="A28" s="2" t="s">
-        <v>305</v>
+        <v>309</v>
       </c>
       <c r="B28" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C28" t="s">
         <v>83</v>
       </c>
       <c r="D28" t="s">
-        <v>306</v>
+        <v>310</v>
       </c>
       <c r="L28">
         <v>2</v>
@@ -4904,16 +4976,16 @@
     </row>
     <row r="29" spans="1:6">
       <c r="A29" s="2" t="s">
-        <v>307</v>
+        <v>311</v>
       </c>
       <c r="B29" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C29" t="s">
         <v>83</v>
       </c>
       <c r="D29" t="s">
-        <v>308</v>
+        <v>312</v>
       </c>
       <c r="F29">
         <v>2</v>
@@ -4921,13 +4993,13 @@
     </row>
     <row r="30" spans="1:11">
       <c r="A30" s="2" t="s">
-        <v>309</v>
+        <v>313</v>
       </c>
       <c r="B30" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="D30" t="s">
-        <v>310</v>
+        <v>314</v>
       </c>
       <c r="K30">
         <v>2</v>
@@ -4935,13 +5007,13 @@
     </row>
     <row r="31" spans="1:7">
       <c r="A31" s="2" t="s">
-        <v>311</v>
+        <v>315</v>
       </c>
       <c r="C31" t="s">
         <v>36</v>
       </c>
       <c r="D31" t="s">
-        <v>312</v>
+        <v>316</v>
       </c>
       <c r="G31">
         <v>2</v>
@@ -4949,16 +5021,16 @@
     </row>
     <row r="32" spans="1:6">
       <c r="A32" s="2" t="s">
-        <v>313</v>
+        <v>317</v>
       </c>
       <c r="B32" t="s">
-        <v>178</v>
+        <v>182</v>
       </c>
       <c r="C32" t="s">
         <v>83</v>
       </c>
       <c r="D32" t="s">
-        <v>314</v>
+        <v>318</v>
       </c>
       <c r="F32">
         <v>2</v>
@@ -4966,13 +5038,13 @@
     </row>
     <row r="33" spans="1:12">
       <c r="A33" s="2" t="s">
-        <v>315</v>
+        <v>319</v>
       </c>
       <c r="B33" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D33" t="s">
-        <v>316</v>
+        <v>320</v>
       </c>
       <c r="L33">
         <v>2</v>
@@ -4980,13 +5052,13 @@
     </row>
     <row r="34" spans="1:11">
       <c r="A34" s="2" t="s">
-        <v>317</v>
+        <v>321</v>
       </c>
       <c r="B34" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D34" t="s">
-        <v>318</v>
+        <v>322</v>
       </c>
       <c r="K34">
         <v>3</v>
@@ -4994,16 +5066,16 @@
     </row>
     <row r="35" spans="1:11">
       <c r="A35" s="2" t="s">
-        <v>319</v>
+        <v>323</v>
       </c>
       <c r="B35" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="C35" t="s">
         <v>23</v>
       </c>
       <c r="D35" t="s">
-        <v>320</v>
+        <v>324</v>
       </c>
       <c r="K35">
         <v>3</v>
@@ -5011,13 +5083,13 @@
     </row>
     <row r="36" spans="1:15">
       <c r="A36" s="2" t="s">
-        <v>321</v>
+        <v>325</v>
       </c>
       <c r="B36" t="s">
-        <v>174</v>
+        <v>178</v>
       </c>
       <c r="D36" t="s">
-        <v>322</v>
+        <v>326</v>
       </c>
       <c r="O36">
         <v>2</v>
@@ -5025,16 +5097,16 @@
     </row>
     <row r="37" spans="1:12">
       <c r="A37" s="2" t="s">
-        <v>323</v>
+        <v>327</v>
       </c>
       <c r="B37" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C37" t="s">
         <v>61</v>
       </c>
       <c r="D37" t="s">
-        <v>324</v>
+        <v>328</v>
       </c>
       <c r="L37">
         <v>2</v>
@@ -5042,13 +5114,13 @@
     </row>
     <row r="38" spans="1:6">
       <c r="A38" s="2" t="s">
-        <v>325</v>
+        <v>329</v>
       </c>
       <c r="C38" t="s">
         <v>83</v>
       </c>
       <c r="D38" t="s">
-        <v>326</v>
+        <v>330</v>
       </c>
       <c r="F38">
         <v>1</v>
@@ -5056,16 +5128,16 @@
     </row>
     <row r="39" spans="1:11">
       <c r="A39" s="2" t="s">
-        <v>327</v>
+        <v>331</v>
       </c>
       <c r="B39" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C39" t="s">
         <v>57</v>
       </c>
       <c r="D39" t="s">
-        <v>328</v>
+        <v>332</v>
       </c>
       <c r="K39">
         <v>2</v>
@@ -5073,16 +5145,16 @@
     </row>
     <row r="40" spans="1:12">
       <c r="A40" s="2" t="s">
-        <v>329</v>
+        <v>333</v>
       </c>
       <c r="B40" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C40" t="s">
         <v>83</v>
       </c>
       <c r="D40" t="s">
-        <v>330</v>
+        <v>334</v>
       </c>
       <c r="L40">
         <v>2</v>
@@ -5090,16 +5162,16 @@
     </row>
     <row r="41" spans="1:6">
       <c r="A41" s="2" t="s">
-        <v>331</v>
+        <v>335</v>
       </c>
       <c r="B41" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C41" t="s">
         <v>64</v>
       </c>
       <c r="D41" t="s">
-        <v>332</v>
+        <v>336</v>
       </c>
       <c r="F41">
         <v>2</v>
@@ -5107,13 +5179,13 @@
     </row>
     <row r="42" spans="1:11">
       <c r="A42" s="2" t="s">
-        <v>333</v>
+        <v>337</v>
       </c>
       <c r="B42" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D42" t="s">
-        <v>334</v>
+        <v>338</v>
       </c>
       <c r="K42">
         <v>2</v>
@@ -5121,13 +5193,13 @@
     </row>
     <row r="43" spans="1:11">
       <c r="A43" s="2" t="s">
-        <v>335</v>
+        <v>339</v>
       </c>
       <c r="C43" t="s">
         <v>83</v>
       </c>
       <c r="D43" t="s">
-        <v>336</v>
+        <v>340</v>
       </c>
       <c r="K43">
         <v>2</v>
@@ -5135,13 +5207,13 @@
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="2" t="s">
-        <v>337</v>
+        <v>341</v>
       </c>
       <c r="C44" t="s">
         <v>91</v>
       </c>
       <c r="D44" t="s">
-        <v>338</v>
+        <v>342</v>
       </c>
       <c r="H44">
         <v>2</v>
@@ -5149,16 +5221,16 @@
     </row>
     <row r="45" spans="1:6">
       <c r="A45" s="2" t="s">
-        <v>339</v>
+        <v>343</v>
       </c>
       <c r="B45" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C45" t="s">
         <v>86</v>
       </c>
       <c r="D45" t="s">
-        <v>340</v>
+        <v>344</v>
       </c>
       <c r="F45">
         <v>5</v>
@@ -5166,13 +5238,13 @@
     </row>
     <row r="46" spans="1:6">
       <c r="A46" s="2" t="s">
-        <v>341</v>
+        <v>345</v>
       </c>
       <c r="B46" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D46" t="s">
-        <v>342</v>
+        <v>346</v>
       </c>
       <c r="F46">
         <v>5</v>
@@ -5180,13 +5252,13 @@
     </row>
     <row r="47" spans="1:6">
       <c r="A47" s="2" t="s">
-        <v>343</v>
+        <v>347</v>
       </c>
       <c r="B47" t="s">
-        <v>156</v>
+        <v>160</v>
       </c>
       <c r="D47" t="s">
-        <v>344</v>
+        <v>348</v>
       </c>
       <c r="F47">
         <v>3</v>
@@ -5194,10 +5266,10 @@
     </row>
     <row r="48" spans="1:15">
       <c r="A48" s="2" t="s">
-        <v>345</v>
+        <v>349</v>
       </c>
       <c r="D48" s="2" t="s">
-        <v>346</v>
+        <v>350</v>
       </c>
       <c r="O48">
         <v>1</v>
@@ -5205,13 +5277,13 @@
     </row>
     <row r="49" spans="1:7">
       <c r="A49" s="2" t="s">
-        <v>347</v>
+        <v>351</v>
       </c>
       <c r="C49" t="s">
         <v>36</v>
       </c>
       <c r="D49" t="s">
-        <v>348</v>
+        <v>352</v>
       </c>
       <c r="G49">
         <v>3</v>
@@ -5219,13 +5291,13 @@
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="2" t="s">
-        <v>349</v>
+        <v>353</v>
       </c>
       <c r="B50" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D50" t="s">
-        <v>350</v>
+        <v>354</v>
       </c>
       <c r="H50">
         <v>2</v>
@@ -5233,13 +5305,13 @@
     </row>
     <row r="51" spans="1:12">
       <c r="A51" s="2" t="s">
-        <v>351</v>
+        <v>355</v>
       </c>
       <c r="C51" t="s">
         <v>86</v>
       </c>
       <c r="D51" t="s">
-        <v>352</v>
+        <v>356</v>
       </c>
       <c r="L51">
         <v>3</v>
@@ -5247,13 +5319,13 @@
     </row>
     <row r="52" spans="1:7">
       <c r="A52" s="2" t="s">
-        <v>353</v>
+        <v>357</v>
       </c>
       <c r="C52" t="s">
         <v>23</v>
       </c>
       <c r="D52" t="s">
-        <v>354</v>
+        <v>358</v>
       </c>
       <c r="G52">
         <v>3</v>
@@ -5261,16 +5333,16 @@
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="2" t="s">
-        <v>355</v>
+        <v>359</v>
       </c>
       <c r="B53" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C53" t="s">
         <v>91</v>
       </c>
       <c r="D53" t="s">
-        <v>356</v>
+        <v>360</v>
       </c>
       <c r="H53">
         <v>5</v>
@@ -5278,13 +5350,13 @@
     </row>
     <row r="54" spans="1:9">
       <c r="A54" s="2" t="s">
-        <v>357</v>
+        <v>361</v>
       </c>
       <c r="B54" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D54" t="s">
-        <v>358</v>
+        <v>362</v>
       </c>
       <c r="I54">
         <v>10</v>
@@ -5292,13 +5364,13 @@
     </row>
     <row r="55" spans="1:9">
       <c r="A55" s="2" t="s">
-        <v>359</v>
+        <v>363</v>
       </c>
       <c r="B55" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D55" t="s">
-        <v>360</v>
+        <v>364</v>
       </c>
       <c r="I55">
         <v>10</v>
@@ -5306,13 +5378,13 @@
     </row>
     <row r="56" spans="1:7">
       <c r="A56" s="2" t="s">
-        <v>361</v>
+        <v>365</v>
       </c>
       <c r="B56" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D56" t="s">
-        <v>362</v>
+        <v>366</v>
       </c>
       <c r="G56">
         <v>5</v>
@@ -5320,13 +5392,13 @@
     </row>
     <row r="57" spans="1:9">
       <c r="A57" s="2" t="s">
-        <v>363</v>
+        <v>367</v>
       </c>
       <c r="B57" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="D57" t="s">
-        <v>364</v>
+        <v>368</v>
       </c>
       <c r="I57">
         <v>10</v>
@@ -5334,13 +5406,13 @@
     </row>
     <row r="58" spans="1:9">
       <c r="A58" s="2" t="s">
-        <v>365</v>
+        <v>369</v>
       </c>
       <c r="B58" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D58" t="s">
-        <v>366</v>
+        <v>370</v>
       </c>
       <c r="I58">
         <v>10</v>
@@ -5348,13 +5420,13 @@
     </row>
     <row r="59" spans="1:7">
       <c r="A59" s="2" t="s">
-        <v>367</v>
+        <v>371</v>
       </c>
       <c r="B59" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D59" t="s">
-        <v>368</v>
+        <v>372</v>
       </c>
       <c r="G59">
         <v>3</v>
@@ -5362,16 +5434,16 @@
     </row>
     <row r="60" spans="1:6">
       <c r="A60" s="2" t="s">
-        <v>369</v>
+        <v>373</v>
       </c>
       <c r="B60" t="s">
-        <v>169</v>
+        <v>173</v>
       </c>
       <c r="C60" t="s">
         <v>86</v>
       </c>
       <c r="D60" t="s">
-        <v>370</v>
+        <v>374</v>
       </c>
       <c r="F60">
         <v>5</v>
@@ -5379,13 +5451,13 @@
     </row>
     <row r="61" spans="1:6">
       <c r="A61" s="2" t="s">
-        <v>371</v>
+        <v>375</v>
       </c>
       <c r="C61" t="s">
         <v>83</v>
       </c>
       <c r="D61" t="s">
-        <v>372</v>
+        <v>376</v>
       </c>
       <c r="F61">
         <v>3</v>
@@ -5393,16 +5465,16 @@
     </row>
     <row r="62" spans="1:13">
       <c r="A62" s="2" t="s">
-        <v>373</v>
+        <v>377</v>
       </c>
       <c r="B62" t="s">
-        <v>121</v>
+        <v>125</v>
       </c>
       <c r="C62" t="s">
         <v>36</v>
       </c>
       <c r="D62" t="s">
-        <v>374</v>
+        <v>378</v>
       </c>
       <c r="M62">
         <v>2</v>
@@ -5410,13 +5482,13 @@
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="2" t="s">
-        <v>375</v>
+        <v>379</v>
       </c>
       <c r="B63" t="s">
-        <v>166</v>
+        <v>170</v>
       </c>
       <c r="D63" t="s">
-        <v>376</v>
+        <v>380</v>
       </c>
       <c r="H63">
         <v>5</v>
@@ -5424,16 +5496,16 @@
     </row>
     <row r="64" spans="1:7">
       <c r="A64" s="2" t="s">
-        <v>377</v>
+        <v>381</v>
       </c>
       <c r="B64" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="C64" t="s">
         <v>23</v>
       </c>
       <c r="D64" t="s">
-        <v>378</v>
+        <v>382</v>
       </c>
       <c r="G64">
         <v>5</v>
@@ -5441,13 +5513,13 @@
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="2" t="s">
-        <v>379</v>
+        <v>383</v>
       </c>
       <c r="B65" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D65" t="s">
-        <v>380</v>
+        <v>384</v>
       </c>
       <c r="H65">
         <v>5</v>
@@ -5455,13 +5527,13 @@
     </row>
     <row r="66" spans="1:15">
       <c r="A66" s="2" t="s">
-        <v>381</v>
+        <v>385</v>
       </c>
       <c r="B66" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D66" t="s">
-        <v>382</v>
+        <v>386</v>
       </c>
       <c r="O66">
         <v>9</v>
@@ -5469,13 +5541,13 @@
     </row>
     <row r="67" spans="1:6">
       <c r="A67" s="2" t="s">
-        <v>383</v>
+        <v>387</v>
       </c>
       <c r="B67" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D67" t="s">
-        <v>384</v>
+        <v>388</v>
       </c>
       <c r="F67">
         <v>5</v>
@@ -5483,13 +5555,13 @@
     </row>
     <row r="68" spans="1:9">
       <c r="A68" s="2" t="s">
-        <v>385</v>
+        <v>389</v>
       </c>
       <c r="B68" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D68" t="s">
-        <v>386</v>
+        <v>390</v>
       </c>
       <c r="I68">
         <v>10</v>
@@ -5497,13 +5569,13 @@
     </row>
     <row r="69" spans="1:15">
       <c r="A69" s="2" t="s">
-        <v>387</v>
+        <v>391</v>
       </c>
       <c r="B69" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="D69" t="s">
-        <v>388</v>
+        <v>392</v>
       </c>
       <c r="O69">
         <v>6</v>
@@ -5511,13 +5583,13 @@
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="2" t="s">
-        <v>389</v>
+        <v>393</v>
       </c>
       <c r="B70" t="s">
-        <v>159</v>
+        <v>163</v>
       </c>
       <c r="D70" t="s">
-        <v>390</v>
+        <v>394</v>
       </c>
       <c r="H70">
         <v>5</v>
@@ -5525,16 +5597,16 @@
     </row>
     <row r="71" spans="1:6">
       <c r="A71" s="6" t="s">
-        <v>391</v>
+        <v>395</v>
       </c>
       <c r="B71" s="7" t="s">
-        <v>209</v>
+        <v>213</v>
       </c>
       <c r="C71" s="7" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D71" s="6" t="s">
-        <v>392</v>
+        <v>396</v>
       </c>
       <c r="F71">
         <v>8</v>
@@ -5550,7 +5622,7 @@
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
   <dimension ref="A1:V45"/>
-  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="13.5"/>
+  <sheetFormatPr defaultColWidth="8.83333333333333" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="17.1666666666667" customWidth="1"/>
     <col min="2" max="2" width="5.66666666666667" customWidth="1"/>
@@ -5630,13 +5702,13 @@
     </row>
     <row r="2" spans="1:17">
       <c r="A2" s="2" t="s">
-        <v>393</v>
+        <v>397</v>
       </c>
       <c r="C2" t="s">
-        <v>113</v>
+        <v>117</v>
       </c>
       <c r="D2" s="1" t="s">
-        <v>394</v>
+        <v>398</v>
       </c>
       <c r="G2">
         <v>5</v>
@@ -5645,10 +5717,10 @@
     </row>
     <row r="3" spans="1:17">
       <c r="A3" s="2" t="s">
-        <v>395</v>
+        <v>399</v>
       </c>
       <c r="D3" s="1" t="s">
-        <v>396</v>
+        <v>400</v>
       </c>
       <c r="N3">
         <v>1</v>
@@ -5657,13 +5729,13 @@
     </row>
     <row r="4" spans="1:17">
       <c r="A4" s="2" t="s">
-        <v>397</v>
+        <v>401</v>
       </c>
       <c r="C4" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D4" s="1" t="s">
-        <v>398</v>
+        <v>402</v>
       </c>
       <c r="F4">
         <v>5</v>
@@ -5672,10 +5744,10 @@
     </row>
     <row r="5" spans="1:15">
       <c r="A5" s="2" t="s">
-        <v>399</v>
+        <v>403</v>
       </c>
       <c r="D5" s="1" t="s">
-        <v>400</v>
+        <v>404</v>
       </c>
       <c r="O5">
         <v>5</v>
@@ -5683,10 +5755,10 @@
     </row>
     <row r="6" spans="1:17">
       <c r="A6" s="2" t="s">
-        <v>401</v>
+        <v>405</v>
       </c>
       <c r="D6" s="1" t="s">
-        <v>402</v>
+        <v>406</v>
       </c>
       <c r="I6">
         <v>5</v>
@@ -5695,13 +5767,13 @@
     </row>
     <row r="7" spans="1:17">
       <c r="A7" s="2" t="s">
-        <v>403</v>
+        <v>407</v>
       </c>
       <c r="C7" t="s">
-        <v>106</v>
+        <v>110</v>
       </c>
       <c r="D7" s="1" t="s">
-        <v>404</v>
+        <v>408</v>
       </c>
       <c r="H7">
         <v>7</v>
@@ -5710,10 +5782,10 @@
     </row>
     <row r="8" spans="1:12">
       <c r="A8" s="2" t="s">
-        <v>405</v>
+        <v>409</v>
       </c>
       <c r="D8" s="1" t="s">
-        <v>406</v>
+        <v>410</v>
       </c>
       <c r="L8">
         <v>5</v>
@@ -5721,10 +5793,10 @@
     </row>
     <row r="9" spans="1:11">
       <c r="A9" s="2" t="s">
-        <v>407</v>
+        <v>411</v>
       </c>
       <c r="D9" s="1" t="s">
-        <v>408</v>
+        <v>412</v>
       </c>
       <c r="K9">
         <v>5</v>
